--- a/artfynd/A 45199-2025 artfynd.xlsx
+++ b/artfynd/A 45199-2025 artfynd.xlsx
@@ -2525,45 +2525,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129538675</v>
+        <v>129539529</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440902</v>
+        <v>440725</v>
       </c>
       <c r="R19" t="n">
-        <v>6754135</v>
+        <v>6754011</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2595,7 +2600,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2605,7 +2610,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2632,38 +2637,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129539529</v>
+        <v>129538905</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2672,10 +2677,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440725</v>
+        <v>440970</v>
       </c>
       <c r="R20" t="n">
-        <v>6754011</v>
+        <v>6754114</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2707,7 +2712,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2717,7 +2722,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2744,38 +2749,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129538905</v>
+        <v>129543195</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2784,10 +2789,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440970</v>
+        <v>440708</v>
       </c>
       <c r="R21" t="n">
-        <v>6754114</v>
+        <v>6754371</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2819,7 +2824,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2829,7 +2834,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2844,62 +2849,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129543195</v>
+        <v>129543219</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440708</v>
+        <v>440890</v>
       </c>
       <c r="R22" t="n">
-        <v>6754371</v>
+        <v>6754082</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2968,7 +2968,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129543219</v>
+        <v>129538675</v>
       </c>
       <c r="B23" t="n">
         <v>79044</v>
@@ -3003,10 +3003,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440890</v>
+        <v>440902</v>
       </c>
       <c r="R23" t="n">
-        <v>6754082</v>
+        <v>6754135</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3063,12 +3063,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -5045,50 +5045,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129539589</v>
+        <v>129543145</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440769</v>
+        <v>440723</v>
       </c>
       <c r="R42" t="n">
-        <v>6754064</v>
+        <v>6754344</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5120,7 +5115,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5130,7 +5125,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5145,57 +5140,62 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129543145</v>
+        <v>129538433</v>
       </c>
       <c r="B43" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440723</v>
+        <v>440937</v>
       </c>
       <c r="R43" t="n">
-        <v>6754344</v>
+        <v>6754141</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5252,19 +5252,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129538433</v>
+        <v>129539589</v>
       </c>
       <c r="B44" t="n">
         <v>8450</v>
@@ -5304,10 +5304,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440937</v>
+        <v>440769</v>
       </c>
       <c r="R44" t="n">
-        <v>6754141</v>
+        <v>6754064</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5819,10 +5819,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129539404</v>
+        <v>129543220</v>
       </c>
       <c r="B49" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5830,39 +5830,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440775</v>
+        <v>440851</v>
       </c>
       <c r="R49" t="n">
-        <v>6753988</v>
+        <v>6754062</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5894,7 +5889,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5904,7 +5899,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5919,57 +5914,62 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129543220</v>
+        <v>129543198</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440851</v>
+        <v>440824</v>
       </c>
       <c r="R50" t="n">
-        <v>6754062</v>
+        <v>6754177</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6038,50 +6038,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129543198</v>
+        <v>129543236</v>
       </c>
       <c r="B51" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440824</v>
+        <v>440970</v>
       </c>
       <c r="R51" t="n">
-        <v>6754177</v>
+        <v>6754114</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6113,7 +6108,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6123,7 +6118,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6150,10 +6145,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129543236</v>
+        <v>129543166</v>
       </c>
       <c r="B52" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6161,34 +6156,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440970</v>
+        <v>440772</v>
       </c>
       <c r="R52" t="n">
-        <v>6754114</v>
+        <v>6754089</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6257,7 +6257,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129543166</v>
+        <v>129539404</v>
       </c>
       <c r="B53" t="n">
         <v>57724</v>
@@ -6297,10 +6297,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440772</v>
+        <v>440775</v>
       </c>
       <c r="R53" t="n">
-        <v>6754089</v>
+        <v>6753988</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6357,19 +6357,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129538256</v>
+        <v>129543185</v>
       </c>
       <c r="B54" t="n">
         <v>8450</v>
@@ -6400,7 +6400,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6409,10 +6409,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440944</v>
+        <v>440888</v>
       </c>
       <c r="R54" t="n">
-        <v>6754122</v>
+        <v>6754217</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6469,62 +6469,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129543185</v>
+        <v>129543230</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440888</v>
+        <v>440779</v>
       </c>
       <c r="R55" t="n">
-        <v>6754217</v>
+        <v>6754063</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6556,7 +6551,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6566,7 +6561,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6593,10 +6588,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129543230</v>
+        <v>129538554</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6604,21 +6599,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6628,10 +6623,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440779</v>
+        <v>440919</v>
       </c>
       <c r="R56" t="n">
-        <v>6754063</v>
+        <v>6754174</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6663,7 +6658,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6673,7 +6668,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6688,57 +6683,62 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129538554</v>
+        <v>129538256</v>
       </c>
       <c r="B57" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440919</v>
+        <v>440944</v>
       </c>
       <c r="R57" t="n">
-        <v>6754174</v>
+        <v>6754122</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7352,10 +7352,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129543157</v>
+        <v>129543245</v>
       </c>
       <c r="B63" t="n">
-        <v>57887</v>
+        <v>78710</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7363,39 +7363,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440759</v>
+        <v>440986</v>
       </c>
       <c r="R63" t="n">
-        <v>6754342</v>
+        <v>6754157</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7427,7 +7422,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7437,7 +7432,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7446,6 +7441,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7464,38 +7460,38 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129543179</v>
+        <v>129543157</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>57887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7504,10 +7500,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440821</v>
+        <v>440759</v>
       </c>
       <c r="R64" t="n">
-        <v>6754050</v>
+        <v>6754342</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7539,7 +7535,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7549,7 +7545,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7576,7 +7572,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129543176</v>
+        <v>129543179</v>
       </c>
       <c r="B65" t="n">
         <v>8450</v>
@@ -7607,7 +7603,7 @@
       <c r="I65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7616,10 +7612,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440820</v>
+        <v>440821</v>
       </c>
       <c r="R65" t="n">
-        <v>6754121</v>
+        <v>6754050</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7651,7 +7647,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7661,7 +7657,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7688,45 +7684,50 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129539371</v>
+        <v>129543176</v>
       </c>
       <c r="B66" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440769</v>
+        <v>440820</v>
       </c>
       <c r="R66" t="n">
-        <v>6754008</v>
+        <v>6754121</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7758,7 +7759,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7768,7 +7769,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7783,57 +7784,62 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129543245</v>
+        <v>129543192</v>
       </c>
       <c r="B67" t="n">
-        <v>78710</v>
+        <v>8450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>440986</v>
+        <v>440742</v>
       </c>
       <c r="R67" t="n">
-        <v>6754157</v>
+        <v>6754310</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7865,7 +7871,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7875,7 +7881,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7884,7 +7890,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7903,50 +7908,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129543192</v>
+        <v>129539371</v>
       </c>
       <c r="B68" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440742</v>
+        <v>440769</v>
       </c>
       <c r="R68" t="n">
-        <v>6754310</v>
+        <v>6754008</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8003,12 +8003,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8234,7 +8234,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129543143</v>
+        <v>129543141</v>
       </c>
       <c r="B71" t="n">
         <v>79663</v>
@@ -8269,10 +8269,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>440893</v>
+        <v>440974</v>
       </c>
       <c r="R71" t="n">
-        <v>6754230</v>
+        <v>6754141</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8304,7 +8304,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8341,45 +8341,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129543141</v>
+        <v>129543178</v>
       </c>
       <c r="B72" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>440974</v>
+        <v>440816</v>
       </c>
       <c r="R72" t="n">
-        <v>6754141</v>
+        <v>6754178</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8411,7 +8416,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8421,7 +8426,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8448,50 +8453,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129543178</v>
+        <v>129543143</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>440816</v>
+        <v>440893</v>
       </c>
       <c r="R73" t="n">
-        <v>6754178</v>
+        <v>6754230</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9320,50 +9320,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129538573</v>
+        <v>129543221</v>
       </c>
       <c r="B81" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>440932</v>
+        <v>440739</v>
       </c>
       <c r="R81" t="n">
-        <v>6754178</v>
+        <v>6754147</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9395,7 +9390,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9405,7 +9400,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9420,44 +9415,44 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129543221</v>
+        <v>129543164</v>
       </c>
       <c r="B82" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9467,10 +9462,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>440739</v>
+        <v>440708</v>
       </c>
       <c r="R82" t="n">
-        <v>6754147</v>
+        <v>6754116</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9502,7 +9497,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9512,7 +9507,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9539,32 +9539,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129543164</v>
+        <v>129543154</v>
       </c>
       <c r="B83" t="n">
-        <v>80178</v>
+        <v>90582</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>1962</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9574,10 +9574,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>440708</v>
+        <v>440770</v>
       </c>
       <c r="R83" t="n">
-        <v>6754116</v>
+        <v>6754101</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9619,12 +9619,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9651,45 +9646,50 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129543154</v>
+        <v>129543202</v>
       </c>
       <c r="B84" t="n">
-        <v>90582</v>
+        <v>8450</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>440770</v>
+        <v>440918</v>
       </c>
       <c r="R84" t="n">
-        <v>6754101</v>
+        <v>6754161</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9758,7 +9758,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129543202</v>
+        <v>129543173</v>
       </c>
       <c r="B85" t="n">
         <v>8450</v>
@@ -9789,7 +9789,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9798,10 +9798,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>440918</v>
+        <v>440917</v>
       </c>
       <c r="R85" t="n">
-        <v>6754161</v>
+        <v>6754255</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9870,7 +9870,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129543173</v>
+        <v>129543203</v>
       </c>
       <c r="B86" t="n">
         <v>8450</v>
@@ -9901,7 +9901,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9910,10 +9910,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>440917</v>
+        <v>440946</v>
       </c>
       <c r="R86" t="n">
-        <v>6754255</v>
+        <v>6754123</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9982,7 +9982,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129543203</v>
+        <v>129538573</v>
       </c>
       <c r="B87" t="n">
         <v>8450</v>
@@ -10013,7 +10013,7 @@
       <c r="I87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10022,10 +10022,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>440946</v>
+        <v>440932</v>
       </c>
       <c r="R87" t="n">
-        <v>6754123</v>
+        <v>6754178</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10082,12 +10082,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10522,50 +10522,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129543175</v>
+        <v>129543142</v>
       </c>
       <c r="B92" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>440896</v>
+        <v>440949</v>
       </c>
       <c r="R92" t="n">
-        <v>6754124</v>
+        <v>6754170</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10597,7 +10592,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10607,7 +10602,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10634,45 +10629,50 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129543142</v>
+        <v>129543175</v>
       </c>
       <c r="B93" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>440949</v>
+        <v>440896</v>
       </c>
       <c r="R93" t="n">
-        <v>6754170</v>
+        <v>6754124</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10704,7 +10704,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10714,7 +10714,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11841,10 +11841,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129538156</v>
+        <v>129543217</v>
       </c>
       <c r="B104" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11852,39 +11852,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>440982</v>
+        <v>440902</v>
       </c>
       <c r="R104" t="n">
-        <v>6754123</v>
+        <v>6754164</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11916,7 +11911,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11926,7 +11921,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11941,22 +11936,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129538088</v>
+        <v>129543247</v>
       </c>
       <c r="B105" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11964,21 +11959,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11988,10 +11983,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>441007</v>
+        <v>440894</v>
       </c>
       <c r="R105" t="n">
-        <v>6754124</v>
+        <v>6754104</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12023,7 +12018,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12033,7 +12028,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12042,28 +12037,29 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129543217</v>
+        <v>129538156</v>
       </c>
       <c r="B106" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12071,34 +12067,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>440902</v>
+        <v>440982</v>
       </c>
       <c r="R106" t="n">
-        <v>6754164</v>
+        <v>6754123</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12130,7 +12131,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12140,7 +12141,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12155,22 +12156,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129543247</v>
+        <v>129538088</v>
       </c>
       <c r="B107" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12178,21 +12179,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12202,10 +12203,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>440894</v>
+        <v>441007</v>
       </c>
       <c r="R107" t="n">
-        <v>6754104</v>
+        <v>6754124</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12237,7 +12238,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12247,7 +12248,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12256,19 +12257,18 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>

--- a/artfynd/A 45199-2025 artfynd.xlsx
+++ b/artfynd/A 45199-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129539413</v>
+        <v>129539829</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440775</v>
+        <v>440861</v>
       </c>
       <c r="R2" t="n">
-        <v>6753988</v>
+        <v>6754168</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129539829</v>
+        <v>129539413</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440861</v>
+        <v>440775</v>
       </c>
       <c r="R3" t="n">
-        <v>6754168</v>
+        <v>6753988</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1005,7 +1005,7 @@
         <v>129543238</v>
       </c>
       <c r="B5" t="n">
-        <v>91823</v>
+        <v>91826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129543183</v>
+        <v>129543239</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>80084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1120,39 +1120,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6457</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440945</v>
+        <v>440708</v>
       </c>
       <c r="R6" t="n">
-        <v>6754252</v>
+        <v>6754116</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,7 +1179,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1194,7 +1189,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,32 +1221,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129543239</v>
+        <v>129543147</v>
       </c>
       <c r="B7" t="n">
-        <v>80084</v>
+        <v>79663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6457</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440708</v>
+        <v>440701</v>
       </c>
       <c r="R7" t="n">
-        <v>6754116</v>
+        <v>6754185</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1301,12 +1301,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,10 +1328,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129543147</v>
+        <v>129539852</v>
       </c>
       <c r="B8" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1344,21 +1339,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1368,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440701</v>
+        <v>440880</v>
       </c>
       <c r="R8" t="n">
-        <v>6754185</v>
+        <v>6754175</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,7 +1398,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1413,7 +1408,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1428,44 +1423,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129543168</v>
+        <v>129539462</v>
       </c>
       <c r="B9" t="n">
-        <v>92836</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440718</v>
+        <v>440787</v>
       </c>
       <c r="R9" t="n">
-        <v>6754157</v>
+        <v>6753947</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,7 +1505,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1520,7 +1515,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,62 +1530,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129543191</v>
+        <v>129543168</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>92839</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>4365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440733</v>
+        <v>440718</v>
       </c>
       <c r="R10" t="n">
-        <v>6754283</v>
+        <v>6754157</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,7 +1612,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1632,7 +1622,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,45 +1649,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543158</v>
+        <v>129543183</v>
       </c>
       <c r="B11" t="n">
-        <v>91571</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440892</v>
+        <v>440945</v>
       </c>
       <c r="R11" t="n">
-        <v>6754225</v>
+        <v>6754252</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1724,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1739,7 +1734,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,45 +1761,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129539852</v>
+        <v>129543191</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440880</v>
+        <v>440733</v>
       </c>
       <c r="R12" t="n">
-        <v>6754175</v>
+        <v>6754283</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1861,57 +1861,62 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129539462</v>
+        <v>129539316</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440787</v>
+        <v>440779</v>
       </c>
       <c r="R13" t="n">
-        <v>6753947</v>
+        <v>6754008</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,50 +1985,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129539316</v>
+        <v>129543158</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>91574</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440779</v>
+        <v>440892</v>
       </c>
       <c r="R14" t="n">
-        <v>6754008</v>
+        <v>6754225</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2080,12 +2080,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2306,7 +2306,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129543182</v>
+        <v>129539028</v>
       </c>
       <c r="B17" t="n">
         <v>8450</v>
@@ -2335,21 +2335,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440934</v>
+        <v>440970</v>
       </c>
       <c r="R17" t="n">
-        <v>6754244</v>
+        <v>6754114</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2381,7 +2376,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2391,7 +2386,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,19 +2401,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129539028</v>
+        <v>129543182</v>
       </c>
       <c r="B18" t="n">
         <v>8450</v>
@@ -2447,16 +2442,21 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440970</v>
+        <v>440934</v>
       </c>
       <c r="R18" t="n">
-        <v>6754114</v>
+        <v>6754244</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2513,62 +2513,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129539529</v>
+        <v>129538675</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440725</v>
+        <v>440902</v>
       </c>
       <c r="R19" t="n">
-        <v>6754011</v>
+        <v>6754135</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2600,7 +2595,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2610,7 +2605,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2637,10 +2632,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129538905</v>
+        <v>129543219</v>
       </c>
       <c r="B20" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2648,39 +2643,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440970</v>
+        <v>440890</v>
       </c>
       <c r="R20" t="n">
-        <v>6754114</v>
+        <v>6754082</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2712,7 +2702,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2722,7 +2712,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2737,50 +2727,50 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129543195</v>
+        <v>129538905</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2789,10 +2779,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440708</v>
+        <v>440970</v>
       </c>
       <c r="R21" t="n">
-        <v>6754371</v>
+        <v>6754114</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2824,7 +2814,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2834,7 +2824,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2849,57 +2839,62 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129543219</v>
+        <v>129543195</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440890</v>
+        <v>440708</v>
       </c>
       <c r="R22" t="n">
-        <v>6754082</v>
+        <v>6754371</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2931,7 +2926,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2941,7 +2936,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2968,45 +2963,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129538675</v>
+        <v>129539529</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440902</v>
+        <v>440725</v>
       </c>
       <c r="R23" t="n">
-        <v>6754135</v>
+        <v>6754011</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3075,10 +3075,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129539521</v>
+        <v>129538680</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3086,34 +3086,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440725</v>
+        <v>440918</v>
       </c>
       <c r="R24" t="n">
-        <v>6754011</v>
+        <v>6754126</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3145,7 +3150,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3155,7 +3160,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3289,7 +3294,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129543228</v>
+        <v>129539521</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3324,10 +3329,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440716</v>
+        <v>440725</v>
       </c>
       <c r="R26" t="n">
-        <v>6754354</v>
+        <v>6754011</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3359,7 +3364,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3369,7 +3374,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3384,19 +3389,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543229</v>
+        <v>129543228</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3431,10 +3436,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440638</v>
+        <v>440716</v>
       </c>
       <c r="R27" t="n">
-        <v>6754239</v>
+        <v>6754354</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3466,7 +3471,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3476,7 +3481,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3503,10 +3508,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129538680</v>
+        <v>129543229</v>
       </c>
       <c r="B28" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3514,39 +3519,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440918</v>
+        <v>440638</v>
       </c>
       <c r="R28" t="n">
-        <v>6754126</v>
+        <v>6754239</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3603,62 +3603,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543188</v>
+        <v>129543222</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440824</v>
+        <v>440728</v>
       </c>
       <c r="R29" t="n">
-        <v>6754063</v>
+        <v>6754306</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3690,7 +3685,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3700,7 +3695,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3727,50 +3722,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129543201</v>
+        <v>129543233</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440885</v>
+        <v>440819</v>
       </c>
       <c r="R30" t="n">
-        <v>6754148</v>
+        <v>6754114</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3802,7 +3792,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3812,7 +3802,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3839,45 +3829,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129543222</v>
+        <v>129543188</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440728</v>
+        <v>440824</v>
       </c>
       <c r="R31" t="n">
-        <v>6754306</v>
+        <v>6754063</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3909,7 +3904,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3919,7 +3914,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3946,7 +3941,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129543187</v>
+        <v>129543201</v>
       </c>
       <c r="B32" t="n">
         <v>8450</v>
@@ -3986,10 +3981,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440887</v>
+        <v>440885</v>
       </c>
       <c r="R32" t="n">
-        <v>6754181</v>
+        <v>6754148</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4021,7 +4016,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4031,7 +4026,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4058,45 +4053,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129543233</v>
+        <v>129543187</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440819</v>
+        <v>440887</v>
       </c>
       <c r="R33" t="n">
-        <v>6754114</v>
+        <v>6754181</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4389,10 +4389,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129539754</v>
+        <v>129543235</v>
       </c>
       <c r="B36" t="n">
-        <v>91571</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4400,38 +4400,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440820</v>
+        <v>440863</v>
       </c>
       <c r="R36" t="n">
-        <v>6754096</v>
+        <v>6754131</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4463,7 +4459,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4473,7 +4469,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4488,12 +4484,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4719,45 +4715,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129543235</v>
+        <v>129543190</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440863</v>
+        <v>440773</v>
       </c>
       <c r="R39" t="n">
-        <v>6754131</v>
+        <v>6754088</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4789,7 +4790,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4799,7 +4800,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4826,38 +4827,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543190</v>
+        <v>129539754</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>91574</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4866,10 +4866,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440773</v>
+        <v>440820</v>
       </c>
       <c r="R40" t="n">
-        <v>6754088</v>
+        <v>6754096</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4926,12 +4926,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4941,7 +4941,7 @@
         <v>129543159</v>
       </c>
       <c r="B41" t="n">
-        <v>91571</v>
+        <v>91574</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5045,45 +5045,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129543145</v>
+        <v>129539589</v>
       </c>
       <c r="B42" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440723</v>
+        <v>440769</v>
       </c>
       <c r="R42" t="n">
-        <v>6754344</v>
+        <v>6754064</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5115,7 +5120,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5125,7 +5130,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5140,12 +5145,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5264,50 +5269,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129539589</v>
+        <v>129543145</v>
       </c>
       <c r="B44" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440769</v>
+        <v>440723</v>
       </c>
       <c r="R44" t="n">
-        <v>6754064</v>
+        <v>6754344</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5364,62 +5364,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129539814</v>
+        <v>129543226</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440861</v>
+        <v>440757</v>
       </c>
       <c r="R45" t="n">
-        <v>6754168</v>
+        <v>6754337</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5451,7 +5446,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5461,7 +5456,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5476,19 +5471,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129538170</v>
+        <v>129543194</v>
       </c>
       <c r="B46" t="n">
         <v>8450</v>
@@ -5519,7 +5514,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5528,10 +5523,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440982</v>
+        <v>440745</v>
       </c>
       <c r="R46" t="n">
-        <v>6754123</v>
+        <v>6754333</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5563,7 +5558,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5573,7 +5568,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5588,57 +5583,62 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129543226</v>
+        <v>129539814</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440757</v>
+        <v>440861</v>
       </c>
       <c r="R47" t="n">
-        <v>6754337</v>
+        <v>6754168</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5695,19 +5695,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129543194</v>
+        <v>129538170</v>
       </c>
       <c r="B48" t="n">
         <v>8450</v>
@@ -5738,7 +5738,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440745</v>
+        <v>440982</v>
       </c>
       <c r="R48" t="n">
-        <v>6754333</v>
+        <v>6754123</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5807,22 +5807,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129543220</v>
+        <v>129539404</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5830,34 +5830,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440851</v>
+        <v>440775</v>
       </c>
       <c r="R49" t="n">
-        <v>6754062</v>
+        <v>6753988</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5889,7 +5894,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5899,7 +5904,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5914,50 +5919,50 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129543198</v>
+        <v>129543166</v>
       </c>
       <c r="B50" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5966,10 +5971,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440824</v>
+        <v>440772</v>
       </c>
       <c r="R50" t="n">
-        <v>6754177</v>
+        <v>6754089</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6001,7 +6006,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6011,7 +6016,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6038,7 +6043,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129543236</v>
+        <v>129543220</v>
       </c>
       <c r="B51" t="n">
         <v>79044</v>
@@ -6073,10 +6078,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440970</v>
+        <v>440851</v>
       </c>
       <c r="R51" t="n">
-        <v>6754114</v>
+        <v>6754062</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6108,7 +6113,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6118,7 +6123,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6145,10 +6150,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129543166</v>
+        <v>129543236</v>
       </c>
       <c r="B52" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6156,39 +6161,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440772</v>
+        <v>440970</v>
       </c>
       <c r="R52" t="n">
-        <v>6754089</v>
+        <v>6754114</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6257,38 +6257,38 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129539404</v>
+        <v>129543198</v>
       </c>
       <c r="B53" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6297,10 +6297,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440775</v>
+        <v>440824</v>
       </c>
       <c r="R53" t="n">
-        <v>6753988</v>
+        <v>6754177</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6357,12 +6357,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6481,45 +6481,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129543230</v>
+        <v>129538256</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440779</v>
+        <v>440944</v>
       </c>
       <c r="R55" t="n">
-        <v>6754063</v>
+        <v>6754122</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6551,7 +6556,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6561,7 +6566,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6576,12 +6581,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6695,50 +6700,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129538256</v>
+        <v>129543230</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440944</v>
+        <v>440779</v>
       </c>
       <c r="R57" t="n">
-        <v>6754122</v>
+        <v>6754063</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6795,62 +6795,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129543181</v>
+        <v>129543213</v>
       </c>
       <c r="B58" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440990</v>
+        <v>440996</v>
       </c>
       <c r="R58" t="n">
-        <v>6754140</v>
+        <v>6754160</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6882,7 +6877,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6892,7 +6887,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6922,7 +6917,7 @@
         <v>129543144</v>
       </c>
       <c r="B59" t="n">
-        <v>91473</v>
+        <v>91476</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7026,7 +7021,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129543197</v>
+        <v>129543181</v>
       </c>
       <c r="B60" t="n">
         <v>8450</v>
@@ -7066,10 +7061,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440785</v>
+        <v>440990</v>
       </c>
       <c r="R60" t="n">
-        <v>6754107</v>
+        <v>6754140</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7101,7 +7096,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7111,7 +7106,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7138,7 +7133,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129543213</v>
+        <v>129538786</v>
       </c>
       <c r="B61" t="n">
         <v>79044</v>
@@ -7173,10 +7168,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>440996</v>
+        <v>440918</v>
       </c>
       <c r="R61" t="n">
-        <v>6754160</v>
+        <v>6754126</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7233,57 +7228,62 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129538786</v>
+        <v>129543197</v>
       </c>
       <c r="B62" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>440918</v>
+        <v>440785</v>
       </c>
       <c r="R62" t="n">
-        <v>6754126</v>
+        <v>6754107</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7315,7 +7315,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7340,22 +7340,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129543245</v>
+        <v>129543157</v>
       </c>
       <c r="B63" t="n">
-        <v>78710</v>
+        <v>57887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7363,34 +7363,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440986</v>
+        <v>440759</v>
       </c>
       <c r="R63" t="n">
-        <v>6754157</v>
+        <v>6754342</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7422,7 +7427,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7432,7 +7437,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7441,7 +7446,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7460,38 +7464,38 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129543157</v>
+        <v>129543179</v>
       </c>
       <c r="B64" t="n">
-        <v>57887</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7500,10 +7504,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440759</v>
+        <v>440821</v>
       </c>
       <c r="R64" t="n">
-        <v>6754342</v>
+        <v>6754050</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7535,7 +7539,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7545,7 +7549,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7572,7 +7576,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129543179</v>
+        <v>129543176</v>
       </c>
       <c r="B65" t="n">
         <v>8450</v>
@@ -7603,7 +7607,7 @@
       <c r="I65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7612,10 +7616,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440821</v>
+        <v>440820</v>
       </c>
       <c r="R65" t="n">
-        <v>6754050</v>
+        <v>6754121</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7647,7 +7651,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7657,7 +7661,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7684,7 +7688,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129543176</v>
+        <v>129543192</v>
       </c>
       <c r="B66" t="n">
         <v>8450</v>
@@ -7715,7 +7719,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7724,10 +7728,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440820</v>
+        <v>440742</v>
       </c>
       <c r="R66" t="n">
-        <v>6754121</v>
+        <v>6754310</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7759,7 +7763,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7769,7 +7773,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7796,50 +7800,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129543192</v>
+        <v>129543245</v>
       </c>
       <c r="B67" t="n">
-        <v>8450</v>
+        <v>78710</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>440742</v>
+        <v>440986</v>
       </c>
       <c r="R67" t="n">
-        <v>6754310</v>
+        <v>6754157</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7871,7 +7870,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7881,7 +7880,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7890,6 +7889,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8015,10 +8015,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129538247</v>
+        <v>129543246</v>
       </c>
       <c r="B69" t="n">
-        <v>57724</v>
+        <v>78710</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8026,39 +8026,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440944</v>
+        <v>440893</v>
       </c>
       <c r="R69" t="n">
-        <v>6754122</v>
+        <v>6754230</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8090,7 +8085,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8100,7 +8095,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8109,25 +8104,26 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129538126</v>
+        <v>129543225</v>
       </c>
       <c r="B70" t="n">
         <v>79044</v>
@@ -8162,10 +8158,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>441002</v>
+        <v>440764</v>
       </c>
       <c r="R70" t="n">
-        <v>6754112</v>
+        <v>6754320</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8197,7 +8193,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8207,7 +8203,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8222,22 +8218,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129543141</v>
+        <v>129543218</v>
       </c>
       <c r="B71" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8245,21 +8241,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8269,10 +8265,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>440974</v>
+        <v>440888</v>
       </c>
       <c r="R71" t="n">
-        <v>6754141</v>
+        <v>6754157</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8304,7 +8300,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8314,7 +8310,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8341,50 +8337,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129543178</v>
+        <v>129538126</v>
       </c>
       <c r="B72" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>440816</v>
+        <v>441002</v>
       </c>
       <c r="R72" t="n">
-        <v>6754178</v>
+        <v>6754112</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8416,7 +8407,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8426,7 +8417,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8441,22 +8432,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129543143</v>
+        <v>129543224</v>
       </c>
       <c r="B73" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8464,21 +8455,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8488,10 +8479,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>440893</v>
+        <v>440774</v>
       </c>
       <c r="R73" t="n">
-        <v>6754230</v>
+        <v>6754313</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8523,7 +8514,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8533,7 +8524,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8560,10 +8551,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129543225</v>
+        <v>129538247</v>
       </c>
       <c r="B74" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8571,34 +8562,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>440764</v>
+        <v>440944</v>
       </c>
       <c r="R74" t="n">
-        <v>6754320</v>
+        <v>6754122</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8630,7 +8626,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8640,7 +8636,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8655,22 +8651,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129543218</v>
+        <v>129543141</v>
       </c>
       <c r="B75" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8678,21 +8674,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8702,10 +8698,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>440888</v>
+        <v>440974</v>
       </c>
       <c r="R75" t="n">
-        <v>6754157</v>
+        <v>6754141</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8737,7 +8733,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8747,7 +8743,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8774,10 +8770,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129543246</v>
+        <v>129543143</v>
       </c>
       <c r="B76" t="n">
-        <v>78710</v>
+        <v>79663</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8785,21 +8781,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8863,7 +8859,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8882,7 +8877,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129543199</v>
+        <v>129543178</v>
       </c>
       <c r="B77" t="n">
         <v>8450</v>
@@ -8913,7 +8908,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -8922,10 +8917,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>440855</v>
+        <v>440816</v>
       </c>
       <c r="R77" t="n">
-        <v>6754166</v>
+        <v>6754178</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8957,7 +8952,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8967,7 +8962,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8994,45 +8989,50 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129543224</v>
+        <v>129543199</v>
       </c>
       <c r="B78" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>440774</v>
+        <v>440855</v>
       </c>
       <c r="R78" t="n">
-        <v>6754313</v>
+        <v>6754166</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9101,32 +9101,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129543215</v>
+        <v>129543164</v>
       </c>
       <c r="B79" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9136,10 +9136,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>440930</v>
+        <v>440708</v>
       </c>
       <c r="R79" t="n">
-        <v>6754182</v>
+        <v>6754116</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9171,7 +9171,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9181,7 +9181,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9320,45 +9325,50 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129543221</v>
+        <v>129538573</v>
       </c>
       <c r="B81" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>440739</v>
+        <v>440932</v>
       </c>
       <c r="R81" t="n">
-        <v>6754147</v>
+        <v>6754178</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9390,7 +9400,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9400,7 +9410,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9415,22 +9425,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129543164</v>
+        <v>129543202</v>
       </c>
       <c r="B82" t="n">
-        <v>80178</v>
+        <v>8450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9438,34 +9448,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>440708</v>
+        <v>440918</v>
       </c>
       <c r="R82" t="n">
-        <v>6754116</v>
+        <v>6754161</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9497,7 +9512,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9507,12 +9522,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9539,45 +9549,50 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129543154</v>
+        <v>129543173</v>
       </c>
       <c r="B83" t="n">
-        <v>90582</v>
+        <v>8450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>440770</v>
+        <v>440917</v>
       </c>
       <c r="R83" t="n">
-        <v>6754101</v>
+        <v>6754255</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9609,7 +9624,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9619,7 +9634,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9646,7 +9661,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129543202</v>
+        <v>129543203</v>
       </c>
       <c r="B84" t="n">
         <v>8450</v>
@@ -9686,10 +9701,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>440918</v>
+        <v>440946</v>
       </c>
       <c r="R84" t="n">
-        <v>6754161</v>
+        <v>6754123</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9721,7 +9736,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9731,7 +9746,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9758,50 +9773,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129543173</v>
+        <v>129543154</v>
       </c>
       <c r="B85" t="n">
-        <v>8450</v>
+        <v>90585</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>1962</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>440917</v>
+        <v>440770</v>
       </c>
       <c r="R85" t="n">
-        <v>6754255</v>
+        <v>6754101</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9833,7 +9843,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9843,7 +9853,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9870,50 +9880,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129543203</v>
+        <v>129543215</v>
       </c>
       <c r="B86" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>440946</v>
+        <v>440930</v>
       </c>
       <c r="R86" t="n">
-        <v>6754123</v>
+        <v>6754182</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9945,7 +9950,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9955,7 +9960,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9982,50 +9987,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129538573</v>
+        <v>129543221</v>
       </c>
       <c r="B87" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>440932</v>
+        <v>440739</v>
       </c>
       <c r="R87" t="n">
-        <v>6754178</v>
+        <v>6754147</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10082,22 +10082,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129543171</v>
+        <v>129538100</v>
       </c>
       <c r="B88" t="n">
-        <v>91603</v>
+        <v>79663</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10105,21 +10105,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10129,10 +10129,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>440996</v>
+        <v>441007</v>
       </c>
       <c r="R88" t="n">
-        <v>6754160</v>
+        <v>6754124</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10189,19 +10189,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129543223</v>
+        <v>129538198</v>
       </c>
       <c r="B89" t="n">
         <v>79044</v>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>440754</v>
+        <v>440969</v>
       </c>
       <c r="R89" t="n">
-        <v>6754304</v>
+        <v>6754129</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10271,7 +10271,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10296,19 +10296,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129538198</v>
+        <v>129543223</v>
       </c>
       <c r="B90" t="n">
         <v>79044</v>
@@ -10343,10 +10343,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>440969</v>
+        <v>440754</v>
       </c>
       <c r="R90" t="n">
-        <v>6754129</v>
+        <v>6754304</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10378,7 +10378,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10403,22 +10403,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129538100</v>
+        <v>129543171</v>
       </c>
       <c r="B91" t="n">
-        <v>79663</v>
+        <v>91606</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10426,21 +10426,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10450,10 +10450,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>441007</v>
+        <v>440996</v>
       </c>
       <c r="R91" t="n">
-        <v>6754124</v>
+        <v>6754160</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10510,12 +10510,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10629,50 +10629,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129543175</v>
+        <v>129543153</v>
       </c>
       <c r="B93" t="n">
-        <v>8450</v>
+        <v>90585</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>1962</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>440896</v>
+        <v>440976</v>
       </c>
       <c r="R93" t="n">
-        <v>6754124</v>
+        <v>6754143</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10704,7 +10699,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10714,7 +10709,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10741,45 +10736,50 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129543153</v>
+        <v>129543175</v>
       </c>
       <c r="B94" t="n">
-        <v>90582</v>
+        <v>8450</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>440976</v>
+        <v>440896</v>
       </c>
       <c r="R94" t="n">
-        <v>6754143</v>
+        <v>6754124</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11169,10 +11169,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129543170</v>
+        <v>129543152</v>
       </c>
       <c r="B98" t="n">
-        <v>57727</v>
+        <v>90585</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11180,39 +11180,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>440677</v>
+        <v>440718</v>
       </c>
       <c r="R98" t="n">
-        <v>6754247</v>
+        <v>6754157</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11244,7 +11239,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11254,12 +11249,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11398,45 +11388,50 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129543152</v>
+        <v>129538483</v>
       </c>
       <c r="B100" t="n">
-        <v>90582</v>
+        <v>8450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>440718</v>
+        <v>440916</v>
       </c>
       <c r="R100" t="n">
-        <v>6754157</v>
+        <v>6754159</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11468,7 +11463,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11478,7 +11473,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11493,12 +11488,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11617,7 +11612,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129538483</v>
+        <v>129538851</v>
       </c>
       <c r="B102" t="n">
         <v>8450</v>
@@ -11657,10 +11652,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>440916</v>
+        <v>440918</v>
       </c>
       <c r="R102" t="n">
-        <v>6754159</v>
+        <v>6754126</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11729,38 +11724,38 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129538851</v>
+        <v>129543170</v>
       </c>
       <c r="B103" t="n">
-        <v>8450</v>
+        <v>57727</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11769,10 +11764,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>440918</v>
+        <v>440677</v>
       </c>
       <c r="R103" t="n">
-        <v>6754126</v>
+        <v>6754247</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11804,7 +11799,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11814,7 +11809,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11829,12 +11829,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -11948,10 +11948,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129543247</v>
+        <v>129538088</v>
       </c>
       <c r="B105" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11959,21 +11959,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11983,10 +11983,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>440894</v>
+        <v>441007</v>
       </c>
       <c r="R105" t="n">
-        <v>6754104</v>
+        <v>6754124</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12028,7 +12028,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12037,19 +12037,18 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -12168,10 +12167,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129538088</v>
+        <v>129543247</v>
       </c>
       <c r="B107" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12179,21 +12178,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12203,10 +12202,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>441007</v>
+        <v>440894</v>
       </c>
       <c r="R107" t="n">
-        <v>6754124</v>
+        <v>6754104</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12238,7 +12237,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12248,7 +12247,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12257,18 +12256,19 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>

--- a/artfynd/A 45199-2025 artfynd.xlsx
+++ b/artfynd/A 45199-2025 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129539829</v>
+        <v>129539413</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440861</v>
+        <v>440775</v>
       </c>
       <c r="R2" t="n">
-        <v>6754168</v>
+        <v>6753988</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,50 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129539413</v>
+        <v>129539829</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440775</v>
+        <v>440861</v>
       </c>
       <c r="R3" t="n">
-        <v>6753988</v>
+        <v>6754168</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129543238</v>
+        <v>129543168</v>
       </c>
       <c r="B5" t="n">
-        <v>91826</v>
+        <v>92839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,21 +1013,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>4365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440966</v>
+        <v>440718</v>
       </c>
       <c r="R5" t="n">
-        <v>6754151</v>
+        <v>6754157</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,32 +1109,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129543239</v>
+        <v>129543158</v>
       </c>
       <c r="B6" t="n">
-        <v>80084</v>
+        <v>91574</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6457</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440708</v>
+        <v>440892</v>
       </c>
       <c r="R6" t="n">
-        <v>6754116</v>
+        <v>6754225</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1189,12 +1189,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,32 +1216,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129543147</v>
+        <v>129543238</v>
       </c>
       <c r="B7" t="n">
-        <v>79663</v>
+        <v>91826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1256,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440701</v>
+        <v>440966</v>
       </c>
       <c r="R7" t="n">
-        <v>6754185</v>
+        <v>6754151</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,7 +1286,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1301,7 +1296,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1328,32 +1323,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129539852</v>
+        <v>129543239</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>80084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1363,10 +1358,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440880</v>
+        <v>440708</v>
       </c>
       <c r="R8" t="n">
-        <v>6754175</v>
+        <v>6754116</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,7 +1393,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1408,7 +1403,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,22 +1423,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129539462</v>
+        <v>129543147</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1446,21 +1446,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440787</v>
+        <v>440701</v>
       </c>
       <c r="R9" t="n">
-        <v>6753947</v>
+        <v>6754185</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1530,44 +1530,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129543168</v>
+        <v>129539852</v>
       </c>
       <c r="B10" t="n">
-        <v>92839</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440718</v>
+        <v>440880</v>
       </c>
       <c r="R10" t="n">
-        <v>6754157</v>
+        <v>6754175</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1637,62 +1637,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543183</v>
+        <v>129539462</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440945</v>
+        <v>440787</v>
       </c>
       <c r="R11" t="n">
-        <v>6754252</v>
+        <v>6753947</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1719,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1734,7 +1729,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1749,19 +1744,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129543191</v>
+        <v>129543183</v>
       </c>
       <c r="B12" t="n">
         <v>8450</v>
@@ -1801,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440733</v>
+        <v>440945</v>
       </c>
       <c r="R12" t="n">
-        <v>6754283</v>
+        <v>6754252</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,7 +1831,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1846,7 +1841,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1873,7 +1868,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129539316</v>
+        <v>129543191</v>
       </c>
       <c r="B13" t="n">
         <v>8450</v>
@@ -1904,7 +1899,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1913,10 +1908,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440779</v>
+        <v>440733</v>
       </c>
       <c r="R13" t="n">
-        <v>6754008</v>
+        <v>6754283</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,7 +1943,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1958,7 +1953,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1973,57 +1968,62 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129543158</v>
+        <v>129539316</v>
       </c>
       <c r="B14" t="n">
-        <v>91574</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440892</v>
+        <v>440779</v>
       </c>
       <c r="R14" t="n">
-        <v>6754225</v>
+        <v>6754008</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2080,44 +2080,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129543216</v>
+        <v>129539028</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440945</v>
+        <v>440970</v>
       </c>
       <c r="R15" t="n">
-        <v>6754252</v>
+        <v>6754114</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,57 +2187,62 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129543227</v>
+        <v>129543182</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440744</v>
+        <v>440934</v>
       </c>
       <c r="R16" t="n">
-        <v>6754336</v>
+        <v>6754244</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2269,7 +2274,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2279,7 +2284,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2306,32 +2311,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129539028</v>
+        <v>129543216</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2341,10 +2346,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440970</v>
+        <v>440945</v>
       </c>
       <c r="R17" t="n">
-        <v>6754114</v>
+        <v>6754252</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2376,7 +2381,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2386,7 +2391,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2401,62 +2406,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543182</v>
+        <v>129543227</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440934</v>
+        <v>440744</v>
       </c>
       <c r="R18" t="n">
-        <v>6754244</v>
+        <v>6754336</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2525,10 +2525,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129538675</v>
+        <v>129538905</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2536,34 +2536,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440902</v>
+        <v>440970</v>
       </c>
       <c r="R19" t="n">
-        <v>6754135</v>
+        <v>6754114</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2739,10 +2744,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129538905</v>
+        <v>129538675</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2750,39 +2755,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440970</v>
+        <v>440902</v>
       </c>
       <c r="R21" t="n">
-        <v>6754114</v>
+        <v>6754135</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -4389,10 +4389,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129543235</v>
+        <v>129539754</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>91574</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4400,34 +4400,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440863</v>
+        <v>440820</v>
       </c>
       <c r="R36" t="n">
-        <v>6754131</v>
+        <v>6754096</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4459,7 +4463,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4469,7 +4473,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4484,22 +4488,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129539703</v>
+        <v>129543159</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>91574</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4507,21 +4511,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4531,10 +4535,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440820</v>
+        <v>440738</v>
       </c>
       <c r="R37" t="n">
-        <v>6754096</v>
+        <v>6754021</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4566,7 +4570,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4576,7 +4580,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4591,22 +4595,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129539312</v>
+        <v>129539703</v>
       </c>
       <c r="B38" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4614,39 +4618,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440779</v>
+        <v>440820</v>
       </c>
       <c r="R38" t="n">
-        <v>6754008</v>
+        <v>6754096</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4715,38 +4714,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129543190</v>
+        <v>129539312</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4755,10 +4754,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440773</v>
+        <v>440779</v>
       </c>
       <c r="R39" t="n">
-        <v>6754088</v>
+        <v>6754008</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4790,7 +4789,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4800,7 +4799,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4815,22 +4814,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129539754</v>
+        <v>129543235</v>
       </c>
       <c r="B40" t="n">
-        <v>91574</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4838,38 +4837,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440820</v>
+        <v>440863</v>
       </c>
       <c r="R40" t="n">
-        <v>6754096</v>
+        <v>6754131</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4901,7 +4896,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4911,7 +4906,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4926,57 +4921,62 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129543159</v>
+        <v>129543190</v>
       </c>
       <c r="B41" t="n">
-        <v>91574</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440738</v>
+        <v>440773</v>
       </c>
       <c r="R41" t="n">
-        <v>6754021</v>
+        <v>6754088</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5045,50 +5045,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129539589</v>
+        <v>129543145</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440769</v>
+        <v>440723</v>
       </c>
       <c r="R42" t="n">
-        <v>6754064</v>
+        <v>6754344</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5120,7 +5115,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5130,7 +5125,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5145,19 +5140,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129538433</v>
+        <v>129539589</v>
       </c>
       <c r="B43" t="n">
         <v>8450</v>
@@ -5197,10 +5192,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440937</v>
+        <v>440769</v>
       </c>
       <c r="R43" t="n">
-        <v>6754141</v>
+        <v>6754064</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5232,7 +5227,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5242,7 +5237,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5269,45 +5264,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129543145</v>
+        <v>129538433</v>
       </c>
       <c r="B44" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440723</v>
+        <v>440937</v>
       </c>
       <c r="R44" t="n">
-        <v>6754344</v>
+        <v>6754141</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5364,57 +5364,62 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129543226</v>
+        <v>129543194</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440757</v>
+        <v>440745</v>
       </c>
       <c r="R45" t="n">
-        <v>6754337</v>
+        <v>6754333</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5446,7 +5451,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5456,7 +5461,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5483,7 +5488,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129543194</v>
+        <v>129539814</v>
       </c>
       <c r="B46" t="n">
         <v>8450</v>
@@ -5523,10 +5528,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440745</v>
+        <v>440861</v>
       </c>
       <c r="R46" t="n">
-        <v>6754333</v>
+        <v>6754168</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5558,7 +5563,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5568,7 +5573,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5583,19 +5588,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129539814</v>
+        <v>129538170</v>
       </c>
       <c r="B47" t="n">
         <v>8450</v>
@@ -5626,7 +5631,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5635,10 +5640,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440861</v>
+        <v>440982</v>
       </c>
       <c r="R47" t="n">
-        <v>6754168</v>
+        <v>6754123</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5670,7 +5675,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5680,7 +5685,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5707,50 +5712,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129538170</v>
+        <v>129543226</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440982</v>
+        <v>440757</v>
       </c>
       <c r="R48" t="n">
-        <v>6754123</v>
+        <v>6754337</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5807,12 +5807,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6369,50 +6369,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129543185</v>
+        <v>129543230</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440888</v>
+        <v>440779</v>
       </c>
       <c r="R54" t="n">
-        <v>6754217</v>
+        <v>6754063</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6444,7 +6439,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6454,7 +6449,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6481,50 +6476,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129538256</v>
+        <v>129538554</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440944</v>
+        <v>440919</v>
       </c>
       <c r="R55" t="n">
-        <v>6754122</v>
+        <v>6754174</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6593,45 +6583,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129538554</v>
+        <v>129543185</v>
       </c>
       <c r="B56" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440919</v>
+        <v>440888</v>
       </c>
       <c r="R56" t="n">
-        <v>6754174</v>
+        <v>6754217</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6663,7 +6658,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6673,7 +6668,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6688,57 +6683,62 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129543230</v>
+        <v>129538256</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440779</v>
+        <v>440944</v>
       </c>
       <c r="R57" t="n">
-        <v>6754063</v>
+        <v>6754122</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6795,57 +6795,62 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129543213</v>
+        <v>129543181</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440996</v>
+        <v>440990</v>
       </c>
       <c r="R58" t="n">
-        <v>6754160</v>
+        <v>6754140</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6877,7 +6882,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6887,7 +6892,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6914,45 +6919,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129543144</v>
+        <v>129543197</v>
       </c>
       <c r="B59" t="n">
-        <v>91476</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3242</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440718</v>
+        <v>440785</v>
       </c>
       <c r="R59" t="n">
-        <v>6754215</v>
+        <v>6754107</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6984,7 +6994,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6994,7 +7004,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7021,50 +7031,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129543181</v>
+        <v>129543144</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>91476</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>3242</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440990</v>
+        <v>440718</v>
       </c>
       <c r="R60" t="n">
-        <v>6754140</v>
+        <v>6754215</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7096,7 +7101,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7106,7 +7111,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7240,50 +7245,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129543197</v>
+        <v>129543213</v>
       </c>
       <c r="B62" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>440785</v>
+        <v>440996</v>
       </c>
       <c r="R62" t="n">
-        <v>6754107</v>
+        <v>6754160</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7315,7 +7315,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7352,10 +7352,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129543157</v>
+        <v>129543245</v>
       </c>
       <c r="B63" t="n">
-        <v>57887</v>
+        <v>78710</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7363,39 +7363,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440759</v>
+        <v>440986</v>
       </c>
       <c r="R63" t="n">
-        <v>6754342</v>
+        <v>6754157</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7427,7 +7422,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7437,7 +7432,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7446,6 +7441,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7464,50 +7460,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129543179</v>
+        <v>129539371</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440821</v>
+        <v>440769</v>
       </c>
       <c r="R64" t="n">
-        <v>6754050</v>
+        <v>6754008</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7539,7 +7530,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7549,7 +7540,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7564,50 +7555,50 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129543176</v>
+        <v>129543157</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>57887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7616,10 +7607,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440820</v>
+        <v>440759</v>
       </c>
       <c r="R65" t="n">
-        <v>6754121</v>
+        <v>6754342</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7651,7 +7642,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7661,7 +7652,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7688,7 +7679,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129543192</v>
+        <v>129543179</v>
       </c>
       <c r="B66" t="n">
         <v>8450</v>
@@ -7728,10 +7719,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440742</v>
+        <v>440821</v>
       </c>
       <c r="R66" t="n">
-        <v>6754310</v>
+        <v>6754050</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7763,7 +7754,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7773,7 +7764,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7800,45 +7791,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129543245</v>
+        <v>129543176</v>
       </c>
       <c r="B67" t="n">
-        <v>78710</v>
+        <v>8450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>440986</v>
+        <v>440820</v>
       </c>
       <c r="R67" t="n">
-        <v>6754157</v>
+        <v>6754121</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7870,7 +7866,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7880,7 +7876,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7889,7 +7885,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7908,45 +7903,50 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129539371</v>
+        <v>129543192</v>
       </c>
       <c r="B68" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440769</v>
+        <v>440742</v>
       </c>
       <c r="R68" t="n">
-        <v>6754008</v>
+        <v>6754310</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8003,57 +8003,62 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129543246</v>
+        <v>129543178</v>
       </c>
       <c r="B69" t="n">
-        <v>78710</v>
+        <v>8450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440893</v>
+        <v>440816</v>
       </c>
       <c r="R69" t="n">
-        <v>6754230</v>
+        <v>6754178</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8085,7 +8090,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8095,7 +8100,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8104,7 +8109,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8123,45 +8127,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129543225</v>
+        <v>129543199</v>
       </c>
       <c r="B70" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440764</v>
+        <v>440855</v>
       </c>
       <c r="R70" t="n">
-        <v>6754320</v>
+        <v>6754166</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8193,7 +8202,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8203,7 +8212,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8230,10 +8239,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129543218</v>
+        <v>129543246</v>
       </c>
       <c r="B71" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8241,21 +8250,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8265,10 +8274,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>440888</v>
+        <v>440893</v>
       </c>
       <c r="R71" t="n">
-        <v>6754157</v>
+        <v>6754230</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8300,7 +8309,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8310,7 +8319,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8319,6 +8328,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8337,10 +8347,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129538126</v>
+        <v>129538247</v>
       </c>
       <c r="B72" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8348,34 +8358,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>441002</v>
+        <v>440944</v>
       </c>
       <c r="R72" t="n">
-        <v>6754112</v>
+        <v>6754122</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8444,10 +8459,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129543224</v>
+        <v>129543141</v>
       </c>
       <c r="B73" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8455,21 +8470,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8479,10 +8494,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>440774</v>
+        <v>440974</v>
       </c>
       <c r="R73" t="n">
-        <v>6754313</v>
+        <v>6754141</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8514,7 +8529,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8524,7 +8539,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8551,10 +8566,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129538247</v>
+        <v>129543225</v>
       </c>
       <c r="B74" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8562,39 +8577,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>440944</v>
+        <v>440764</v>
       </c>
       <c r="R74" t="n">
-        <v>6754122</v>
+        <v>6754320</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8626,7 +8636,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8636,7 +8646,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8651,22 +8661,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129543141</v>
+        <v>129543218</v>
       </c>
       <c r="B75" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8674,21 +8684,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8698,10 +8708,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>440974</v>
+        <v>440888</v>
       </c>
       <c r="R75" t="n">
-        <v>6754141</v>
+        <v>6754157</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8733,7 +8743,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8743,7 +8753,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8770,10 +8780,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129543143</v>
+        <v>129538126</v>
       </c>
       <c r="B76" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8781,21 +8791,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8805,10 +8815,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>440893</v>
+        <v>441002</v>
       </c>
       <c r="R76" t="n">
-        <v>6754230</v>
+        <v>6754112</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8840,7 +8850,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8850,7 +8860,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8865,62 +8875,57 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129543178</v>
+        <v>129543143</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>440816</v>
+        <v>440893</v>
       </c>
       <c r="R77" t="n">
-        <v>6754178</v>
+        <v>6754230</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8952,7 +8957,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8962,7 +8967,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8989,50 +8994,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129543199</v>
+        <v>129543224</v>
       </c>
       <c r="B78" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>440855</v>
+        <v>440774</v>
       </c>
       <c r="R78" t="n">
-        <v>6754166</v>
+        <v>6754313</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9101,32 +9101,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129543164</v>
+        <v>129543154</v>
       </c>
       <c r="B79" t="n">
-        <v>80178</v>
+        <v>90585</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>1962</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9136,10 +9136,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>440708</v>
+        <v>440770</v>
       </c>
       <c r="R79" t="n">
-        <v>6754116</v>
+        <v>6754101</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9171,7 +9171,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9181,12 +9181,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9213,10 +9208,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129543155</v>
+        <v>129543164</v>
       </c>
       <c r="B80" t="n">
-        <v>56917</v>
+        <v>80178</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9224,39 +9219,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>440878</v>
+        <v>440708</v>
       </c>
       <c r="R80" t="n">
-        <v>6754126</v>
+        <v>6754116</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9288,7 +9278,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9298,7 +9288,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9325,50 +9320,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129538573</v>
+        <v>129543215</v>
       </c>
       <c r="B81" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>440932</v>
+        <v>440930</v>
       </c>
       <c r="R81" t="n">
-        <v>6754178</v>
+        <v>6754182</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9400,7 +9390,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9410,7 +9400,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9425,62 +9415,57 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129543202</v>
+        <v>129543221</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>440918</v>
+        <v>440739</v>
       </c>
       <c r="R82" t="n">
-        <v>6754161</v>
+        <v>6754147</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9512,7 +9497,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9522,7 +9507,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9549,10 +9534,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129543173</v>
+        <v>129543155</v>
       </c>
       <c r="B83" t="n">
-        <v>8450</v>
+        <v>56917</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9560,27 +9545,27 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9589,10 +9574,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>440917</v>
+        <v>440878</v>
       </c>
       <c r="R83" t="n">
-        <v>6754255</v>
+        <v>6754126</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9624,7 +9609,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9634,7 +9619,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9661,7 +9646,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129543203</v>
+        <v>129538573</v>
       </c>
       <c r="B84" t="n">
         <v>8450</v>
@@ -9692,7 +9677,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9701,10 +9686,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>440946</v>
+        <v>440932</v>
       </c>
       <c r="R84" t="n">
-        <v>6754123</v>
+        <v>6754178</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9736,7 +9721,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9746,7 +9731,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9761,57 +9746,62 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129543154</v>
+        <v>129543202</v>
       </c>
       <c r="B85" t="n">
-        <v>90585</v>
+        <v>8450</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>440770</v>
+        <v>440918</v>
       </c>
       <c r="R85" t="n">
-        <v>6754101</v>
+        <v>6754161</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9843,7 +9833,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9853,7 +9843,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9880,45 +9870,50 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129543215</v>
+        <v>129543173</v>
       </c>
       <c r="B86" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>440930</v>
+        <v>440917</v>
       </c>
       <c r="R86" t="n">
-        <v>6754182</v>
+        <v>6754255</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9950,7 +9945,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9960,7 +9955,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9987,45 +9982,50 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129543221</v>
+        <v>129543203</v>
       </c>
       <c r="B87" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>440739</v>
+        <v>440946</v>
       </c>
       <c r="R87" t="n">
-        <v>6754147</v>
+        <v>6754123</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10094,10 +10094,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129538100</v>
+        <v>129543171</v>
       </c>
       <c r="B88" t="n">
-        <v>79663</v>
+        <v>91606</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10105,21 +10105,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10129,10 +10129,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>441007</v>
+        <v>440996</v>
       </c>
       <c r="R88" t="n">
-        <v>6754124</v>
+        <v>6754160</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10189,12 +10189,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -10415,10 +10415,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129543171</v>
+        <v>129538100</v>
       </c>
       <c r="B91" t="n">
-        <v>91606</v>
+        <v>79663</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10426,21 +10426,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10450,10 +10450,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>440996</v>
+        <v>441007</v>
       </c>
       <c r="R91" t="n">
-        <v>6754160</v>
+        <v>6754124</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10510,22 +10510,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129543142</v>
+        <v>129543153</v>
       </c>
       <c r="B92" t="n">
-        <v>79663</v>
+        <v>90585</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10533,21 +10533,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10557,10 +10557,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>440949</v>
+        <v>440976</v>
       </c>
       <c r="R92" t="n">
-        <v>6754170</v>
+        <v>6754143</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10602,7 +10602,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10629,10 +10629,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129543153</v>
+        <v>129543142</v>
       </c>
       <c r="B93" t="n">
-        <v>90585</v>
+        <v>79663</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10640,21 +10640,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10664,10 +10664,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>440976</v>
+        <v>440949</v>
       </c>
       <c r="R93" t="n">
-        <v>6754143</v>
+        <v>6754170</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10709,7 +10709,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11276,38 +11276,38 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129543174</v>
+        <v>129543170</v>
       </c>
       <c r="B99" t="n">
-        <v>8450</v>
+        <v>57727</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -11316,10 +11316,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>440876</v>
+        <v>440677</v>
       </c>
       <c r="R99" t="n">
-        <v>6754211</v>
+        <v>6754247</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11361,7 +11361,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11388,7 +11393,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129538483</v>
+        <v>129543174</v>
       </c>
       <c r="B100" t="n">
         <v>8450</v>
@@ -11428,10 +11433,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>440916</v>
+        <v>440876</v>
       </c>
       <c r="R100" t="n">
-        <v>6754159</v>
+        <v>6754211</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11463,7 +11468,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11473,7 +11478,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11488,19 +11493,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129543189</v>
+        <v>129538483</v>
       </c>
       <c r="B101" t="n">
         <v>8450</v>
@@ -11531,7 +11536,7 @@
       <c r="I101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -11540,10 +11545,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>440793</v>
+        <v>440916</v>
       </c>
       <c r="R101" t="n">
-        <v>6754070</v>
+        <v>6754159</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11575,7 +11580,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11585,7 +11590,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11600,19 +11605,19 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129538851</v>
+        <v>129543189</v>
       </c>
       <c r="B102" t="n">
         <v>8450</v>
@@ -11643,7 +11648,7 @@
       <c r="I102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -11652,10 +11657,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>440918</v>
+        <v>440793</v>
       </c>
       <c r="R102" t="n">
-        <v>6754126</v>
+        <v>6754070</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11687,7 +11692,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11697,7 +11702,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11712,50 +11717,50 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129543170</v>
+        <v>129538851</v>
       </c>
       <c r="B103" t="n">
-        <v>57727</v>
+        <v>8450</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11764,10 +11769,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>440677</v>
+        <v>440918</v>
       </c>
       <c r="R103" t="n">
-        <v>6754247</v>
+        <v>6754126</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11799,7 +11804,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11809,12 +11814,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11829,22 +11829,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129543217</v>
+        <v>129543247</v>
       </c>
       <c r="B104" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11852,21 +11852,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11876,10 +11876,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>440902</v>
+        <v>440894</v>
       </c>
       <c r="R104" t="n">
-        <v>6754164</v>
+        <v>6754104</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11911,7 +11911,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11921,7 +11921,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11930,6 +11930,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11948,10 +11949,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129538088</v>
+        <v>129538156</v>
       </c>
       <c r="B105" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11959,34 +11960,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>441007</v>
+        <v>440982</v>
       </c>
       <c r="R105" t="n">
-        <v>6754124</v>
+        <v>6754123</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12055,10 +12061,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129538156</v>
+        <v>129543217</v>
       </c>
       <c r="B106" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12066,39 +12072,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>440982</v>
+        <v>440902</v>
       </c>
       <c r="R106" t="n">
-        <v>6754123</v>
+        <v>6754164</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12130,7 +12131,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12140,7 +12141,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12155,22 +12156,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129543247</v>
+        <v>129538088</v>
       </c>
       <c r="B107" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12178,21 +12179,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12202,10 +12203,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>440894</v>
+        <v>441007</v>
       </c>
       <c r="R107" t="n">
-        <v>6754104</v>
+        <v>6754124</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12237,7 +12238,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12247,7 +12248,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12256,19 +12257,18 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>

--- a/artfynd/A 45199-2025 artfynd.xlsx
+++ b/artfynd/A 45199-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129539413</v>
+        <v>129539829</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440775</v>
+        <v>440861</v>
       </c>
       <c r="R2" t="n">
-        <v>6753988</v>
+        <v>6754168</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129539829</v>
+        <v>129539413</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440861</v>
+        <v>440775</v>
       </c>
       <c r="R3" t="n">
-        <v>6754168</v>
+        <v>6753988</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129543168</v>
+        <v>129543238</v>
       </c>
       <c r="B5" t="n">
-        <v>92839</v>
+        <v>91826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,21 +1013,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4365</v>
+        <v>65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440718</v>
+        <v>440966</v>
       </c>
       <c r="R5" t="n">
-        <v>6754157</v>
+        <v>6754151</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1216,32 +1216,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129543238</v>
+        <v>129539462</v>
       </c>
       <c r="B7" t="n">
-        <v>91826</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440966</v>
+        <v>440787</v>
       </c>
       <c r="R7" t="n">
-        <v>6754151</v>
+        <v>6753947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,44 +1311,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129543239</v>
+        <v>129539852</v>
       </c>
       <c r="B8" t="n">
-        <v>80084</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1358,10 +1358,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440708</v>
+        <v>440880</v>
       </c>
       <c r="R8" t="n">
-        <v>6754116</v>
+        <v>6754175</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1403,12 +1403,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,44 +1418,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129543147</v>
+        <v>129543239</v>
       </c>
       <c r="B9" t="n">
-        <v>79663</v>
+        <v>80084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6457</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1470,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440701</v>
+        <v>440708</v>
       </c>
       <c r="R9" t="n">
-        <v>6754185</v>
+        <v>6754116</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,7 +1500,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1515,7 +1510,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1542,10 +1542,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129539852</v>
+        <v>129543147</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,21 +1553,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440880</v>
+        <v>440701</v>
       </c>
       <c r="R10" t="n">
-        <v>6754175</v>
+        <v>6754185</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1637,44 +1637,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129539462</v>
+        <v>129543168</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>92839</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440787</v>
+        <v>440718</v>
       </c>
       <c r="R11" t="n">
-        <v>6753947</v>
+        <v>6754157</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1744,12 +1744,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2092,32 +2092,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129539028</v>
+        <v>129543227</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440970</v>
+        <v>440744</v>
       </c>
       <c r="R15" t="n">
-        <v>6754114</v>
+        <v>6754336</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,62 +2187,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129543182</v>
+        <v>129543216</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440934</v>
+        <v>440945</v>
       </c>
       <c r="R16" t="n">
-        <v>6754244</v>
+        <v>6754252</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2311,32 +2306,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129543216</v>
+        <v>129539028</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2346,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440945</v>
+        <v>440970</v>
       </c>
       <c r="R17" t="n">
-        <v>6754252</v>
+        <v>6754114</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2381,7 +2376,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2391,7 +2386,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,57 +2401,62 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543227</v>
+        <v>129543182</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440744</v>
+        <v>440934</v>
       </c>
       <c r="R18" t="n">
-        <v>6754336</v>
+        <v>6754244</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3075,10 +3075,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129538680</v>
+        <v>129543228</v>
       </c>
       <c r="B24" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3086,39 +3086,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440918</v>
+        <v>440716</v>
       </c>
       <c r="R24" t="n">
-        <v>6754126</v>
+        <v>6754354</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3150,7 +3145,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3160,7 +3155,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3175,19 +3170,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129543234</v>
+        <v>129539521</v>
       </c>
       <c r="B25" t="n">
         <v>79044</v>
@@ -3222,10 +3217,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440834</v>
+        <v>440725</v>
       </c>
       <c r="R25" t="n">
-        <v>6754152</v>
+        <v>6754011</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3257,7 +3252,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3267,7 +3262,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3282,19 +3277,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129539521</v>
+        <v>129543234</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3329,10 +3324,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440725</v>
+        <v>440834</v>
       </c>
       <c r="R26" t="n">
-        <v>6754011</v>
+        <v>6754152</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3364,7 +3359,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3374,7 +3369,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3389,19 +3384,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543228</v>
+        <v>129543229</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3436,10 +3431,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440716</v>
+        <v>440638</v>
       </c>
       <c r="R27" t="n">
-        <v>6754354</v>
+        <v>6754239</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3471,7 +3466,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3481,7 +3476,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3508,10 +3503,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543229</v>
+        <v>129538680</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3519,34 +3514,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440638</v>
+        <v>440918</v>
       </c>
       <c r="R28" t="n">
-        <v>6754239</v>
+        <v>6754126</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3603,19 +3603,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543222</v>
+        <v>129543233</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440728</v>
+        <v>440819</v>
       </c>
       <c r="R29" t="n">
-        <v>6754306</v>
+        <v>6754114</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3722,7 +3722,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129543233</v>
+        <v>129543222</v>
       </c>
       <c r="B30" t="n">
         <v>79044</v>
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440819</v>
+        <v>440728</v>
       </c>
       <c r="R30" t="n">
-        <v>6754114</v>
+        <v>6754306</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4389,37 +4389,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129539754</v>
+        <v>129543190</v>
       </c>
       <c r="B36" t="n">
-        <v>91574</v>
+        <v>8450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4428,10 +4429,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440820</v>
+        <v>440773</v>
       </c>
       <c r="R36" t="n">
-        <v>6754096</v>
+        <v>6754088</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4463,7 +4464,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4473,7 +4474,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4488,19 +4489,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129543159</v>
+        <v>129539754</v>
       </c>
       <c r="B37" t="n">
         <v>91574</v>
@@ -4528,17 +4529,21 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440738</v>
+        <v>440820</v>
       </c>
       <c r="R37" t="n">
-        <v>6754021</v>
+        <v>6754096</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4570,7 +4575,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4580,7 +4585,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4595,22 +4600,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129539703</v>
+        <v>129543159</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>91574</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4618,21 +4623,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4642,10 +4647,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440820</v>
+        <v>440738</v>
       </c>
       <c r="R38" t="n">
-        <v>6754096</v>
+        <v>6754021</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4677,7 +4682,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4687,7 +4692,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4702,22 +4707,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129539312</v>
+        <v>129543235</v>
       </c>
       <c r="B39" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4725,39 +4730,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440779</v>
+        <v>440863</v>
       </c>
       <c r="R39" t="n">
-        <v>6754008</v>
+        <v>6754131</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4814,19 +4814,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543235</v>
+        <v>129539703</v>
       </c>
       <c r="B40" t="n">
         <v>79044</v>
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440863</v>
+        <v>440820</v>
       </c>
       <c r="R40" t="n">
-        <v>6754131</v>
+        <v>6754096</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4921,50 +4921,50 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129543190</v>
+        <v>129539312</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440773</v>
+        <v>440779</v>
       </c>
       <c r="R41" t="n">
-        <v>6754088</v>
+        <v>6754008</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5033,12 +5033,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5376,50 +5376,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129543194</v>
+        <v>129543226</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440745</v>
+        <v>440757</v>
       </c>
       <c r="R45" t="n">
-        <v>6754333</v>
+        <v>6754337</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5451,7 +5446,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5461,7 +5456,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5488,7 +5483,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129539814</v>
+        <v>129543194</v>
       </c>
       <c r="B46" t="n">
         <v>8450</v>
@@ -5528,10 +5523,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440861</v>
+        <v>440745</v>
       </c>
       <c r="R46" t="n">
-        <v>6754168</v>
+        <v>6754333</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5563,7 +5558,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5573,7 +5568,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5588,19 +5583,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129538170</v>
+        <v>129539814</v>
       </c>
       <c r="B47" t="n">
         <v>8450</v>
@@ -5631,7 +5626,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5640,10 +5635,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440982</v>
+        <v>440861</v>
       </c>
       <c r="R47" t="n">
-        <v>6754123</v>
+        <v>6754168</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5675,7 +5670,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5685,7 +5680,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5712,45 +5707,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129543226</v>
+        <v>129538170</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440757</v>
+        <v>440982</v>
       </c>
       <c r="R48" t="n">
-        <v>6754337</v>
+        <v>6754123</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5807,22 +5807,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129539404</v>
+        <v>129543236</v>
       </c>
       <c r="B49" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5830,39 +5830,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440775</v>
+        <v>440970</v>
       </c>
       <c r="R49" t="n">
-        <v>6753988</v>
+        <v>6754114</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5894,7 +5889,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5904,7 +5899,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5919,22 +5914,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129543166</v>
+        <v>129543220</v>
       </c>
       <c r="B50" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5942,39 +5937,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440772</v>
+        <v>440851</v>
       </c>
       <c r="R50" t="n">
-        <v>6754089</v>
+        <v>6754062</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6006,7 +5996,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6016,7 +6006,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6043,10 +6033,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129543220</v>
+        <v>129539404</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6054,34 +6044,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440851</v>
+        <v>440775</v>
       </c>
       <c r="R51" t="n">
-        <v>6754062</v>
+        <v>6753988</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6113,7 +6108,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6123,7 +6118,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6138,22 +6133,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129543236</v>
+        <v>129543166</v>
       </c>
       <c r="B52" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6161,34 +6156,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440970</v>
+        <v>440772</v>
       </c>
       <c r="R52" t="n">
-        <v>6754114</v>
+        <v>6754089</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6807,50 +6807,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129543181</v>
+        <v>129543144</v>
       </c>
       <c r="B58" t="n">
-        <v>8450</v>
+        <v>91476</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>3242</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440990</v>
+        <v>440718</v>
       </c>
       <c r="R58" t="n">
-        <v>6754140</v>
+        <v>6754215</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6882,7 +6877,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6892,7 +6887,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6919,50 +6914,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129543197</v>
+        <v>129543213</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440785</v>
+        <v>440996</v>
       </c>
       <c r="R59" t="n">
-        <v>6754107</v>
+        <v>6754160</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6994,7 +6984,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7004,7 +6994,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7031,10 +7021,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129543144</v>
+        <v>129538786</v>
       </c>
       <c r="B60" t="n">
-        <v>91476</v>
+        <v>79044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7042,21 +7032,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7066,10 +7056,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440718</v>
+        <v>440918</v>
       </c>
       <c r="R60" t="n">
-        <v>6754215</v>
+        <v>6754126</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7101,7 +7091,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7111,7 +7101,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7126,57 +7116,62 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129538786</v>
+        <v>129543181</v>
       </c>
       <c r="B61" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>440918</v>
+        <v>440990</v>
       </c>
       <c r="R61" t="n">
-        <v>6754126</v>
+        <v>6754140</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7208,7 +7203,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7218,7 +7213,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7233,57 +7228,62 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129543213</v>
+        <v>129543197</v>
       </c>
       <c r="B62" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>440996</v>
+        <v>440785</v>
       </c>
       <c r="R62" t="n">
-        <v>6754160</v>
+        <v>6754107</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7315,7 +7315,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7567,38 +7567,38 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129543157</v>
+        <v>129543179</v>
       </c>
       <c r="B65" t="n">
-        <v>57887</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7607,10 +7607,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440759</v>
+        <v>440821</v>
       </c>
       <c r="R65" t="n">
-        <v>6754342</v>
+        <v>6754050</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7679,7 +7679,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129543179</v>
+        <v>129543176</v>
       </c>
       <c r="B66" t="n">
         <v>8450</v>
@@ -7710,7 +7710,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440821</v>
+        <v>440820</v>
       </c>
       <c r="R66" t="n">
-        <v>6754050</v>
+        <v>6754121</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7791,7 +7791,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129543176</v>
+        <v>129543192</v>
       </c>
       <c r="B67" t="n">
         <v>8450</v>
@@ -7822,7 +7822,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>440820</v>
+        <v>440742</v>
       </c>
       <c r="R67" t="n">
-        <v>6754121</v>
+        <v>6754310</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7903,38 +7903,38 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129543192</v>
+        <v>129543157</v>
       </c>
       <c r="B68" t="n">
-        <v>8450</v>
+        <v>57887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7943,10 +7943,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440742</v>
+        <v>440759</v>
       </c>
       <c r="R68" t="n">
-        <v>6754310</v>
+        <v>6754342</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8015,50 +8015,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129543178</v>
+        <v>129543225</v>
       </c>
       <c r="B69" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440816</v>
+        <v>440764</v>
       </c>
       <c r="R69" t="n">
-        <v>6754178</v>
+        <v>6754320</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8090,7 +8085,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8100,7 +8095,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8127,50 +8122,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129543199</v>
+        <v>129538126</v>
       </c>
       <c r="B70" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440855</v>
+        <v>441002</v>
       </c>
       <c r="R70" t="n">
-        <v>6754166</v>
+        <v>6754112</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8202,7 +8192,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8212,7 +8202,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8227,22 +8217,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129543246</v>
+        <v>129543141</v>
       </c>
       <c r="B71" t="n">
-        <v>78710</v>
+        <v>79663</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8250,21 +8240,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8274,10 +8264,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>440893</v>
+        <v>440974</v>
       </c>
       <c r="R71" t="n">
-        <v>6754230</v>
+        <v>6754141</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8309,7 +8299,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8319,7 +8309,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8328,7 +8318,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8347,10 +8336,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129538247</v>
+        <v>129543218</v>
       </c>
       <c r="B72" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8358,39 +8347,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>440944</v>
+        <v>440888</v>
       </c>
       <c r="R72" t="n">
-        <v>6754122</v>
+        <v>6754157</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8422,7 +8406,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8432,7 +8416,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8447,19 +8431,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129543141</v>
+        <v>129543143</v>
       </c>
       <c r="B73" t="n">
         <v>79663</v>
@@ -8494,10 +8478,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>440974</v>
+        <v>440893</v>
       </c>
       <c r="R73" t="n">
-        <v>6754141</v>
+        <v>6754230</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8529,7 +8513,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8539,7 +8523,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8566,7 +8550,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129543225</v>
+        <v>129543224</v>
       </c>
       <c r="B74" t="n">
         <v>79044</v>
@@ -8601,10 +8585,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>440764</v>
+        <v>440774</v>
       </c>
       <c r="R74" t="n">
-        <v>6754320</v>
+        <v>6754313</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8673,10 +8657,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129543218</v>
+        <v>129538247</v>
       </c>
       <c r="B75" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8684,34 +8668,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>440888</v>
+        <v>440944</v>
       </c>
       <c r="R75" t="n">
-        <v>6754157</v>
+        <v>6754122</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8743,7 +8732,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8753,7 +8742,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8768,22 +8757,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129538126</v>
+        <v>129543246</v>
       </c>
       <c r="B76" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8791,21 +8780,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8815,10 +8804,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>441002</v>
+        <v>440893</v>
       </c>
       <c r="R76" t="n">
-        <v>6754112</v>
+        <v>6754230</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8850,7 +8839,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8860,7 +8849,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8869,63 +8858,69 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129543143</v>
+        <v>129543178</v>
       </c>
       <c r="B77" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>440893</v>
+        <v>440816</v>
       </c>
       <c r="R77" t="n">
-        <v>6754230</v>
+        <v>6754178</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8957,7 +8952,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8967,7 +8962,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8994,45 +8989,50 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129543224</v>
+        <v>129543199</v>
       </c>
       <c r="B78" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>440774</v>
+        <v>440855</v>
       </c>
       <c r="R78" t="n">
-        <v>6754313</v>
+        <v>6754166</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9101,32 +9101,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129543154</v>
+        <v>129543164</v>
       </c>
       <c r="B79" t="n">
-        <v>90585</v>
+        <v>80178</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1962</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9136,10 +9136,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>440770</v>
+        <v>440708</v>
       </c>
       <c r="R79" t="n">
-        <v>6754101</v>
+        <v>6754116</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9171,7 +9171,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9181,7 +9181,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9208,32 +9213,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129543164</v>
+        <v>129543215</v>
       </c>
       <c r="B80" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9243,10 +9248,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>440708</v>
+        <v>440930</v>
       </c>
       <c r="R80" t="n">
-        <v>6754116</v>
+        <v>6754182</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9278,7 +9283,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9288,12 +9293,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9320,10 +9320,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129543215</v>
+        <v>129543154</v>
       </c>
       <c r="B81" t="n">
-        <v>79044</v>
+        <v>90585</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9331,21 +9331,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9355,10 +9355,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>440930</v>
+        <v>440770</v>
       </c>
       <c r="R81" t="n">
-        <v>6754182</v>
+        <v>6754101</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9390,7 +9390,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10201,7 +10201,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129538198</v>
+        <v>129543223</v>
       </c>
       <c r="B89" t="n">
         <v>79044</v>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>440969</v>
+        <v>440754</v>
       </c>
       <c r="R89" t="n">
-        <v>6754129</v>
+        <v>6754304</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10271,7 +10271,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10296,19 +10296,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129543223</v>
+        <v>129538198</v>
       </c>
       <c r="B90" t="n">
         <v>79044</v>
@@ -10343,10 +10343,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>440754</v>
+        <v>440969</v>
       </c>
       <c r="R90" t="n">
-        <v>6754304</v>
+        <v>6754129</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10378,7 +10378,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10403,12 +10403,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -10955,7 +10955,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129543232</v>
+        <v>129543214</v>
       </c>
       <c r="B96" t="n">
         <v>79044</v>
@@ -10990,10 +10990,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>440798</v>
+        <v>440948</v>
       </c>
       <c r="R96" t="n">
-        <v>6754119</v>
+        <v>6754156</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11062,7 +11062,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129543214</v>
+        <v>129543232</v>
       </c>
       <c r="B97" t="n">
         <v>79044</v>
@@ -11097,10 +11097,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>440948</v>
+        <v>440798</v>
       </c>
       <c r="R97" t="n">
-        <v>6754156</v>
+        <v>6754119</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11132,7 +11132,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11169,45 +11169,50 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129543152</v>
+        <v>129543174</v>
       </c>
       <c r="B98" t="n">
-        <v>90585</v>
+        <v>8450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>440718</v>
+        <v>440876</v>
       </c>
       <c r="R98" t="n">
-        <v>6754157</v>
+        <v>6754211</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11239,7 +11244,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11249,7 +11254,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11276,38 +11281,38 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129543170</v>
+        <v>129538483</v>
       </c>
       <c r="B99" t="n">
-        <v>57727</v>
+        <v>8450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -11316,10 +11321,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>440677</v>
+        <v>440916</v>
       </c>
       <c r="R99" t="n">
-        <v>6754247</v>
+        <v>6754159</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11351,7 +11356,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11361,12 +11366,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11381,19 +11381,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129543174</v>
+        <v>129543189</v>
       </c>
       <c r="B100" t="n">
         <v>8450</v>
@@ -11424,7 +11424,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11433,10 +11433,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>440876</v>
+        <v>440793</v>
       </c>
       <c r="R100" t="n">
-        <v>6754211</v>
+        <v>6754070</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11505,7 +11505,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129538483</v>
+        <v>129538851</v>
       </c>
       <c r="B101" t="n">
         <v>8450</v>
@@ -11545,10 +11545,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>440916</v>
+        <v>440918</v>
       </c>
       <c r="R101" t="n">
-        <v>6754159</v>
+        <v>6754126</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11617,50 +11617,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129543189</v>
+        <v>129543152</v>
       </c>
       <c r="B102" t="n">
-        <v>8450</v>
+        <v>90585</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>1962</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>440793</v>
+        <v>440718</v>
       </c>
       <c r="R102" t="n">
-        <v>6754070</v>
+        <v>6754157</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11692,7 +11687,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11702,7 +11697,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11729,38 +11724,38 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129538851</v>
+        <v>129543170</v>
       </c>
       <c r="B103" t="n">
-        <v>8450</v>
+        <v>57727</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11769,10 +11764,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>440918</v>
+        <v>440677</v>
       </c>
       <c r="R103" t="n">
-        <v>6754126</v>
+        <v>6754247</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11804,7 +11799,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11814,7 +11809,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11829,12 +11829,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -11949,10 +11949,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129538156</v>
+        <v>129538088</v>
       </c>
       <c r="B105" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11960,39 +11960,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>440982</v>
+        <v>441007</v>
       </c>
       <c r="R105" t="n">
-        <v>6754123</v>
+        <v>6754124</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12061,10 +12056,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129543217</v>
+        <v>129538156</v>
       </c>
       <c r="B106" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12072,34 +12067,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>440902</v>
+        <v>440982</v>
       </c>
       <c r="R106" t="n">
-        <v>6754164</v>
+        <v>6754123</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12141,7 +12141,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12156,19 +12156,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129538088</v>
+        <v>129543217</v>
       </c>
       <c r="B107" t="n">
         <v>79044</v>
@@ -12203,10 +12203,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>441007</v>
+        <v>440902</v>
       </c>
       <c r="R107" t="n">
-        <v>6754124</v>
+        <v>6754164</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12238,7 +12238,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12263,12 +12263,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>

--- a/artfynd/A 45199-2025 artfynd.xlsx
+++ b/artfynd/A 45199-2025 artfynd.xlsx
@@ -894,45 +894,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129543240</v>
+        <v>129543183</v>
       </c>
       <c r="B4" t="n">
-        <v>78710</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440736</v>
+        <v>440945</v>
       </c>
       <c r="R4" t="n">
-        <v>6754282</v>
+        <v>6754252</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,7 +988,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1002,45 +1006,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129543238</v>
+        <v>129543191</v>
       </c>
       <c r="B5" t="n">
-        <v>91826</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440966</v>
+        <v>440733</v>
       </c>
       <c r="R5" t="n">
-        <v>6754151</v>
+        <v>6754283</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1082,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,45 +1118,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129543158</v>
+        <v>129539316</v>
       </c>
       <c r="B6" t="n">
-        <v>91574</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440892</v>
+        <v>440779</v>
       </c>
       <c r="R6" t="n">
-        <v>6754225</v>
+        <v>6754008</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1189,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,22 +1218,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129539462</v>
+        <v>129543240</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440787</v>
+        <v>440736</v>
       </c>
       <c r="R7" t="n">
-        <v>6753947</v>
+        <v>6754282</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1296,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,50 +1319,51 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129539852</v>
+        <v>129543238</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>91826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1358,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440880</v>
+        <v>440966</v>
       </c>
       <c r="R8" t="n">
-        <v>6754175</v>
+        <v>6754151</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,7 +1408,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1403,7 +1418,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1418,12 +1433,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1642,39 +1657,39 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543168</v>
+        <v>129543158</v>
       </c>
       <c r="B11" t="n">
-        <v>92839</v>
+        <v>91574</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4365</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1684,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440718</v>
+        <v>440892</v>
       </c>
       <c r="R11" t="n">
-        <v>6754157</v>
+        <v>6754225</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,7 +1734,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1729,7 +1744,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1749,57 +1764,52 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129543183</v>
+        <v>129543168</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>92839</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>4365</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440945</v>
+        <v>440718</v>
       </c>
       <c r="R12" t="n">
-        <v>6754252</v>
+        <v>6754157</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1831,7 +1841,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1841,7 +1851,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1868,50 +1878,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129543191</v>
+        <v>129539852</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440733</v>
+        <v>440880</v>
       </c>
       <c r="R13" t="n">
-        <v>6754283</v>
+        <v>6754175</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,7 +1948,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1953,7 +1958,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1968,62 +1973,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129539316</v>
+        <v>129539462</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440779</v>
+        <v>440787</v>
       </c>
       <c r="R14" t="n">
-        <v>6754008</v>
+        <v>6753947</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2092,7 +2092,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129543227</v>
+        <v>129543216</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440744</v>
+        <v>440945</v>
       </c>
       <c r="R15" t="n">
-        <v>6754336</v>
+        <v>6754252</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2199,7 +2199,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129543216</v>
+        <v>129543227</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440945</v>
+        <v>440744</v>
       </c>
       <c r="R16" t="n">
-        <v>6754252</v>
+        <v>6754336</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2525,10 +2525,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129538905</v>
+        <v>129543219</v>
       </c>
       <c r="B19" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2536,39 +2536,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440970</v>
+        <v>440890</v>
       </c>
       <c r="R19" t="n">
-        <v>6754114</v>
+        <v>6754082</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2600,7 +2595,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2610,7 +2605,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2625,19 +2620,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129543219</v>
+        <v>129538675</v>
       </c>
       <c r="B20" t="n">
         <v>79044</v>
@@ -2672,10 +2667,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440890</v>
+        <v>440902</v>
       </c>
       <c r="R20" t="n">
-        <v>6754082</v>
+        <v>6754135</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2707,7 +2702,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2717,7 +2712,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2732,57 +2727,62 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129538675</v>
+        <v>129543195</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440902</v>
+        <v>440708</v>
       </c>
       <c r="R21" t="n">
-        <v>6754135</v>
+        <v>6754371</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2839,19 +2839,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129543195</v>
+        <v>129539529</v>
       </c>
       <c r="B22" t="n">
         <v>8450</v>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440708</v>
+        <v>440725</v>
       </c>
       <c r="R22" t="n">
-        <v>6754371</v>
+        <v>6754011</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2951,50 +2951,50 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129539529</v>
+        <v>129538905</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3003,10 +3003,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440725</v>
+        <v>440970</v>
       </c>
       <c r="R23" t="n">
-        <v>6754011</v>
+        <v>6754114</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3075,10 +3075,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129543228</v>
+        <v>129538680</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3086,34 +3086,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440716</v>
+        <v>440918</v>
       </c>
       <c r="R24" t="n">
-        <v>6754354</v>
+        <v>6754126</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3145,7 +3150,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3155,7 +3160,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3170,19 +3175,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129539521</v>
+        <v>129543234</v>
       </c>
       <c r="B25" t="n">
         <v>79044</v>
@@ -3217,10 +3222,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440725</v>
+        <v>440834</v>
       </c>
       <c r="R25" t="n">
-        <v>6754011</v>
+        <v>6754152</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3252,7 +3257,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3262,7 +3267,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3277,19 +3282,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129543234</v>
+        <v>129539521</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3324,10 +3329,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440834</v>
+        <v>440725</v>
       </c>
       <c r="R26" t="n">
-        <v>6754152</v>
+        <v>6754011</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3359,7 +3364,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3369,7 +3374,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3384,19 +3389,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543229</v>
+        <v>129543228</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3431,10 +3436,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440638</v>
+        <v>440716</v>
       </c>
       <c r="R27" t="n">
-        <v>6754239</v>
+        <v>6754354</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3466,7 +3471,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3476,7 +3481,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3503,10 +3508,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129538680</v>
+        <v>129543229</v>
       </c>
       <c r="B28" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3514,39 +3519,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440918</v>
+        <v>440638</v>
       </c>
       <c r="R28" t="n">
-        <v>6754126</v>
+        <v>6754239</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3603,19 +3603,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543233</v>
+        <v>129543222</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440819</v>
+        <v>440728</v>
       </c>
       <c r="R29" t="n">
-        <v>6754114</v>
+        <v>6754306</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3722,7 +3722,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129543222</v>
+        <v>129543233</v>
       </c>
       <c r="B30" t="n">
         <v>79044</v>
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440728</v>
+        <v>440819</v>
       </c>
       <c r="R30" t="n">
-        <v>6754306</v>
+        <v>6754114</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4389,38 +4389,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129543190</v>
+        <v>129539754</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>91574</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4429,10 +4428,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440773</v>
+        <v>440820</v>
       </c>
       <c r="R36" t="n">
-        <v>6754088</v>
+        <v>6754096</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4464,7 +4463,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4474,7 +4473,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4489,19 +4488,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129539754</v>
+        <v>129543159</v>
       </c>
       <c r="B37" t="n">
         <v>91574</v>
@@ -4529,21 +4528,17 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440820</v>
+        <v>440738</v>
       </c>
       <c r="R37" t="n">
-        <v>6754096</v>
+        <v>6754021</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4575,7 +4570,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4585,7 +4580,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4600,22 +4595,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129543159</v>
+        <v>129543235</v>
       </c>
       <c r="B38" t="n">
-        <v>91574</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4623,21 +4618,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4647,10 +4642,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440738</v>
+        <v>440863</v>
       </c>
       <c r="R38" t="n">
-        <v>6754021</v>
+        <v>6754131</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4682,7 +4677,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4692,7 +4687,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4719,7 +4714,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129543235</v>
+        <v>129539703</v>
       </c>
       <c r="B39" t="n">
         <v>79044</v>
@@ -4754,10 +4749,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440863</v>
+        <v>440820</v>
       </c>
       <c r="R39" t="n">
-        <v>6754131</v>
+        <v>6754096</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4789,7 +4784,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4799,7 +4794,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4814,57 +4809,62 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129539703</v>
+        <v>129543190</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440820</v>
+        <v>440773</v>
       </c>
       <c r="R40" t="n">
-        <v>6754096</v>
+        <v>6754088</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4921,12 +4921,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5045,45 +5045,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129543145</v>
+        <v>129539589</v>
       </c>
       <c r="B42" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440723</v>
+        <v>440769</v>
       </c>
       <c r="R42" t="n">
-        <v>6754344</v>
+        <v>6754064</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5115,7 +5120,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5125,7 +5130,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5140,19 +5145,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129539589</v>
+        <v>129538433</v>
       </c>
       <c r="B43" t="n">
         <v>8450</v>
@@ -5192,10 +5197,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440769</v>
+        <v>440937</v>
       </c>
       <c r="R43" t="n">
-        <v>6754064</v>
+        <v>6754141</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5227,7 +5232,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5237,7 +5242,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5264,50 +5269,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129538433</v>
+        <v>129543145</v>
       </c>
       <c r="B44" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440937</v>
+        <v>440723</v>
       </c>
       <c r="R44" t="n">
-        <v>6754141</v>
+        <v>6754344</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5364,12 +5364,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5819,10 +5819,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129543236</v>
+        <v>129539404</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5830,34 +5830,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440970</v>
+        <v>440775</v>
       </c>
       <c r="R49" t="n">
-        <v>6754114</v>
+        <v>6753988</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5889,7 +5894,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5899,7 +5904,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5914,22 +5919,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129543220</v>
+        <v>129543166</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5937,34 +5942,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440851</v>
+        <v>440772</v>
       </c>
       <c r="R50" t="n">
-        <v>6754062</v>
+        <v>6754089</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5996,7 +6006,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6006,7 +6016,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6026,17 +6036,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129539404</v>
+        <v>129543220</v>
       </c>
       <c r="B51" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6044,39 +6054,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440775</v>
+        <v>440851</v>
       </c>
       <c r="R51" t="n">
-        <v>6753988</v>
+        <v>6754062</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6108,7 +6113,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6118,7 +6123,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6133,22 +6138,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129543166</v>
+        <v>129543236</v>
       </c>
       <c r="B52" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6156,39 +6161,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440772</v>
+        <v>440970</v>
       </c>
       <c r="R52" t="n">
-        <v>6754089</v>
+        <v>6754114</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6907,14 +6907,14 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129543213</v>
+        <v>129538786</v>
       </c>
       <c r="B59" t="n">
         <v>79044</v>
@@ -6949,10 +6949,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440996</v>
+        <v>440918</v>
       </c>
       <c r="R59" t="n">
-        <v>6754160</v>
+        <v>6754126</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7009,19 +7009,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129538786</v>
+        <v>129543213</v>
       </c>
       <c r="B60" t="n">
         <v>79044</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440918</v>
+        <v>440996</v>
       </c>
       <c r="R60" t="n">
-        <v>6754126</v>
+        <v>6754160</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7116,19 +7116,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129543181</v>
+        <v>129543197</v>
       </c>
       <c r="B61" t="n">
         <v>8450</v>
@@ -7168,10 +7168,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>440990</v>
+        <v>440785</v>
       </c>
       <c r="R61" t="n">
-        <v>6754140</v>
+        <v>6754107</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7240,7 +7240,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129543197</v>
+        <v>129543181</v>
       </c>
       <c r="B62" t="n">
         <v>8450</v>
@@ -7280,10 +7280,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>440785</v>
+        <v>440990</v>
       </c>
       <c r="R62" t="n">
-        <v>6754107</v>
+        <v>6754140</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7315,7 +7315,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8008,17 +8008,17 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129543225</v>
+        <v>129543246</v>
       </c>
       <c r="B69" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8026,21 +8026,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8050,10 +8050,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440764</v>
+        <v>440893</v>
       </c>
       <c r="R69" t="n">
-        <v>6754320</v>
+        <v>6754230</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8104,6 +8104,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8122,10 +8123,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129538126</v>
+        <v>129538247</v>
       </c>
       <c r="B70" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8133,34 +8134,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>441002</v>
+        <v>440944</v>
       </c>
       <c r="R70" t="n">
-        <v>6754112</v>
+        <v>6754122</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8229,10 +8235,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129543141</v>
+        <v>129543225</v>
       </c>
       <c r="B71" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8240,21 +8246,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8264,10 +8270,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>440974</v>
+        <v>440764</v>
       </c>
       <c r="R71" t="n">
-        <v>6754141</v>
+        <v>6754320</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8299,7 +8305,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8309,7 +8315,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8443,10 +8449,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129543143</v>
+        <v>129543224</v>
       </c>
       <c r="B73" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8454,21 +8460,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8478,10 +8484,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>440893</v>
+        <v>440774</v>
       </c>
       <c r="R73" t="n">
-        <v>6754230</v>
+        <v>6754313</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8513,7 +8519,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8523,7 +8529,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8550,10 +8556,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129543224</v>
+        <v>129543141</v>
       </c>
       <c r="B74" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8561,21 +8567,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8585,10 +8591,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>440774</v>
+        <v>440974</v>
       </c>
       <c r="R74" t="n">
-        <v>6754313</v>
+        <v>6754141</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8620,7 +8626,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8630,7 +8636,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8650,17 +8656,17 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129538247</v>
+        <v>129543143</v>
       </c>
       <c r="B75" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8668,39 +8674,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>440944</v>
+        <v>440893</v>
       </c>
       <c r="R75" t="n">
-        <v>6754122</v>
+        <v>6754230</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8732,7 +8733,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8742,7 +8743,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8757,57 +8758,62 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129543246</v>
+        <v>129543178</v>
       </c>
       <c r="B76" t="n">
-        <v>78710</v>
+        <v>8450</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>440893</v>
+        <v>440816</v>
       </c>
       <c r="R76" t="n">
-        <v>6754230</v>
+        <v>6754178</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8839,7 +8845,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8849,7 +8855,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8858,7 +8864,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8877,7 +8882,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129543178</v>
+        <v>129543199</v>
       </c>
       <c r="B77" t="n">
         <v>8450</v>
@@ -8908,7 +8913,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -8917,10 +8922,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>440816</v>
+        <v>440855</v>
       </c>
       <c r="R77" t="n">
-        <v>6754178</v>
+        <v>6754166</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8952,7 +8957,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8962,7 +8967,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8989,50 +8994,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129543199</v>
+        <v>129538126</v>
       </c>
       <c r="B78" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>440855</v>
+        <v>441002</v>
       </c>
       <c r="R78" t="n">
-        <v>6754166</v>
+        <v>6754112</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9089,44 +9089,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129543164</v>
+        <v>129543154</v>
       </c>
       <c r="B79" t="n">
-        <v>80178</v>
+        <v>90585</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>1962</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9136,10 +9136,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>440708</v>
+        <v>440770</v>
       </c>
       <c r="R79" t="n">
-        <v>6754116</v>
+        <v>6754101</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9171,7 +9171,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9181,12 +9181,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9206,7 +9201,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9320,10 +9315,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129543154</v>
+        <v>129543221</v>
       </c>
       <c r="B81" t="n">
-        <v>90585</v>
+        <v>79044</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9331,21 +9326,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9355,10 +9350,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>440770</v>
+        <v>440739</v>
       </c>
       <c r="R81" t="n">
-        <v>6754101</v>
+        <v>6754147</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9390,7 +9385,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9400,7 +9395,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9427,32 +9422,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129543221</v>
+        <v>129543164</v>
       </c>
       <c r="B82" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9462,10 +9457,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>440739</v>
+        <v>440708</v>
       </c>
       <c r="R82" t="n">
-        <v>6754147</v>
+        <v>6754116</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9497,7 +9492,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9507,7 +9502,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9527,17 +9527,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129543155</v>
+        <v>129538573</v>
       </c>
       <c r="B83" t="n">
-        <v>56917</v>
+        <v>8450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9545,27 +9545,27 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9574,10 +9574,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>440878</v>
+        <v>440932</v>
       </c>
       <c r="R83" t="n">
-        <v>6754126</v>
+        <v>6754178</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9634,19 +9634,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129538573</v>
+        <v>129543202</v>
       </c>
       <c r="B84" t="n">
         <v>8450</v>
@@ -9677,7 +9677,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>440932</v>
+        <v>440918</v>
       </c>
       <c r="R84" t="n">
-        <v>6754178</v>
+        <v>6754161</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9746,19 +9746,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129543202</v>
+        <v>129543173</v>
       </c>
       <c r="B85" t="n">
         <v>8450</v>
@@ -9789,7 +9789,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9798,10 +9798,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>440918</v>
+        <v>440917</v>
       </c>
       <c r="R85" t="n">
-        <v>6754161</v>
+        <v>6754255</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9870,7 +9870,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129543173</v>
+        <v>129543203</v>
       </c>
       <c r="B86" t="n">
         <v>8450</v>
@@ -9901,7 +9901,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9910,10 +9910,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>440917</v>
+        <v>440946</v>
       </c>
       <c r="R86" t="n">
-        <v>6754255</v>
+        <v>6754123</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9982,10 +9982,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129543203</v>
+        <v>129543155</v>
       </c>
       <c r="B87" t="n">
-        <v>8450</v>
+        <v>56917</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9993,27 +9993,27 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10022,10 +10022,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>440946</v>
+        <v>440878</v>
       </c>
       <c r="R87" t="n">
-        <v>6754123</v>
+        <v>6754126</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10087,17 +10087,17 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129543171</v>
+        <v>129538198</v>
       </c>
       <c r="B88" t="n">
-        <v>91606</v>
+        <v>79044</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10105,21 +10105,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10129,10 +10129,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>440996</v>
+        <v>440969</v>
       </c>
       <c r="R88" t="n">
-        <v>6754160</v>
+        <v>6754129</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10189,12 +10189,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -10308,10 +10308,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129538198</v>
+        <v>129543171</v>
       </c>
       <c r="B90" t="n">
-        <v>79044</v>
+        <v>91606</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10319,21 +10319,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10343,10 +10343,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>440969</v>
+        <v>440996</v>
       </c>
       <c r="R90" t="n">
-        <v>6754129</v>
+        <v>6754160</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10403,12 +10403,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -10622,7 +10622,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10729,7 +10729,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -10955,7 +10955,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129543214</v>
+        <v>129543232</v>
       </c>
       <c r="B96" t="n">
         <v>79044</v>
@@ -10990,10 +10990,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>440948</v>
+        <v>440798</v>
       </c>
       <c r="R96" t="n">
-        <v>6754156</v>
+        <v>6754119</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11062,7 +11062,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129543232</v>
+        <v>129543214</v>
       </c>
       <c r="B97" t="n">
         <v>79044</v>
@@ -11097,10 +11097,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>440798</v>
+        <v>440948</v>
       </c>
       <c r="R97" t="n">
-        <v>6754119</v>
+        <v>6754156</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11132,7 +11132,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11169,50 +11169,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129543174</v>
+        <v>129543152</v>
       </c>
       <c r="B98" t="n">
-        <v>8450</v>
+        <v>90585</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>1962</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>440876</v>
+        <v>440718</v>
       </c>
       <c r="R98" t="n">
-        <v>6754211</v>
+        <v>6754157</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11244,7 +11239,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11254,7 +11249,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11274,45 +11269,45 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129538483</v>
+        <v>129543170</v>
       </c>
       <c r="B99" t="n">
-        <v>8450</v>
+        <v>57727</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -11321,10 +11316,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>440916</v>
+        <v>440677</v>
       </c>
       <c r="R99" t="n">
-        <v>6754159</v>
+        <v>6754247</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11356,7 +11351,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11366,7 +11361,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11381,19 +11381,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129543189</v>
+        <v>129543174</v>
       </c>
       <c r="B100" t="n">
         <v>8450</v>
@@ -11424,7 +11424,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11433,10 +11433,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>440793</v>
+        <v>440876</v>
       </c>
       <c r="R100" t="n">
-        <v>6754070</v>
+        <v>6754211</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11505,7 +11505,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129538851</v>
+        <v>129538483</v>
       </c>
       <c r="B101" t="n">
         <v>8450</v>
@@ -11545,10 +11545,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>440918</v>
+        <v>440916</v>
       </c>
       <c r="R101" t="n">
-        <v>6754126</v>
+        <v>6754159</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11617,45 +11617,50 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129543152</v>
+        <v>129543189</v>
       </c>
       <c r="B102" t="n">
-        <v>90585</v>
+        <v>8450</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>440718</v>
+        <v>440793</v>
       </c>
       <c r="R102" t="n">
-        <v>6754157</v>
+        <v>6754070</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11687,7 +11692,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11697,7 +11702,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11724,38 +11729,38 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129543170</v>
+        <v>129538851</v>
       </c>
       <c r="B103" t="n">
-        <v>57727</v>
+        <v>8450</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11764,10 +11769,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>440677</v>
+        <v>440918</v>
       </c>
       <c r="R103" t="n">
-        <v>6754247</v>
+        <v>6754126</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11799,7 +11804,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11809,12 +11814,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11829,22 +11829,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129543247</v>
+        <v>129543217</v>
       </c>
       <c r="B104" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11852,21 +11852,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11876,10 +11876,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>440894</v>
+        <v>440902</v>
       </c>
       <c r="R104" t="n">
-        <v>6754104</v>
+        <v>6754164</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11911,7 +11911,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11921,7 +11921,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11930,7 +11930,6 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -12056,10 +12055,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129538156</v>
+        <v>129543247</v>
       </c>
       <c r="B106" t="n">
-        <v>57724</v>
+        <v>78710</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12067,39 +12066,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>440982</v>
+        <v>440894</v>
       </c>
       <c r="R106" t="n">
-        <v>6754123</v>
+        <v>6754104</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12131,7 +12125,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12141,7 +12135,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12150,28 +12144,29 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129543217</v>
+        <v>129538156</v>
       </c>
       <c r="B107" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12179,34 +12174,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>440902</v>
+        <v>440982</v>
       </c>
       <c r="R107" t="n">
-        <v>6754164</v>
+        <v>6754123</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12238,7 +12238,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12263,12 +12263,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>

--- a/artfynd/A 45199-2025 artfynd.xlsx
+++ b/artfynd/A 45199-2025 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129539829</v>
+        <v>129539413</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440861</v>
+        <v>440775</v>
       </c>
       <c r="R2" t="n">
-        <v>6754168</v>
+        <v>6753988</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,50 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129539413</v>
+        <v>129539829</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440775</v>
+        <v>440861</v>
       </c>
       <c r="R3" t="n">
-        <v>6753988</v>
+        <v>6754168</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,50 +894,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129543183</v>
+        <v>129543240</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>78710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440945</v>
+        <v>440736</v>
       </c>
       <c r="R4" t="n">
-        <v>6754252</v>
+        <v>6754282</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,6 +983,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1006,50 +1002,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129543191</v>
+        <v>129543158</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>91574</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440733</v>
+        <v>440892</v>
       </c>
       <c r="R5" t="n">
-        <v>6754283</v>
+        <v>6754225</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1072,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1082,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129539316</v>
+        <v>129543191</v>
       </c>
       <c r="B6" t="n">
         <v>8450</v>
@@ -1149,7 +1140,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1158,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440779</v>
+        <v>440733</v>
       </c>
       <c r="R6" t="n">
-        <v>6754008</v>
+        <v>6754283</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1184,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1194,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,57 +1209,62 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129543240</v>
+        <v>129539316</v>
       </c>
       <c r="B7" t="n">
-        <v>78710</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440736</v>
+        <v>440779</v>
       </c>
       <c r="R7" t="n">
-        <v>6754282</v>
+        <v>6754008</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1296,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1306,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1319,64 +1315,68 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129543238</v>
+        <v>129543183</v>
       </c>
       <c r="B8" t="n">
-        <v>91826</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440966</v>
+        <v>440945</v>
       </c>
       <c r="R8" t="n">
-        <v>6754151</v>
+        <v>6754252</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,32 +1445,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129543239</v>
+        <v>129539852</v>
       </c>
       <c r="B9" t="n">
-        <v>80084</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440708</v>
+        <v>440880</v>
       </c>
       <c r="R9" t="n">
-        <v>6754116</v>
+        <v>6754175</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1525,12 +1525,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,22 +1540,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129543147</v>
+        <v>129539462</v>
       </c>
       <c r="B10" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,21 +1563,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1592,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440701</v>
+        <v>440787</v>
       </c>
       <c r="R10" t="n">
-        <v>6754185</v>
+        <v>6753947</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,7 +1622,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1637,7 +1632,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,44 +1647,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543158</v>
+        <v>129543238</v>
       </c>
       <c r="B11" t="n">
-        <v>91574</v>
+        <v>91826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>65</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440892</v>
+        <v>440966</v>
       </c>
       <c r="R11" t="n">
-        <v>6754225</v>
+        <v>6754151</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,7 +1729,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1744,7 +1739,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1764,7 +1759,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1878,32 +1873,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129539852</v>
+        <v>129543239</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>80084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1913,10 +1908,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440880</v>
+        <v>440708</v>
       </c>
       <c r="R13" t="n">
-        <v>6754175</v>
+        <v>6754116</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,7 +1943,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1958,7 +1953,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1973,22 +1973,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129539462</v>
+        <v>129543147</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,21 +1996,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440787</v>
+        <v>440701</v>
       </c>
       <c r="R14" t="n">
-        <v>6753947</v>
+        <v>6754185</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2080,19 +2080,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129543216</v>
+        <v>129543227</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440945</v>
+        <v>440744</v>
       </c>
       <c r="R15" t="n">
-        <v>6754252</v>
+        <v>6754336</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2199,7 +2199,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129543227</v>
+        <v>129543216</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440744</v>
+        <v>440945</v>
       </c>
       <c r="R16" t="n">
-        <v>6754336</v>
+        <v>6754252</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2306,7 +2306,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129539028</v>
+        <v>129543182</v>
       </c>
       <c r="B17" t="n">
         <v>8450</v>
@@ -2335,16 +2335,21 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440970</v>
+        <v>440934</v>
       </c>
       <c r="R17" t="n">
-        <v>6754114</v>
+        <v>6754244</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2376,7 +2381,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2386,7 +2391,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2401,19 +2406,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543182</v>
+        <v>129539028</v>
       </c>
       <c r="B18" t="n">
         <v>8450</v>
@@ -2442,21 +2447,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440934</v>
+        <v>440970</v>
       </c>
       <c r="R18" t="n">
-        <v>6754244</v>
+        <v>6754114</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2513,12 +2513,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2739,38 +2739,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129543195</v>
+        <v>129538905</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440708</v>
+        <v>440970</v>
       </c>
       <c r="R21" t="n">
-        <v>6754371</v>
+        <v>6754114</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2839,19 +2839,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129539529</v>
+        <v>129543195</v>
       </c>
       <c r="B22" t="n">
         <v>8450</v>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440725</v>
+        <v>440708</v>
       </c>
       <c r="R22" t="n">
-        <v>6754011</v>
+        <v>6754371</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2951,50 +2951,50 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129538905</v>
+        <v>129539529</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3003,10 +3003,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440970</v>
+        <v>440725</v>
       </c>
       <c r="R23" t="n">
-        <v>6754114</v>
+        <v>6754011</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3075,10 +3075,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129538680</v>
+        <v>129543234</v>
       </c>
       <c r="B24" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3086,39 +3086,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440918</v>
+        <v>440834</v>
       </c>
       <c r="R24" t="n">
-        <v>6754126</v>
+        <v>6754152</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3150,7 +3145,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3160,7 +3155,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3175,19 +3170,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129543234</v>
+        <v>129539521</v>
       </c>
       <c r="B25" t="n">
         <v>79044</v>
@@ -3222,10 +3217,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440834</v>
+        <v>440725</v>
       </c>
       <c r="R25" t="n">
-        <v>6754152</v>
+        <v>6754011</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3257,7 +3252,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3267,7 +3262,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3282,19 +3277,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129539521</v>
+        <v>129543228</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3329,10 +3324,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440725</v>
+        <v>440716</v>
       </c>
       <c r="R26" t="n">
-        <v>6754011</v>
+        <v>6754354</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3364,7 +3359,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3374,7 +3369,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3389,19 +3384,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543228</v>
+        <v>129543229</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3436,10 +3431,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440716</v>
+        <v>440638</v>
       </c>
       <c r="R27" t="n">
-        <v>6754354</v>
+        <v>6754239</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3471,7 +3466,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3481,7 +3476,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3508,10 +3503,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543229</v>
+        <v>129538680</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3519,34 +3514,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440638</v>
+        <v>440918</v>
       </c>
       <c r="R28" t="n">
-        <v>6754239</v>
+        <v>6754126</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3603,12 +3603,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3829,7 +3829,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129543188</v>
+        <v>129543201</v>
       </c>
       <c r="B31" t="n">
         <v>8450</v>
@@ -3869,10 +3869,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440824</v>
+        <v>440885</v>
       </c>
       <c r="R31" t="n">
-        <v>6754063</v>
+        <v>6754148</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3941,7 +3941,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129543201</v>
+        <v>129543196</v>
       </c>
       <c r="B32" t="n">
         <v>8450</v>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440885</v>
+        <v>440716</v>
       </c>
       <c r="R32" t="n">
-        <v>6754148</v>
+        <v>6754046</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4277,7 +4277,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129543196</v>
+        <v>129543188</v>
       </c>
       <c r="B35" t="n">
         <v>8450</v>
@@ -4317,10 +4317,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440716</v>
+        <v>440824</v>
       </c>
       <c r="R35" t="n">
-        <v>6754046</v>
+        <v>6754063</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4389,10 +4389,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129539754</v>
+        <v>129543235</v>
       </c>
       <c r="B36" t="n">
-        <v>91574</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4400,38 +4400,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440820</v>
+        <v>440863</v>
       </c>
       <c r="R36" t="n">
-        <v>6754096</v>
+        <v>6754131</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4463,7 +4459,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4473,7 +4469,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4488,19 +4484,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129543159</v>
+        <v>129539754</v>
       </c>
       <c r="B37" t="n">
         <v>91574</v>
@@ -4528,17 +4524,21 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440738</v>
+        <v>440820</v>
       </c>
       <c r="R37" t="n">
-        <v>6754021</v>
+        <v>6754096</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4595,22 +4595,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129543235</v>
+        <v>129543159</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>91574</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4618,21 +4618,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4642,10 +4642,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440863</v>
+        <v>440738</v>
       </c>
       <c r="R38" t="n">
-        <v>6754131</v>
+        <v>6754021</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4714,10 +4714,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129539703</v>
+        <v>129539312</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4725,34 +4725,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440820</v>
+        <v>440779</v>
       </c>
       <c r="R39" t="n">
-        <v>6754096</v>
+        <v>6754008</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4821,50 +4826,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543190</v>
+        <v>129539703</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440773</v>
+        <v>440820</v>
       </c>
       <c r="R40" t="n">
-        <v>6754088</v>
+        <v>6754096</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4921,50 +4921,50 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129539312</v>
+        <v>129543190</v>
       </c>
       <c r="B41" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440779</v>
+        <v>440773</v>
       </c>
       <c r="R41" t="n">
-        <v>6754008</v>
+        <v>6754088</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5033,62 +5033,57 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129539589</v>
+        <v>129543145</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440769</v>
+        <v>440723</v>
       </c>
       <c r="R42" t="n">
-        <v>6754064</v>
+        <v>6754344</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5120,7 +5115,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5130,7 +5125,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5145,12 +5140,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5269,45 +5264,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129543145</v>
+        <v>129539589</v>
       </c>
       <c r="B44" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440723</v>
+        <v>440769</v>
       </c>
       <c r="R44" t="n">
-        <v>6754344</v>
+        <v>6754064</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5364,57 +5364,62 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129543226</v>
+        <v>129539814</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440757</v>
+        <v>440861</v>
       </c>
       <c r="R45" t="n">
-        <v>6754337</v>
+        <v>6754168</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5446,7 +5451,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5456,7 +5461,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5471,19 +5476,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129543194</v>
+        <v>129538170</v>
       </c>
       <c r="B46" t="n">
         <v>8450</v>
@@ -5514,7 +5519,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5523,10 +5528,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440745</v>
+        <v>440982</v>
       </c>
       <c r="R46" t="n">
-        <v>6754333</v>
+        <v>6754123</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5558,7 +5563,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5568,7 +5573,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5583,19 +5588,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129539814</v>
+        <v>129543194</v>
       </c>
       <c r="B47" t="n">
         <v>8450</v>
@@ -5635,10 +5640,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440861</v>
+        <v>440745</v>
       </c>
       <c r="R47" t="n">
-        <v>6754168</v>
+        <v>6754333</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5670,7 +5675,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5680,7 +5685,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5695,62 +5700,57 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129538170</v>
+        <v>129543226</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440982</v>
+        <v>440757</v>
       </c>
       <c r="R48" t="n">
-        <v>6754123</v>
+        <v>6754337</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5807,22 +5807,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129539404</v>
+        <v>129543220</v>
       </c>
       <c r="B49" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5830,39 +5830,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440775</v>
+        <v>440851</v>
       </c>
       <c r="R49" t="n">
-        <v>6753988</v>
+        <v>6754062</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5894,7 +5889,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5904,7 +5899,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5919,22 +5914,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129543166</v>
+        <v>129543236</v>
       </c>
       <c r="B50" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5942,39 +5937,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440772</v>
+        <v>440970</v>
       </c>
       <c r="R50" t="n">
-        <v>6754089</v>
+        <v>6754114</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6006,7 +5996,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6016,7 +6006,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6036,17 +6026,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129543220</v>
+        <v>129539404</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6054,34 +6044,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440851</v>
+        <v>440775</v>
       </c>
       <c r="R51" t="n">
-        <v>6754062</v>
+        <v>6753988</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6113,7 +6108,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6123,7 +6118,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6138,22 +6133,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129543236</v>
+        <v>129543166</v>
       </c>
       <c r="B52" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6161,34 +6156,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440970</v>
+        <v>440772</v>
       </c>
       <c r="R52" t="n">
-        <v>6754114</v>
+        <v>6754089</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6476,45 +6476,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129538554</v>
+        <v>129543185</v>
       </c>
       <c r="B55" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440919</v>
+        <v>440888</v>
       </c>
       <c r="R55" t="n">
-        <v>6754174</v>
+        <v>6754217</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6546,7 +6551,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6556,7 +6561,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6571,19 +6576,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129543185</v>
+        <v>129538256</v>
       </c>
       <c r="B56" t="n">
         <v>8450</v>
@@ -6614,7 +6619,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6623,10 +6628,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440888</v>
+        <v>440944</v>
       </c>
       <c r="R56" t="n">
-        <v>6754217</v>
+        <v>6754122</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6658,7 +6663,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6668,7 +6673,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6683,62 +6688,57 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129538256</v>
+        <v>129538554</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440944</v>
+        <v>440919</v>
       </c>
       <c r="R57" t="n">
-        <v>6754122</v>
+        <v>6754174</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6807,10 +6807,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129543144</v>
+        <v>129543213</v>
       </c>
       <c r="B58" t="n">
-        <v>91476</v>
+        <v>79044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6818,21 +6818,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440718</v>
+        <v>440996</v>
       </c>
       <c r="R58" t="n">
-        <v>6754215</v>
+        <v>6754160</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6907,17 +6907,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129538786</v>
+        <v>129543144</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>91476</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6925,21 +6925,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6949,10 +6949,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440918</v>
+        <v>440718</v>
       </c>
       <c r="R59" t="n">
-        <v>6754126</v>
+        <v>6754215</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7009,19 +7009,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129543213</v>
+        <v>129538786</v>
       </c>
       <c r="B60" t="n">
         <v>79044</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440996</v>
+        <v>440918</v>
       </c>
       <c r="R60" t="n">
-        <v>6754160</v>
+        <v>6754126</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7116,19 +7116,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129543197</v>
+        <v>129543181</v>
       </c>
       <c r="B61" t="n">
         <v>8450</v>
@@ -7168,10 +7168,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>440785</v>
+        <v>440990</v>
       </c>
       <c r="R61" t="n">
-        <v>6754107</v>
+        <v>6754140</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7240,7 +7240,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129543181</v>
+        <v>129543197</v>
       </c>
       <c r="B62" t="n">
         <v>8450</v>
@@ -7280,10 +7280,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>440990</v>
+        <v>440785</v>
       </c>
       <c r="R62" t="n">
-        <v>6754140</v>
+        <v>6754107</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7315,7 +7315,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7352,10 +7352,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129543245</v>
+        <v>129543157</v>
       </c>
       <c r="B63" t="n">
-        <v>78710</v>
+        <v>57887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7363,34 +7363,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440986</v>
+        <v>440759</v>
       </c>
       <c r="R63" t="n">
-        <v>6754157</v>
+        <v>6754342</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7422,7 +7427,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7432,7 +7437,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7441,7 +7446,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7460,45 +7464,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129539371</v>
+        <v>129543179</v>
       </c>
       <c r="B64" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440769</v>
+        <v>440821</v>
       </c>
       <c r="R64" t="n">
-        <v>6754008</v>
+        <v>6754050</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7530,7 +7539,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7540,7 +7549,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7555,19 +7564,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129543179</v>
+        <v>129543176</v>
       </c>
       <c r="B65" t="n">
         <v>8450</v>
@@ -7598,7 +7607,7 @@
       <c r="I65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7607,10 +7616,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440821</v>
+        <v>440820</v>
       </c>
       <c r="R65" t="n">
-        <v>6754050</v>
+        <v>6754121</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7642,7 +7651,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7652,7 +7661,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7679,7 +7688,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129543176</v>
+        <v>129543192</v>
       </c>
       <c r="B66" t="n">
         <v>8450</v>
@@ -7710,7 +7719,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7719,10 +7728,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440820</v>
+        <v>440742</v>
       </c>
       <c r="R66" t="n">
-        <v>6754121</v>
+        <v>6754310</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7754,7 +7763,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7764,7 +7773,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7791,50 +7800,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129543192</v>
+        <v>129543245</v>
       </c>
       <c r="B67" t="n">
-        <v>8450</v>
+        <v>78710</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>440742</v>
+        <v>440986</v>
       </c>
       <c r="R67" t="n">
-        <v>6754310</v>
+        <v>6754157</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7866,7 +7870,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7876,7 +7880,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7885,6 +7889,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7903,10 +7908,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129543157</v>
+        <v>129539371</v>
       </c>
       <c r="B68" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7914,39 +7919,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440759</v>
+        <v>440769</v>
       </c>
       <c r="R68" t="n">
-        <v>6754342</v>
+        <v>6754008</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8003,22 +8003,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129543246</v>
+        <v>129543218</v>
       </c>
       <c r="B69" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8026,21 +8026,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8050,10 +8050,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440893</v>
+        <v>440888</v>
       </c>
       <c r="R69" t="n">
-        <v>6754230</v>
+        <v>6754157</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8104,7 +8104,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8123,10 +8122,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129538247</v>
+        <v>129543224</v>
       </c>
       <c r="B70" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8134,39 +8133,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440944</v>
+        <v>440774</v>
       </c>
       <c r="R70" t="n">
-        <v>6754122</v>
+        <v>6754313</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8198,7 +8192,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8208,7 +8202,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8223,12 +8217,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8342,7 +8336,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129543218</v>
+        <v>129538126</v>
       </c>
       <c r="B72" t="n">
         <v>79044</v>
@@ -8377,10 +8371,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>440888</v>
+        <v>441002</v>
       </c>
       <c r="R72" t="n">
-        <v>6754157</v>
+        <v>6754112</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8412,7 +8406,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8422,7 +8416,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8437,22 +8431,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129543224</v>
+        <v>129538247</v>
       </c>
       <c r="B73" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8460,34 +8454,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>440774</v>
+        <v>440944</v>
       </c>
       <c r="R73" t="n">
-        <v>6754313</v>
+        <v>6754122</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8519,7 +8518,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8529,7 +8528,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8544,22 +8543,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129543141</v>
+        <v>129543246</v>
       </c>
       <c r="B74" t="n">
-        <v>79663</v>
+        <v>78710</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8567,21 +8566,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8591,10 +8590,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>440974</v>
+        <v>440893</v>
       </c>
       <c r="R74" t="n">
-        <v>6754141</v>
+        <v>6754230</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8626,7 +8625,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8636,7 +8635,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8645,6 +8644,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8656,14 +8656,14 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129543143</v>
+        <v>129543141</v>
       </c>
       <c r="B75" t="n">
         <v>79663</v>
@@ -8698,10 +8698,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>440893</v>
+        <v>440974</v>
       </c>
       <c r="R75" t="n">
-        <v>6754230</v>
+        <v>6754141</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8763,57 +8763,52 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129543178</v>
+        <v>129543143</v>
       </c>
       <c r="B76" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>440816</v>
+        <v>440893</v>
       </c>
       <c r="R76" t="n">
-        <v>6754178</v>
+        <v>6754230</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8845,7 +8840,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8855,7 +8850,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8994,45 +8989,50 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129538126</v>
+        <v>129543178</v>
       </c>
       <c r="B78" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>441002</v>
+        <v>440816</v>
       </c>
       <c r="R78" t="n">
-        <v>6754112</v>
+        <v>6754178</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9089,12 +9089,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9422,10 +9422,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129543164</v>
+        <v>129543155</v>
       </c>
       <c r="B82" t="n">
-        <v>80178</v>
+        <v>56917</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9433,34 +9433,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>440708</v>
+        <v>440878</v>
       </c>
       <c r="R82" t="n">
-        <v>6754116</v>
+        <v>6754126</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9492,7 +9497,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9502,12 +9507,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9527,14 +9527,14 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129538573</v>
+        <v>129543173</v>
       </c>
       <c r="B83" t="n">
         <v>8450</v>
@@ -9574,10 +9574,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>440932</v>
+        <v>440917</v>
       </c>
       <c r="R83" t="n">
-        <v>6754178</v>
+        <v>6754255</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9634,19 +9634,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129543202</v>
+        <v>129538573</v>
       </c>
       <c r="B84" t="n">
         <v>8450</v>
@@ -9677,7 +9677,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>440918</v>
+        <v>440932</v>
       </c>
       <c r="R84" t="n">
-        <v>6754161</v>
+        <v>6754178</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9746,19 +9746,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129543173</v>
+        <v>129543203</v>
       </c>
       <c r="B85" t="n">
         <v>8450</v>
@@ -9789,7 +9789,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9798,10 +9798,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>440917</v>
+        <v>440946</v>
       </c>
       <c r="R85" t="n">
-        <v>6754255</v>
+        <v>6754123</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9870,10 +9870,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129543203</v>
+        <v>129543164</v>
       </c>
       <c r="B86" t="n">
-        <v>8450</v>
+        <v>80178</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9881,39 +9881,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6462</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>440946</v>
+        <v>440708</v>
       </c>
       <c r="R86" t="n">
-        <v>6754123</v>
+        <v>6754116</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9945,7 +9940,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9955,7 +9950,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9982,10 +9982,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129543155</v>
+        <v>129543202</v>
       </c>
       <c r="B87" t="n">
-        <v>56917</v>
+        <v>8450</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9993,27 +9993,27 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10022,10 +10022,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>440878</v>
+        <v>440918</v>
       </c>
       <c r="R87" t="n">
-        <v>6754126</v>
+        <v>6754161</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10087,17 +10087,17 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129538198</v>
+        <v>129543171</v>
       </c>
       <c r="B88" t="n">
-        <v>79044</v>
+        <v>91606</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10105,21 +10105,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10129,10 +10129,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>440969</v>
+        <v>440996</v>
       </c>
       <c r="R88" t="n">
-        <v>6754129</v>
+        <v>6754160</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10189,19 +10189,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129543223</v>
+        <v>129538198</v>
       </c>
       <c r="B89" t="n">
         <v>79044</v>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>440754</v>
+        <v>440969</v>
       </c>
       <c r="R89" t="n">
-        <v>6754304</v>
+        <v>6754129</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10271,7 +10271,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10296,22 +10296,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129543171</v>
+        <v>129543223</v>
       </c>
       <c r="B90" t="n">
-        <v>91606</v>
+        <v>79044</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10319,21 +10319,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10343,10 +10343,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>440996</v>
+        <v>440754</v>
       </c>
       <c r="R90" t="n">
-        <v>6754160</v>
+        <v>6754304</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10378,7 +10378,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10622,52 +10622,57 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129543142</v>
+        <v>129543175</v>
       </c>
       <c r="B93" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>440949</v>
+        <v>440896</v>
       </c>
       <c r="R93" t="n">
-        <v>6754170</v>
+        <v>6754124</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10699,7 +10704,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10709,7 +10714,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10729,57 +10734,52 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129543175</v>
+        <v>129543142</v>
       </c>
       <c r="B94" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>440896</v>
+        <v>440949</v>
       </c>
       <c r="R94" t="n">
-        <v>6754124</v>
+        <v>6754170</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11269,45 +11269,45 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129543170</v>
+        <v>129543189</v>
       </c>
       <c r="B99" t="n">
-        <v>57727</v>
+        <v>8450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -11316,10 +11316,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>440677</v>
+        <v>440793</v>
       </c>
       <c r="R99" t="n">
-        <v>6754247</v>
+        <v>6754070</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11361,12 +11361,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11393,7 +11388,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129543174</v>
+        <v>129538851</v>
       </c>
       <c r="B100" t="n">
         <v>8450</v>
@@ -11433,10 +11428,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>440876</v>
+        <v>440918</v>
       </c>
       <c r="R100" t="n">
-        <v>6754211</v>
+        <v>6754126</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11468,7 +11463,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11478,7 +11473,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11493,50 +11488,50 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129538483</v>
+        <v>129543170</v>
       </c>
       <c r="B101" t="n">
-        <v>8450</v>
+        <v>57727</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -11545,10 +11540,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>440916</v>
+        <v>440677</v>
       </c>
       <c r="R101" t="n">
-        <v>6754159</v>
+        <v>6754247</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11580,7 +11575,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11590,7 +11585,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11605,19 +11605,19 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129543189</v>
+        <v>129538483</v>
       </c>
       <c r="B102" t="n">
         <v>8450</v>
@@ -11648,7 +11648,7 @@
       <c r="I102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -11657,10 +11657,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>440793</v>
+        <v>440916</v>
       </c>
       <c r="R102" t="n">
-        <v>6754070</v>
+        <v>6754159</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11692,7 +11692,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11702,7 +11702,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11717,19 +11717,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129538851</v>
+        <v>129543174</v>
       </c>
       <c r="B103" t="n">
         <v>8450</v>
@@ -11769,10 +11769,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>440918</v>
+        <v>440876</v>
       </c>
       <c r="R103" t="n">
-        <v>6754126</v>
+        <v>6754211</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11829,22 +11829,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129543217</v>
+        <v>129543247</v>
       </c>
       <c r="B104" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11852,21 +11852,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11876,10 +11876,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>440902</v>
+        <v>440894</v>
       </c>
       <c r="R104" t="n">
-        <v>6754164</v>
+        <v>6754104</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11911,7 +11911,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11921,7 +11921,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11930,6 +11930,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11948,7 +11949,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129538088</v>
+        <v>129543217</v>
       </c>
       <c r="B105" t="n">
         <v>79044</v>
@@ -11983,10 +11984,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>441007</v>
+        <v>440902</v>
       </c>
       <c r="R105" t="n">
-        <v>6754124</v>
+        <v>6754164</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12018,7 +12019,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12028,7 +12029,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12043,22 +12044,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129543247</v>
+        <v>129538088</v>
       </c>
       <c r="B106" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12066,21 +12067,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12090,10 +12091,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>440894</v>
+        <v>441007</v>
       </c>
       <c r="R106" t="n">
-        <v>6754104</v>
+        <v>6754124</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12125,7 +12126,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12135,7 +12136,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12144,19 +12145,18 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>

--- a/artfynd/A 45199-2025 artfynd.xlsx
+++ b/artfynd/A 45199-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129539413</v>
+        <v>129539829</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440775</v>
+        <v>440861</v>
       </c>
       <c r="R2" t="n">
-        <v>6753988</v>
+        <v>6754168</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129539829</v>
+        <v>129539413</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440861</v>
+        <v>440775</v>
       </c>
       <c r="R3" t="n">
-        <v>6754168</v>
+        <v>6753988</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129543240</v>
+        <v>129543238</v>
       </c>
       <c r="B4" t="n">
-        <v>78710</v>
+        <v>91826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440736</v>
+        <v>440966</v>
       </c>
       <c r="R4" t="n">
-        <v>6754282</v>
+        <v>6754151</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,7 +983,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1109,50 +1108,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129543191</v>
+        <v>129539852</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440733</v>
+        <v>440880</v>
       </c>
       <c r="R6" t="n">
-        <v>6754283</v>
+        <v>6754175</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1194,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,62 +1203,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129539316</v>
+        <v>129539462</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440779</v>
+        <v>440787</v>
       </c>
       <c r="R7" t="n">
-        <v>6754008</v>
+        <v>6753947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,50 +1322,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129543183</v>
+        <v>129543240</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>78710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440945</v>
+        <v>440736</v>
       </c>
       <c r="R8" t="n">
-        <v>6754252</v>
+        <v>6754282</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1418,7 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,6 +1411,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1445,32 +1430,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129539852</v>
+        <v>129543168</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>92839</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1480,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440880</v>
+        <v>440718</v>
       </c>
       <c r="R9" t="n">
-        <v>6754175</v>
+        <v>6754157</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,7 +1500,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1525,7 +1510,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,44 +1525,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129539462</v>
+        <v>129543239</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>80084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1587,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440787</v>
+        <v>440708</v>
       </c>
       <c r="R10" t="n">
-        <v>6753947</v>
+        <v>6754116</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,7 +1607,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1632,7 +1617,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1647,44 +1637,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543238</v>
+        <v>129543147</v>
       </c>
       <c r="B11" t="n">
-        <v>91826</v>
+        <v>79663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1694,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440966</v>
+        <v>440701</v>
       </c>
       <c r="R11" t="n">
-        <v>6754151</v>
+        <v>6754185</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1719,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1739,7 +1729,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,45 +1756,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129543168</v>
+        <v>129543183</v>
       </c>
       <c r="B12" t="n">
-        <v>92839</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4365</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440718</v>
+        <v>440945</v>
       </c>
       <c r="R12" t="n">
-        <v>6754157</v>
+        <v>6754252</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,7 +1831,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1846,7 +1841,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1873,10 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129543239</v>
+        <v>129543191</v>
       </c>
       <c r="B13" t="n">
-        <v>80084</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1884,34 +1879,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6457</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440708</v>
+        <v>440733</v>
       </c>
       <c r="R13" t="n">
-        <v>6754116</v>
+        <v>6754283</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1953,12 +1953,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,45 +1980,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129543147</v>
+        <v>129539316</v>
       </c>
       <c r="B14" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440701</v>
+        <v>440779</v>
       </c>
       <c r="R14" t="n">
-        <v>6754185</v>
+        <v>6754008</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2080,19 +2080,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129543227</v>
+        <v>129543216</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440744</v>
+        <v>440945</v>
       </c>
       <c r="R15" t="n">
-        <v>6754336</v>
+        <v>6754252</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2199,7 +2199,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129543216</v>
+        <v>129543227</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440945</v>
+        <v>440744</v>
       </c>
       <c r="R16" t="n">
-        <v>6754252</v>
+        <v>6754336</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2306,7 +2306,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129543182</v>
+        <v>129539028</v>
       </c>
       <c r="B17" t="n">
         <v>8450</v>
@@ -2335,21 +2335,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440934</v>
+        <v>440970</v>
       </c>
       <c r="R17" t="n">
-        <v>6754244</v>
+        <v>6754114</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2381,7 +2376,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2391,7 +2386,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,19 +2401,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129539028</v>
+        <v>129543182</v>
       </c>
       <c r="B18" t="n">
         <v>8450</v>
@@ -2447,16 +2442,21 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440970</v>
+        <v>440934</v>
       </c>
       <c r="R18" t="n">
-        <v>6754114</v>
+        <v>6754244</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2513,12 +2513,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3829,7 +3829,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129543201</v>
+        <v>129543188</v>
       </c>
       <c r="B31" t="n">
         <v>8450</v>
@@ -3869,10 +3869,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440885</v>
+        <v>440824</v>
       </c>
       <c r="R31" t="n">
-        <v>6754148</v>
+        <v>6754063</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3941,7 +3941,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129543196</v>
+        <v>129543201</v>
       </c>
       <c r="B32" t="n">
         <v>8450</v>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440716</v>
+        <v>440885</v>
       </c>
       <c r="R32" t="n">
-        <v>6754046</v>
+        <v>6754148</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4277,7 +4277,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129543188</v>
+        <v>129543196</v>
       </c>
       <c r="B35" t="n">
         <v>8450</v>
@@ -4317,10 +4317,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440824</v>
+        <v>440716</v>
       </c>
       <c r="R35" t="n">
-        <v>6754063</v>
+        <v>6754046</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4389,10 +4389,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129543235</v>
+        <v>129539754</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>91574</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4400,34 +4400,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440863</v>
+        <v>440820</v>
       </c>
       <c r="R36" t="n">
-        <v>6754131</v>
+        <v>6754096</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4459,7 +4463,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4469,7 +4473,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4484,19 +4488,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129539754</v>
+        <v>129543159</v>
       </c>
       <c r="B37" t="n">
         <v>91574</v>
@@ -4524,21 +4528,17 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440820</v>
+        <v>440738</v>
       </c>
       <c r="R37" t="n">
-        <v>6754096</v>
+        <v>6754021</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4595,22 +4595,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129543159</v>
+        <v>129543235</v>
       </c>
       <c r="B38" t="n">
-        <v>91574</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4618,21 +4618,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4642,10 +4642,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440738</v>
+        <v>440863</v>
       </c>
       <c r="R38" t="n">
-        <v>6754021</v>
+        <v>6754131</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4714,10 +4714,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129539312</v>
+        <v>129539703</v>
       </c>
       <c r="B39" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4725,39 +4725,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440779</v>
+        <v>440820</v>
       </c>
       <c r="R39" t="n">
-        <v>6754008</v>
+        <v>6754096</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4826,10 +4821,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129539703</v>
+        <v>129539312</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4837,34 +4832,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440820</v>
+        <v>440779</v>
       </c>
       <c r="R40" t="n">
-        <v>6754096</v>
+        <v>6754008</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5152,7 +5152,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129538433</v>
+        <v>129539589</v>
       </c>
       <c r="B43" t="n">
         <v>8450</v>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440937</v>
+        <v>440769</v>
       </c>
       <c r="R43" t="n">
-        <v>6754141</v>
+        <v>6754064</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5264,7 +5264,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129539589</v>
+        <v>129538433</v>
       </c>
       <c r="B44" t="n">
         <v>8450</v>
@@ -5304,10 +5304,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440769</v>
+        <v>440937</v>
       </c>
       <c r="R44" t="n">
-        <v>6754064</v>
+        <v>6754141</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5376,7 +5376,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129539814</v>
+        <v>129543194</v>
       </c>
       <c r="B45" t="n">
         <v>8450</v>
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440861</v>
+        <v>440745</v>
       </c>
       <c r="R45" t="n">
-        <v>6754168</v>
+        <v>6754333</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5476,19 +5476,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129538170</v>
+        <v>129539814</v>
       </c>
       <c r="B46" t="n">
         <v>8450</v>
@@ -5519,7 +5519,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440982</v>
+        <v>440861</v>
       </c>
       <c r="R46" t="n">
-        <v>6754123</v>
+        <v>6754168</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5563,7 +5563,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5600,7 +5600,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129543194</v>
+        <v>129538170</v>
       </c>
       <c r="B47" t="n">
         <v>8450</v>
@@ -5631,7 +5631,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5640,10 +5640,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440745</v>
+        <v>440982</v>
       </c>
       <c r="R47" t="n">
-        <v>6754333</v>
+        <v>6754123</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5700,12 +5700,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6369,45 +6369,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129543230</v>
+        <v>129543185</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440779</v>
+        <v>440888</v>
       </c>
       <c r="R54" t="n">
-        <v>6754063</v>
+        <v>6754217</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6439,7 +6444,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6449,7 +6454,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6476,7 +6481,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129543185</v>
+        <v>129538256</v>
       </c>
       <c r="B55" t="n">
         <v>8450</v>
@@ -6507,7 +6512,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6516,10 +6521,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440888</v>
+        <v>440944</v>
       </c>
       <c r="R55" t="n">
-        <v>6754217</v>
+        <v>6754122</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6551,7 +6556,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6561,7 +6566,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6576,62 +6581,57 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129538256</v>
+        <v>129538554</v>
       </c>
       <c r="B56" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440944</v>
+        <v>440919</v>
       </c>
       <c r="R56" t="n">
-        <v>6754122</v>
+        <v>6754174</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6700,10 +6700,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129538554</v>
+        <v>129543230</v>
       </c>
       <c r="B57" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6711,21 +6711,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6735,10 +6735,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440919</v>
+        <v>440779</v>
       </c>
       <c r="R57" t="n">
-        <v>6754174</v>
+        <v>6754063</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6795,19 +6795,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129543213</v>
+        <v>129538786</v>
       </c>
       <c r="B58" t="n">
         <v>79044</v>
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440996</v>
+        <v>440918</v>
       </c>
       <c r="R58" t="n">
-        <v>6754160</v>
+        <v>6754126</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6902,22 +6902,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129543144</v>
+        <v>129543213</v>
       </c>
       <c r="B59" t="n">
-        <v>91476</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6925,21 +6925,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6949,10 +6949,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440718</v>
+        <v>440996</v>
       </c>
       <c r="R59" t="n">
-        <v>6754215</v>
+        <v>6754160</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7021,10 +7021,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129538786</v>
+        <v>129543144</v>
       </c>
       <c r="B60" t="n">
-        <v>79044</v>
+        <v>91476</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7032,21 +7032,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440918</v>
+        <v>440718</v>
       </c>
       <c r="R60" t="n">
-        <v>6754126</v>
+        <v>6754215</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7116,12 +7116,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7352,10 +7352,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129543157</v>
+        <v>129543245</v>
       </c>
       <c r="B63" t="n">
-        <v>57887</v>
+        <v>78710</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7363,39 +7363,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440759</v>
+        <v>440986</v>
       </c>
       <c r="R63" t="n">
-        <v>6754342</v>
+        <v>6754157</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7427,7 +7422,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7437,7 +7432,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7446,6 +7441,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7464,50 +7460,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129543179</v>
+        <v>129539371</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440821</v>
+        <v>440769</v>
       </c>
       <c r="R64" t="n">
-        <v>6754050</v>
+        <v>6754008</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7539,7 +7530,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7549,7 +7540,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7564,19 +7555,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129543176</v>
+        <v>129543179</v>
       </c>
       <c r="B65" t="n">
         <v>8450</v>
@@ -7607,7 +7598,7 @@
       <c r="I65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7616,10 +7607,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440820</v>
+        <v>440821</v>
       </c>
       <c r="R65" t="n">
-        <v>6754121</v>
+        <v>6754050</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7651,7 +7642,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7661,7 +7652,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7688,7 +7679,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129543192</v>
+        <v>129543176</v>
       </c>
       <c r="B66" t="n">
         <v>8450</v>
@@ -7719,7 +7710,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7728,10 +7719,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440742</v>
+        <v>440820</v>
       </c>
       <c r="R66" t="n">
-        <v>6754310</v>
+        <v>6754121</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7763,7 +7754,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7773,7 +7764,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7800,45 +7791,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129543245</v>
+        <v>129543192</v>
       </c>
       <c r="B67" t="n">
-        <v>78710</v>
+        <v>8450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>440986</v>
+        <v>440742</v>
       </c>
       <c r="R67" t="n">
-        <v>6754157</v>
+        <v>6754310</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7870,7 +7866,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7880,7 +7876,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7889,7 +7885,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7908,10 +7903,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129539371</v>
+        <v>129543157</v>
       </c>
       <c r="B68" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7919,34 +7914,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440769</v>
+        <v>440759</v>
       </c>
       <c r="R68" t="n">
-        <v>6754008</v>
+        <v>6754342</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8003,22 +8003,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129543218</v>
+        <v>129538247</v>
       </c>
       <c r="B69" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8026,34 +8026,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440888</v>
+        <v>440944</v>
       </c>
       <c r="R69" t="n">
-        <v>6754157</v>
+        <v>6754122</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8085,7 +8090,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8095,7 +8100,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8110,57 +8115,62 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129543224</v>
+        <v>129543178</v>
       </c>
       <c r="B70" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440774</v>
+        <v>440816</v>
       </c>
       <c r="R70" t="n">
-        <v>6754313</v>
+        <v>6754178</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8192,7 +8202,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8202,7 +8212,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8229,45 +8239,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129543225</v>
+        <v>129543199</v>
       </c>
       <c r="B71" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>440764</v>
+        <v>440855</v>
       </c>
       <c r="R71" t="n">
-        <v>6754320</v>
+        <v>6754166</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8299,7 +8314,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8309,7 +8324,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8336,10 +8351,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129538126</v>
+        <v>129543246</v>
       </c>
       <c r="B72" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8347,21 +8362,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8371,10 +8386,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>441002</v>
+        <v>440893</v>
       </c>
       <c r="R72" t="n">
-        <v>6754112</v>
+        <v>6754230</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8406,7 +8421,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8416,7 +8431,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8425,28 +8440,29 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129538247</v>
+        <v>129543141</v>
       </c>
       <c r="B73" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8454,39 +8470,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>440944</v>
+        <v>440974</v>
       </c>
       <c r="R73" t="n">
-        <v>6754122</v>
+        <v>6754141</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8518,7 +8529,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8528,7 +8539,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8543,22 +8554,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129543246</v>
+        <v>129543143</v>
       </c>
       <c r="B74" t="n">
-        <v>78710</v>
+        <v>79663</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8566,21 +8577,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8644,7 +8655,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8663,10 +8673,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129543141</v>
+        <v>129543225</v>
       </c>
       <c r="B75" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8674,21 +8684,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8698,10 +8708,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>440974</v>
+        <v>440764</v>
       </c>
       <c r="R75" t="n">
-        <v>6754141</v>
+        <v>6754320</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8733,7 +8743,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8743,7 +8753,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8770,10 +8780,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129543143</v>
+        <v>129543218</v>
       </c>
       <c r="B76" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8781,21 +8791,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8805,10 +8815,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>440893</v>
+        <v>440888</v>
       </c>
       <c r="R76" t="n">
-        <v>6754230</v>
+        <v>6754157</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8840,7 +8850,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8850,7 +8860,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8877,50 +8887,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129543199</v>
+        <v>129538126</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>440855</v>
+        <v>441002</v>
       </c>
       <c r="R77" t="n">
-        <v>6754166</v>
+        <v>6754112</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8952,7 +8957,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8962,7 +8967,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8977,62 +8982,57 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129543178</v>
+        <v>129543224</v>
       </c>
       <c r="B78" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>440816</v>
+        <v>440774</v>
       </c>
       <c r="R78" t="n">
-        <v>6754178</v>
+        <v>6754313</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9534,7 +9534,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129543173</v>
+        <v>129538573</v>
       </c>
       <c r="B83" t="n">
         <v>8450</v>
@@ -9574,10 +9574,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>440917</v>
+        <v>440932</v>
       </c>
       <c r="R83" t="n">
-        <v>6754255</v>
+        <v>6754178</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9634,19 +9634,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129538573</v>
+        <v>129543202</v>
       </c>
       <c r="B84" t="n">
         <v>8450</v>
@@ -9677,7 +9677,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>440932</v>
+        <v>440918</v>
       </c>
       <c r="R84" t="n">
-        <v>6754178</v>
+        <v>6754161</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9746,19 +9746,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129543203</v>
+        <v>129543173</v>
       </c>
       <c r="B85" t="n">
         <v>8450</v>
@@ -9789,7 +9789,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9798,10 +9798,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>440946</v>
+        <v>440917</v>
       </c>
       <c r="R85" t="n">
-        <v>6754123</v>
+        <v>6754255</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9870,10 +9870,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129543164</v>
+        <v>129543203</v>
       </c>
       <c r="B86" t="n">
-        <v>80178</v>
+        <v>8450</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9881,34 +9881,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6462</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>440708</v>
+        <v>440946</v>
       </c>
       <c r="R86" t="n">
-        <v>6754116</v>
+        <v>6754123</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9940,7 +9945,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9950,12 +9955,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9982,10 +9982,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129543202</v>
+        <v>129543164</v>
       </c>
       <c r="B87" t="n">
-        <v>8450</v>
+        <v>80178</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9993,39 +9993,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>6462</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>440918</v>
+        <v>440708</v>
       </c>
       <c r="R87" t="n">
-        <v>6754161</v>
+        <v>6754116</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10057,7 +10052,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10067,7 +10062,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10094,10 +10094,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129543171</v>
+        <v>129538198</v>
       </c>
       <c r="B88" t="n">
-        <v>91606</v>
+        <v>79044</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10105,21 +10105,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10129,10 +10129,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>440996</v>
+        <v>440969</v>
       </c>
       <c r="R88" t="n">
-        <v>6754160</v>
+        <v>6754129</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10189,19 +10189,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129538198</v>
+        <v>129543223</v>
       </c>
       <c r="B89" t="n">
         <v>79044</v>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>440969</v>
+        <v>440754</v>
       </c>
       <c r="R89" t="n">
-        <v>6754129</v>
+        <v>6754304</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10271,7 +10271,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10296,22 +10296,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129543223</v>
+        <v>129543171</v>
       </c>
       <c r="B90" t="n">
-        <v>79044</v>
+        <v>91606</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10319,21 +10319,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10343,10 +10343,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>440754</v>
+        <v>440996</v>
       </c>
       <c r="R90" t="n">
-        <v>6754304</v>
+        <v>6754160</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10378,7 +10378,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10522,10 +10522,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129543153</v>
+        <v>129543142</v>
       </c>
       <c r="B92" t="n">
-        <v>90585</v>
+        <v>79663</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10533,21 +10533,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10557,10 +10557,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>440976</v>
+        <v>440949</v>
       </c>
       <c r="R92" t="n">
-        <v>6754143</v>
+        <v>6754170</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10602,7 +10602,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10741,10 +10741,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129543142</v>
+        <v>129543153</v>
       </c>
       <c r="B94" t="n">
-        <v>79663</v>
+        <v>90585</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10752,21 +10752,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10776,10 +10776,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>440949</v>
+        <v>440976</v>
       </c>
       <c r="R94" t="n">
-        <v>6754170</v>
+        <v>6754143</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11169,10 +11169,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129543152</v>
+        <v>129543170</v>
       </c>
       <c r="B98" t="n">
-        <v>90585</v>
+        <v>57727</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11180,34 +11180,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>440718</v>
+        <v>440677</v>
       </c>
       <c r="R98" t="n">
-        <v>6754157</v>
+        <v>6754247</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11239,7 +11244,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11249,7 +11254,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11276,7 +11286,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129543189</v>
+        <v>129543174</v>
       </c>
       <c r="B99" t="n">
         <v>8450</v>
@@ -11307,7 +11317,7 @@
       <c r="I99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -11316,10 +11326,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>440793</v>
+        <v>440876</v>
       </c>
       <c r="R99" t="n">
-        <v>6754070</v>
+        <v>6754211</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11351,7 +11361,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11361,7 +11371,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11388,7 +11398,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129538851</v>
+        <v>129538483</v>
       </c>
       <c r="B100" t="n">
         <v>8450</v>
@@ -11428,10 +11438,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>440918</v>
+        <v>440916</v>
       </c>
       <c r="R100" t="n">
-        <v>6754126</v>
+        <v>6754159</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11500,38 +11510,38 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129543170</v>
+        <v>129543189</v>
       </c>
       <c r="B101" t="n">
-        <v>57727</v>
+        <v>8450</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -11540,10 +11550,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>440677</v>
+        <v>440793</v>
       </c>
       <c r="R101" t="n">
-        <v>6754247</v>
+        <v>6754070</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11575,7 +11585,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11585,12 +11595,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11617,7 +11622,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129538483</v>
+        <v>129538851</v>
       </c>
       <c r="B102" t="n">
         <v>8450</v>
@@ -11657,10 +11662,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>440916</v>
+        <v>440918</v>
       </c>
       <c r="R102" t="n">
-        <v>6754159</v>
+        <v>6754126</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11729,50 +11734,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129543174</v>
+        <v>129543152</v>
       </c>
       <c r="B103" t="n">
-        <v>8450</v>
+        <v>90585</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>1962</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>440876</v>
+        <v>440718</v>
       </c>
       <c r="R103" t="n">
-        <v>6754211</v>
+        <v>6754157</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11949,10 +11949,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129543217</v>
+        <v>129538156</v>
       </c>
       <c r="B105" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11960,34 +11960,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>440902</v>
+        <v>440982</v>
       </c>
       <c r="R105" t="n">
-        <v>6754164</v>
+        <v>6754123</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12019,7 +12024,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12029,7 +12034,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12044,19 +12049,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129538088</v>
+        <v>129543217</v>
       </c>
       <c r="B106" t="n">
         <v>79044</v>
@@ -12091,10 +12096,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>441007</v>
+        <v>440902</v>
       </c>
       <c r="R106" t="n">
-        <v>6754124</v>
+        <v>6754164</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12126,7 +12131,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12136,7 +12141,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12151,22 +12156,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129538156</v>
+        <v>129538088</v>
       </c>
       <c r="B107" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12174,39 +12179,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>440982</v>
+        <v>441007</v>
       </c>
       <c r="R107" t="n">
-        <v>6754123</v>
+        <v>6754124</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 45199-2025 artfynd.xlsx
+++ b/artfynd/A 45199-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129539829</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129543238</v>
       </c>
       <c r="B4" t="n">
-        <v>91826</v>
+        <v>91854</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129543158</v>
+        <v>129543240</v>
       </c>
       <c r="B5" t="n">
-        <v>91574</v>
+        <v>78736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440892</v>
+        <v>440736</v>
       </c>
       <c r="R5" t="n">
-        <v>6754225</v>
+        <v>6754282</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,6 +1090,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1108,32 +1109,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129539852</v>
+        <v>129543168</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>92867</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440880</v>
+        <v>440718</v>
       </c>
       <c r="R6" t="n">
-        <v>6754175</v>
+        <v>6754157</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1179,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1189,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,44 +1204,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129539462</v>
+        <v>129543239</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>80110</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440787</v>
+        <v>440708</v>
       </c>
       <c r="R7" t="n">
-        <v>6753947</v>
+        <v>6754116</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1286,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1296,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,22 +1316,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129543240</v>
+        <v>129543147</v>
       </c>
       <c r="B8" t="n">
-        <v>78710</v>
+        <v>79689</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,21 +1339,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440736</v>
+        <v>440701</v>
       </c>
       <c r="R8" t="n">
-        <v>6754282</v>
+        <v>6754185</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1398,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,7 +1408,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,7 +1417,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1430,32 +1435,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129543168</v>
+        <v>129539852</v>
       </c>
       <c r="B9" t="n">
-        <v>92839</v>
+        <v>79070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1465,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440718</v>
+        <v>440880</v>
       </c>
       <c r="R9" t="n">
-        <v>6754157</v>
+        <v>6754175</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,7 +1505,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1510,7 +1515,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1525,44 +1530,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129543239</v>
+        <v>129539462</v>
       </c>
       <c r="B10" t="n">
-        <v>80084</v>
+        <v>79070</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1572,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440708</v>
+        <v>440787</v>
       </c>
       <c r="R10" t="n">
-        <v>6754116</v>
+        <v>6753947</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,7 +1612,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1617,12 +1622,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1637,22 +1637,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543147</v>
+        <v>129543158</v>
       </c>
       <c r="B11" t="n">
-        <v>79663</v>
+        <v>91602</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,21 +1660,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440701</v>
+        <v>440892</v>
       </c>
       <c r="R11" t="n">
-        <v>6754185</v>
+        <v>6754225</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2092,10 +2092,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129543216</v>
+        <v>129543227</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440945</v>
+        <v>440744</v>
       </c>
       <c r="R15" t="n">
-        <v>6754252</v>
+        <v>6754336</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2199,10 +2199,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129543227</v>
+        <v>129543216</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440744</v>
+        <v>440945</v>
       </c>
       <c r="R16" t="n">
-        <v>6754336</v>
+        <v>6754252</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2528,7 +2528,7 @@
         <v>129543219</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129538675</v>
+        <v>129538905</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2643,34 +2643,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440902</v>
+        <v>440970</v>
       </c>
       <c r="R20" t="n">
-        <v>6754135</v>
+        <v>6754114</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,10 +2744,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129538905</v>
+        <v>129538675</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>79070</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2750,39 +2755,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440970</v>
+        <v>440902</v>
       </c>
       <c r="R21" t="n">
-        <v>6754114</v>
+        <v>6754135</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3075,10 +3075,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129543234</v>
+        <v>129538680</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3086,34 +3086,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440834</v>
+        <v>440918</v>
       </c>
       <c r="R24" t="n">
-        <v>6754152</v>
+        <v>6754126</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3145,7 +3150,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3155,7 +3160,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3170,22 +3175,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129539521</v>
+        <v>129543234</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3217,10 +3222,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440725</v>
+        <v>440834</v>
       </c>
       <c r="R25" t="n">
-        <v>6754011</v>
+        <v>6754152</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3252,7 +3257,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3262,7 +3267,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3277,22 +3282,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129543228</v>
+        <v>129539521</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3324,10 +3329,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440716</v>
+        <v>440725</v>
       </c>
       <c r="R26" t="n">
-        <v>6754354</v>
+        <v>6754011</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3359,7 +3364,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3369,7 +3374,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3384,22 +3389,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543229</v>
+        <v>129543228</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3431,10 +3436,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440638</v>
+        <v>440716</v>
       </c>
       <c r="R27" t="n">
-        <v>6754239</v>
+        <v>6754354</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3466,7 +3471,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3476,7 +3481,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3503,10 +3508,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129538680</v>
+        <v>129543229</v>
       </c>
       <c r="B28" t="n">
-        <v>57724</v>
+        <v>79070</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3514,39 +3519,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440918</v>
+        <v>440638</v>
       </c>
       <c r="R28" t="n">
-        <v>6754126</v>
+        <v>6754239</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3603,22 +3603,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543222</v>
+        <v>129543233</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440728</v>
+        <v>440819</v>
       </c>
       <c r="R29" t="n">
-        <v>6754306</v>
+        <v>6754114</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3722,10 +3722,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129543233</v>
+        <v>129543222</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440819</v>
+        <v>440728</v>
       </c>
       <c r="R30" t="n">
-        <v>6754114</v>
+        <v>6754306</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4389,10 +4389,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129539754</v>
+        <v>129543235</v>
       </c>
       <c r="B36" t="n">
-        <v>91574</v>
+        <v>79070</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4400,38 +4400,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440820</v>
+        <v>440863</v>
       </c>
       <c r="R36" t="n">
-        <v>6754096</v>
+        <v>6754131</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4463,7 +4459,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4473,7 +4469,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4488,22 +4484,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129543159</v>
+        <v>129539703</v>
       </c>
       <c r="B37" t="n">
-        <v>91574</v>
+        <v>79070</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4511,21 +4507,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4535,10 +4531,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440738</v>
+        <v>440820</v>
       </c>
       <c r="R37" t="n">
-        <v>6754021</v>
+        <v>6754096</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4570,7 +4566,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4580,7 +4576,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4595,22 +4591,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129543235</v>
+        <v>129539754</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>91602</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4618,34 +4614,38 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440863</v>
+        <v>440820</v>
       </c>
       <c r="R38" t="n">
-        <v>6754131</v>
+        <v>6754096</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4702,22 +4702,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129539703</v>
+        <v>129543159</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>91602</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4725,21 +4725,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440820</v>
+        <v>440738</v>
       </c>
       <c r="R39" t="n">
-        <v>6754096</v>
+        <v>6754021</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4809,12 +4809,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4824,7 +4824,7 @@
         <v>129539312</v>
       </c>
       <c r="B40" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5045,45 +5045,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129543145</v>
+        <v>129539589</v>
       </c>
       <c r="B42" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440723</v>
+        <v>440769</v>
       </c>
       <c r="R42" t="n">
-        <v>6754344</v>
+        <v>6754064</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5115,7 +5120,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5125,7 +5130,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5140,19 +5145,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129539589</v>
+        <v>129538433</v>
       </c>
       <c r="B43" t="n">
         <v>8450</v>
@@ -5192,10 +5197,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440769</v>
+        <v>440937</v>
       </c>
       <c r="R43" t="n">
-        <v>6754064</v>
+        <v>6754141</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5227,7 +5232,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5237,7 +5242,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5264,50 +5269,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129538433</v>
+        <v>129543145</v>
       </c>
       <c r="B44" t="n">
-        <v>8450</v>
+        <v>79102</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440937</v>
+        <v>440723</v>
       </c>
       <c r="R44" t="n">
-        <v>6754141</v>
+        <v>6754344</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5364,62 +5364,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129543194</v>
+        <v>129543226</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>79070</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440745</v>
+        <v>440757</v>
       </c>
       <c r="R45" t="n">
-        <v>6754333</v>
+        <v>6754337</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5451,7 +5446,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5461,7 +5456,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5488,7 +5483,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129539814</v>
+        <v>129543194</v>
       </c>
       <c r="B46" t="n">
         <v>8450</v>
@@ -5528,10 +5523,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440861</v>
+        <v>440745</v>
       </c>
       <c r="R46" t="n">
-        <v>6754168</v>
+        <v>6754333</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5563,7 +5558,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5573,7 +5568,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5588,12 +5583,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5712,45 +5707,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129543226</v>
+        <v>129539814</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440757</v>
+        <v>440861</v>
       </c>
       <c r="R48" t="n">
-        <v>6754337</v>
+        <v>6754168</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5807,12 +5807,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5822,7 +5822,7 @@
         <v>129543220</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>129543236</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>129539404</v>
       </c>
       <c r="B51" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6145,38 +6145,38 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129543166</v>
+        <v>129543198</v>
       </c>
       <c r="B52" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440772</v>
+        <v>440824</v>
       </c>
       <c r="R52" t="n">
-        <v>6754089</v>
+        <v>6754177</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6257,38 +6257,38 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129543198</v>
+        <v>129543166</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6297,10 +6297,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440824</v>
+        <v>440772</v>
       </c>
       <c r="R53" t="n">
-        <v>6754177</v>
+        <v>6754089</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6369,50 +6369,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129543185</v>
+        <v>129543230</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>79070</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440888</v>
+        <v>440779</v>
       </c>
       <c r="R54" t="n">
-        <v>6754217</v>
+        <v>6754063</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6444,7 +6439,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6454,7 +6449,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6481,50 +6476,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129538256</v>
+        <v>129538554</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>79689</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440944</v>
+        <v>440919</v>
       </c>
       <c r="R55" t="n">
-        <v>6754122</v>
+        <v>6754174</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6593,45 +6583,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129538554</v>
+        <v>129543185</v>
       </c>
       <c r="B56" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440919</v>
+        <v>440888</v>
       </c>
       <c r="R56" t="n">
-        <v>6754174</v>
+        <v>6754217</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6663,7 +6658,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6673,7 +6668,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6688,57 +6683,62 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129543230</v>
+        <v>129538256</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440779</v>
+        <v>440944</v>
       </c>
       <c r="R57" t="n">
-        <v>6754063</v>
+        <v>6754122</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6795,12 +6795,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6810,7 +6810,7 @@
         <v>129538786</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6914,10 +6914,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129543213</v>
+        <v>129543144</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>91504</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6925,21 +6925,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6949,10 +6949,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440996</v>
+        <v>440718</v>
       </c>
       <c r="R59" t="n">
-        <v>6754160</v>
+        <v>6754215</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7021,10 +7021,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129543144</v>
+        <v>129543213</v>
       </c>
       <c r="B60" t="n">
-        <v>91476</v>
+        <v>79070</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7032,21 +7032,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440718</v>
+        <v>440996</v>
       </c>
       <c r="R60" t="n">
-        <v>6754215</v>
+        <v>6754160</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7355,7 +7355,7 @@
         <v>129543245</v>
       </c>
       <c r="B63" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>129539371</v>
       </c>
       <c r="B64" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7567,38 +7567,38 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129543179</v>
+        <v>129543157</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>57890</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7607,10 +7607,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440821</v>
+        <v>440759</v>
       </c>
       <c r="R65" t="n">
-        <v>6754050</v>
+        <v>6754342</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7679,7 +7679,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129543176</v>
+        <v>129543179</v>
       </c>
       <c r="B66" t="n">
         <v>8450</v>
@@ -7710,7 +7710,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440820</v>
+        <v>440821</v>
       </c>
       <c r="R66" t="n">
-        <v>6754121</v>
+        <v>6754050</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7791,7 +7791,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129543192</v>
+        <v>129543176</v>
       </c>
       <c r="B67" t="n">
         <v>8450</v>
@@ -7822,7 +7822,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>440742</v>
+        <v>440820</v>
       </c>
       <c r="R67" t="n">
-        <v>6754310</v>
+        <v>6754121</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7903,38 +7903,38 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129543157</v>
+        <v>129543192</v>
       </c>
       <c r="B68" t="n">
-        <v>57887</v>
+        <v>8450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7943,10 +7943,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440759</v>
+        <v>440742</v>
       </c>
       <c r="R68" t="n">
-        <v>6754342</v>
+        <v>6754310</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8015,10 +8015,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129538247</v>
+        <v>129543246</v>
       </c>
       <c r="B69" t="n">
-        <v>57724</v>
+        <v>78736</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8026,39 +8026,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440944</v>
+        <v>440893</v>
       </c>
       <c r="R69" t="n">
-        <v>6754122</v>
+        <v>6754230</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8090,7 +8085,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8100,7 +8095,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8109,68 +8104,64 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129543178</v>
+        <v>129543218</v>
       </c>
       <c r="B70" t="n">
-        <v>8450</v>
+        <v>79070</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440816</v>
+        <v>440888</v>
       </c>
       <c r="R70" t="n">
-        <v>6754178</v>
+        <v>6754157</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8202,7 +8193,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8212,7 +8203,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8239,38 +8230,38 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129543199</v>
+        <v>129538247</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>57727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8279,10 +8270,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>440855</v>
+        <v>440944</v>
       </c>
       <c r="R71" t="n">
-        <v>6754166</v>
+        <v>6754122</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8314,7 +8305,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8324,7 +8315,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8339,22 +8330,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129543246</v>
+        <v>129543141</v>
       </c>
       <c r="B72" t="n">
-        <v>78710</v>
+        <v>79689</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8362,21 +8353,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8386,10 +8377,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>440893</v>
+        <v>440974</v>
       </c>
       <c r="R72" t="n">
-        <v>6754230</v>
+        <v>6754141</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8421,7 +8412,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8431,7 +8422,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8440,7 +8431,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8459,10 +8449,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129543141</v>
+        <v>129543225</v>
       </c>
       <c r="B73" t="n">
-        <v>79663</v>
+        <v>79070</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8470,21 +8460,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8494,10 +8484,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>440974</v>
+        <v>440764</v>
       </c>
       <c r="R73" t="n">
-        <v>6754141</v>
+        <v>6754320</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8529,7 +8519,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8539,7 +8529,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8566,10 +8556,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129543143</v>
+        <v>129538126</v>
       </c>
       <c r="B74" t="n">
-        <v>79663</v>
+        <v>79070</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8577,21 +8567,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8601,10 +8591,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>440893</v>
+        <v>441002</v>
       </c>
       <c r="R74" t="n">
-        <v>6754230</v>
+        <v>6754112</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8636,7 +8626,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8646,7 +8636,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8661,22 +8651,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129543225</v>
+        <v>129543143</v>
       </c>
       <c r="B75" t="n">
-        <v>79044</v>
+        <v>79689</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8684,21 +8674,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8708,10 +8698,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>440764</v>
+        <v>440893</v>
       </c>
       <c r="R75" t="n">
-        <v>6754320</v>
+        <v>6754230</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8743,7 +8733,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8753,7 +8743,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8780,10 +8770,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129543218</v>
+        <v>129543224</v>
       </c>
       <c r="B76" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8815,10 +8805,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>440888</v>
+        <v>440774</v>
       </c>
       <c r="R76" t="n">
-        <v>6754157</v>
+        <v>6754313</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8850,7 +8840,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8860,7 +8850,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8887,45 +8877,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129538126</v>
+        <v>129543178</v>
       </c>
       <c r="B77" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>441002</v>
+        <v>440816</v>
       </c>
       <c r="R77" t="n">
-        <v>6754112</v>
+        <v>6754178</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8957,7 +8952,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8967,7 +8962,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8982,57 +8977,62 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129543224</v>
+        <v>129543199</v>
       </c>
       <c r="B78" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>440774</v>
+        <v>440855</v>
       </c>
       <c r="R78" t="n">
-        <v>6754313</v>
+        <v>6754166</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9101,32 +9101,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129543154</v>
+        <v>129543164</v>
       </c>
       <c r="B79" t="n">
-        <v>90585</v>
+        <v>80204</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1962</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9136,10 +9136,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>440770</v>
+        <v>440708</v>
       </c>
       <c r="R79" t="n">
-        <v>6754101</v>
+        <v>6754116</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9171,7 +9171,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9181,7 +9181,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9208,10 +9213,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129543215</v>
+        <v>129543154</v>
       </c>
       <c r="B80" t="n">
-        <v>79044</v>
+        <v>90613</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9219,21 +9224,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9243,10 +9248,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>440930</v>
+        <v>440770</v>
       </c>
       <c r="R80" t="n">
-        <v>6754182</v>
+        <v>6754101</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9278,7 +9283,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9288,7 +9293,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9318,7 +9323,7 @@
         <v>129543221</v>
       </c>
       <c r="B81" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9425,7 +9430,7 @@
         <v>129543155</v>
       </c>
       <c r="B82" t="n">
-        <v>56917</v>
+        <v>56920</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9534,50 +9539,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129538573</v>
+        <v>129543215</v>
       </c>
       <c r="B83" t="n">
-        <v>8450</v>
+        <v>79070</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>440932</v>
+        <v>440930</v>
       </c>
       <c r="R83" t="n">
-        <v>6754178</v>
+        <v>6754182</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9634,19 +9634,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129543202</v>
+        <v>129538573</v>
       </c>
       <c r="B84" t="n">
         <v>8450</v>
@@ -9677,7 +9677,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>440918</v>
+        <v>440932</v>
       </c>
       <c r="R84" t="n">
-        <v>6754161</v>
+        <v>6754178</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9746,19 +9746,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129543173</v>
+        <v>129543202</v>
       </c>
       <c r="B85" t="n">
         <v>8450</v>
@@ -9789,7 +9789,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9798,10 +9798,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>440917</v>
+        <v>440918</v>
       </c>
       <c r="R85" t="n">
-        <v>6754255</v>
+        <v>6754161</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9870,7 +9870,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129543203</v>
+        <v>129543173</v>
       </c>
       <c r="B86" t="n">
         <v>8450</v>
@@ -9901,7 +9901,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9910,10 +9910,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>440946</v>
+        <v>440917</v>
       </c>
       <c r="R86" t="n">
-        <v>6754123</v>
+        <v>6754255</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9982,10 +9982,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129543164</v>
+        <v>129543203</v>
       </c>
       <c r="B87" t="n">
-        <v>80178</v>
+        <v>8450</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9993,34 +9993,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6462</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>440708</v>
+        <v>440946</v>
       </c>
       <c r="R87" t="n">
-        <v>6754116</v>
+        <v>6754123</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10052,7 +10057,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10062,12 +10067,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10094,10 +10094,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129538198</v>
+        <v>129543171</v>
       </c>
       <c r="B88" t="n">
-        <v>79044</v>
+        <v>91634</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10105,21 +10105,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10129,10 +10129,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>440969</v>
+        <v>440996</v>
       </c>
       <c r="R88" t="n">
-        <v>6754129</v>
+        <v>6754160</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10189,22 +10189,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129543223</v>
+        <v>129538198</v>
       </c>
       <c r="B89" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>440754</v>
+        <v>440969</v>
       </c>
       <c r="R89" t="n">
-        <v>6754304</v>
+        <v>6754129</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10271,7 +10271,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10296,22 +10296,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129543171</v>
+        <v>129543223</v>
       </c>
       <c r="B90" t="n">
-        <v>91606</v>
+        <v>79070</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10319,21 +10319,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10343,10 +10343,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>440996</v>
+        <v>440754</v>
       </c>
       <c r="R90" t="n">
-        <v>6754160</v>
+        <v>6754304</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10378,7 +10378,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10418,7 +10418,7 @@
         <v>129538100</v>
       </c>
       <c r="B91" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10522,10 +10522,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129543142</v>
+        <v>129543153</v>
       </c>
       <c r="B92" t="n">
-        <v>79663</v>
+        <v>90613</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10533,21 +10533,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10557,10 +10557,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>440949</v>
+        <v>440976</v>
       </c>
       <c r="R92" t="n">
-        <v>6754170</v>
+        <v>6754143</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10602,7 +10602,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10629,50 +10629,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129543175</v>
+        <v>129543142</v>
       </c>
       <c r="B93" t="n">
-        <v>8450</v>
+        <v>79689</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>440896</v>
+        <v>440949</v>
       </c>
       <c r="R93" t="n">
-        <v>6754124</v>
+        <v>6754170</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10704,7 +10699,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10714,7 +10709,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10741,45 +10736,50 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129543153</v>
+        <v>129543175</v>
       </c>
       <c r="B94" t="n">
-        <v>90585</v>
+        <v>8450</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>440976</v>
+        <v>440896</v>
       </c>
       <c r="R94" t="n">
-        <v>6754143</v>
+        <v>6754124</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10848,10 +10848,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129543231</v>
+        <v>129543232</v>
       </c>
       <c r="B95" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10883,10 +10883,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>440769</v>
+        <v>440798</v>
       </c>
       <c r="R95" t="n">
-        <v>6754066</v>
+        <v>6754119</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10918,7 +10918,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10928,7 +10928,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10955,10 +10955,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129543232</v>
+        <v>129543214</v>
       </c>
       <c r="B96" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10990,10 +10990,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>440798</v>
+        <v>440948</v>
       </c>
       <c r="R96" t="n">
-        <v>6754119</v>
+        <v>6754156</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11062,10 +11062,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129543214</v>
+        <v>129543231</v>
       </c>
       <c r="B97" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11097,10 +11097,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>440948</v>
+        <v>440769</v>
       </c>
       <c r="R97" t="n">
-        <v>6754156</v>
+        <v>6754066</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11132,7 +11132,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11169,10 +11169,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129543170</v>
+        <v>129543152</v>
       </c>
       <c r="B98" t="n">
-        <v>57727</v>
+        <v>90613</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11180,39 +11180,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>440677</v>
+        <v>440718</v>
       </c>
       <c r="R98" t="n">
-        <v>6754247</v>
+        <v>6754157</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11244,7 +11239,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11254,12 +11249,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11286,38 +11276,38 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129543174</v>
+        <v>129543170</v>
       </c>
       <c r="B99" t="n">
-        <v>8450</v>
+        <v>57730</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -11326,10 +11316,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>440876</v>
+        <v>440677</v>
       </c>
       <c r="R99" t="n">
-        <v>6754211</v>
+        <v>6754247</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11361,7 +11351,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11371,7 +11361,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11510,7 +11505,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129543189</v>
+        <v>129543174</v>
       </c>
       <c r="B101" t="n">
         <v>8450</v>
@@ -11541,7 +11536,7 @@
       <c r="I101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -11550,10 +11545,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>440793</v>
+        <v>440876</v>
       </c>
       <c r="R101" t="n">
-        <v>6754070</v>
+        <v>6754211</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11585,7 +11580,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11595,7 +11590,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11734,45 +11729,50 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129543152</v>
+        <v>129543189</v>
       </c>
       <c r="B103" t="n">
-        <v>90585</v>
+        <v>8450</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>440718</v>
+        <v>440793</v>
       </c>
       <c r="R103" t="n">
-        <v>6754157</v>
+        <v>6754070</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11841,10 +11841,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129543247</v>
+        <v>129538156</v>
       </c>
       <c r="B104" t="n">
-        <v>78710</v>
+        <v>57727</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11852,34 +11852,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>440894</v>
+        <v>440982</v>
       </c>
       <c r="R104" t="n">
-        <v>6754104</v>
+        <v>6754123</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11911,7 +11916,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11921,7 +11926,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11930,29 +11935,28 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129538156</v>
+        <v>129543247</v>
       </c>
       <c r="B105" t="n">
-        <v>57724</v>
+        <v>78736</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11960,39 +11964,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>440982</v>
+        <v>440894</v>
       </c>
       <c r="R105" t="n">
-        <v>6754123</v>
+        <v>6754104</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12024,7 +12023,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12034,7 +12033,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12043,18 +12042,19 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -12064,7 +12064,7 @@
         <v>129543217</v>
       </c>
       <c r="B106" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
         <v>129538088</v>
       </c>
       <c r="B107" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 45199-2025 artfynd.xlsx
+++ b/artfynd/A 45199-2025 artfynd.xlsx
@@ -2632,38 +2632,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129538905</v>
+        <v>129543195</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440970</v>
+        <v>440708</v>
       </c>
       <c r="R20" t="n">
-        <v>6754114</v>
+        <v>6754371</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2732,57 +2732,62 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129538675</v>
+        <v>129539529</v>
       </c>
       <c r="B21" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440902</v>
+        <v>440725</v>
       </c>
       <c r="R21" t="n">
-        <v>6754135</v>
+        <v>6754011</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2814,7 +2819,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2824,7 +2829,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2851,38 +2856,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129543195</v>
+        <v>129538905</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2891,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440708</v>
+        <v>440970</v>
       </c>
       <c r="R22" t="n">
-        <v>6754371</v>
+        <v>6754114</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2926,7 +2931,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2936,7 +2941,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2951,62 +2956,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129539529</v>
+        <v>129538675</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79070</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440725</v>
+        <v>440902</v>
       </c>
       <c r="R23" t="n">
-        <v>6754011</v>
+        <v>6754135</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3615,7 +3615,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543233</v>
+        <v>129543222</v>
       </c>
       <c r="B29" t="n">
         <v>79070</v>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440819</v>
+        <v>440728</v>
       </c>
       <c r="R29" t="n">
-        <v>6754114</v>
+        <v>6754306</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3722,7 +3722,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129543222</v>
+        <v>129543233</v>
       </c>
       <c r="B30" t="n">
         <v>79070</v>
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440728</v>
+        <v>440819</v>
       </c>
       <c r="R30" t="n">
-        <v>6754306</v>
+        <v>6754114</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4821,38 +4821,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129539312</v>
+        <v>129543190</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440779</v>
+        <v>440773</v>
       </c>
       <c r="R40" t="n">
-        <v>6754008</v>
+        <v>6754088</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4921,50 +4921,50 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129543190</v>
+        <v>129539312</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440773</v>
+        <v>440779</v>
       </c>
       <c r="R41" t="n">
-        <v>6754088</v>
+        <v>6754008</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5033,12 +5033,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -6369,45 +6369,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129543230</v>
+        <v>129543185</v>
       </c>
       <c r="B54" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440779</v>
+        <v>440888</v>
       </c>
       <c r="R54" t="n">
-        <v>6754063</v>
+        <v>6754217</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6439,7 +6444,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6449,7 +6454,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6476,45 +6481,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129538554</v>
+        <v>129538256</v>
       </c>
       <c r="B55" t="n">
-        <v>79689</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440919</v>
+        <v>440944</v>
       </c>
       <c r="R55" t="n">
-        <v>6754174</v>
+        <v>6754122</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6583,50 +6593,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129543185</v>
+        <v>129543230</v>
       </c>
       <c r="B56" t="n">
-        <v>8450</v>
+        <v>79070</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440888</v>
+        <v>440779</v>
       </c>
       <c r="R56" t="n">
-        <v>6754217</v>
+        <v>6754063</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6658,7 +6663,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6668,7 +6673,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6695,50 +6700,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129538256</v>
+        <v>129538554</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>79689</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440944</v>
+        <v>440919</v>
       </c>
       <c r="R57" t="n">
-        <v>6754122</v>
+        <v>6754174</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6807,10 +6807,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129538786</v>
+        <v>129543144</v>
       </c>
       <c r="B58" t="n">
-        <v>79070</v>
+        <v>91504</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6818,21 +6818,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440918</v>
+        <v>440718</v>
       </c>
       <c r="R58" t="n">
-        <v>6754126</v>
+        <v>6754215</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6902,22 +6902,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129543144</v>
+        <v>129543213</v>
       </c>
       <c r="B59" t="n">
-        <v>91504</v>
+        <v>79070</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6925,21 +6925,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6949,10 +6949,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440718</v>
+        <v>440996</v>
       </c>
       <c r="R59" t="n">
-        <v>6754215</v>
+        <v>6754160</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7021,7 +7021,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129543213</v>
+        <v>129538786</v>
       </c>
       <c r="B60" t="n">
         <v>79070</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440996</v>
+        <v>440918</v>
       </c>
       <c r="R60" t="n">
-        <v>6754160</v>
+        <v>6754126</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7116,12 +7116,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7352,10 +7352,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129543245</v>
+        <v>129543157</v>
       </c>
       <c r="B63" t="n">
-        <v>78736</v>
+        <v>57890</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7363,34 +7363,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440986</v>
+        <v>440759</v>
       </c>
       <c r="R63" t="n">
-        <v>6754157</v>
+        <v>6754342</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7422,7 +7427,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7432,7 +7437,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7441,7 +7446,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7460,45 +7464,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129539371</v>
+        <v>129543179</v>
       </c>
       <c r="B64" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440769</v>
+        <v>440821</v>
       </c>
       <c r="R64" t="n">
-        <v>6754008</v>
+        <v>6754050</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7530,7 +7539,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7540,7 +7549,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7555,50 +7564,50 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129543157</v>
+        <v>129543176</v>
       </c>
       <c r="B65" t="n">
-        <v>57890</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7607,10 +7616,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440759</v>
+        <v>440820</v>
       </c>
       <c r="R65" t="n">
-        <v>6754342</v>
+        <v>6754121</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7642,7 +7651,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7652,7 +7661,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7679,7 +7688,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129543179</v>
+        <v>129543192</v>
       </c>
       <c r="B66" t="n">
         <v>8450</v>
@@ -7719,10 +7728,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440821</v>
+        <v>440742</v>
       </c>
       <c r="R66" t="n">
-        <v>6754050</v>
+        <v>6754310</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7754,7 +7763,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7764,7 +7773,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7791,50 +7800,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129543176</v>
+        <v>129539371</v>
       </c>
       <c r="B67" t="n">
-        <v>8450</v>
+        <v>79070</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>440820</v>
+        <v>440769</v>
       </c>
       <c r="R67" t="n">
-        <v>6754121</v>
+        <v>6754008</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7866,7 +7870,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7876,7 +7880,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7891,62 +7895,57 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129543192</v>
+        <v>129543245</v>
       </c>
       <c r="B68" t="n">
-        <v>8450</v>
+        <v>78736</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440742</v>
+        <v>440986</v>
       </c>
       <c r="R68" t="n">
-        <v>6754310</v>
+        <v>6754157</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7978,7 +7977,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7988,7 +7987,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7997,6 +7996,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8015,10 +8015,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129543246</v>
+        <v>129543141</v>
       </c>
       <c r="B69" t="n">
-        <v>78736</v>
+        <v>79689</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8026,21 +8026,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8050,10 +8050,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440893</v>
+        <v>440974</v>
       </c>
       <c r="R69" t="n">
-        <v>6754230</v>
+        <v>6754141</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8104,7 +8104,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8123,7 +8122,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129543218</v>
+        <v>129543225</v>
       </c>
       <c r="B70" t="n">
         <v>79070</v>
@@ -8158,10 +8157,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440888</v>
+        <v>440764</v>
       </c>
       <c r="R70" t="n">
-        <v>6754157</v>
+        <v>6754320</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8193,7 +8192,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8203,7 +8202,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8230,10 +8229,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129538247</v>
+        <v>129538126</v>
       </c>
       <c r="B71" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8241,39 +8240,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>440944</v>
+        <v>441002</v>
       </c>
       <c r="R71" t="n">
-        <v>6754122</v>
+        <v>6754112</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8342,7 +8336,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129543141</v>
+        <v>129543143</v>
       </c>
       <c r="B72" t="n">
         <v>79689</v>
@@ -8377,10 +8371,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>440974</v>
+        <v>440893</v>
       </c>
       <c r="R72" t="n">
-        <v>6754141</v>
+        <v>6754230</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8412,7 +8406,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8422,7 +8416,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8449,7 +8443,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129543225</v>
+        <v>129543224</v>
       </c>
       <c r="B73" t="n">
         <v>79070</v>
@@ -8484,10 +8478,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>440764</v>
+        <v>440774</v>
       </c>
       <c r="R73" t="n">
-        <v>6754320</v>
+        <v>6754313</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8556,10 +8550,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129538126</v>
+        <v>129543246</v>
       </c>
       <c r="B74" t="n">
-        <v>79070</v>
+        <v>78736</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8567,21 +8561,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8591,10 +8585,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>441002</v>
+        <v>440893</v>
       </c>
       <c r="R74" t="n">
-        <v>6754112</v>
+        <v>6754230</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8626,7 +8620,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8636,7 +8630,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8645,28 +8639,29 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129543143</v>
+        <v>129543218</v>
       </c>
       <c r="B75" t="n">
-        <v>79689</v>
+        <v>79070</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8674,21 +8669,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8698,10 +8693,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>440893</v>
+        <v>440888</v>
       </c>
       <c r="R75" t="n">
-        <v>6754230</v>
+        <v>6754157</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8733,7 +8728,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8743,7 +8738,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8770,10 +8765,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129543224</v>
+        <v>129538247</v>
       </c>
       <c r="B76" t="n">
-        <v>79070</v>
+        <v>57727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8781,34 +8776,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>440774</v>
+        <v>440944</v>
       </c>
       <c r="R76" t="n">
-        <v>6754313</v>
+        <v>6754122</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8865,12 +8865,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9101,10 +9101,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129543164</v>
+        <v>129538573</v>
       </c>
       <c r="B79" t="n">
-        <v>80204</v>
+        <v>8450</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9112,34 +9112,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>440708</v>
+        <v>440932</v>
       </c>
       <c r="R79" t="n">
-        <v>6754116</v>
+        <v>6754178</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9171,7 +9176,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9181,12 +9186,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9201,57 +9201,62 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129543154</v>
+        <v>129543173</v>
       </c>
       <c r="B80" t="n">
-        <v>90613</v>
+        <v>8450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>440770</v>
+        <v>440917</v>
       </c>
       <c r="R80" t="n">
-        <v>6754101</v>
+        <v>6754255</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9283,7 +9288,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9293,7 +9298,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9320,45 +9325,50 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129543221</v>
+        <v>129543203</v>
       </c>
       <c r="B81" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>440739</v>
+        <v>440946</v>
       </c>
       <c r="R81" t="n">
-        <v>6754147</v>
+        <v>6754123</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9390,7 +9400,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9400,7 +9410,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9427,10 +9437,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129543155</v>
+        <v>129543202</v>
       </c>
       <c r="B82" t="n">
-        <v>56920</v>
+        <v>8450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9438,27 +9448,27 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9467,10 +9477,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>440878</v>
+        <v>440918</v>
       </c>
       <c r="R82" t="n">
-        <v>6754126</v>
+        <v>6754161</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9502,7 +9512,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9512,7 +9522,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9646,50 +9656,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129538573</v>
+        <v>129543221</v>
       </c>
       <c r="B84" t="n">
-        <v>8450</v>
+        <v>79070</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>440932</v>
+        <v>440739</v>
       </c>
       <c r="R84" t="n">
-        <v>6754178</v>
+        <v>6754147</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9721,7 +9726,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9731,7 +9736,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9746,22 +9751,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129543202</v>
+        <v>129543164</v>
       </c>
       <c r="B85" t="n">
-        <v>8450</v>
+        <v>80204</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9769,39 +9774,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>440918</v>
+        <v>440708</v>
       </c>
       <c r="R85" t="n">
-        <v>6754161</v>
+        <v>6754116</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9843,7 +9843,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9870,50 +9875,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129543173</v>
+        <v>129543154</v>
       </c>
       <c r="B86" t="n">
-        <v>8450</v>
+        <v>90613</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>1962</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>440917</v>
+        <v>440770</v>
       </c>
       <c r="R86" t="n">
-        <v>6754255</v>
+        <v>6754101</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9982,10 +9982,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129543203</v>
+        <v>129543155</v>
       </c>
       <c r="B87" t="n">
-        <v>8450</v>
+        <v>56920</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9993,27 +9993,27 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10022,10 +10022,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>440946</v>
+        <v>440878</v>
       </c>
       <c r="R87" t="n">
-        <v>6754123</v>
+        <v>6754126</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10522,45 +10522,50 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129543153</v>
+        <v>129543175</v>
       </c>
       <c r="B92" t="n">
-        <v>90613</v>
+        <v>8450</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>440976</v>
+        <v>440896</v>
       </c>
       <c r="R92" t="n">
-        <v>6754143</v>
+        <v>6754124</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10592,7 +10597,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10602,7 +10607,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10629,10 +10634,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129543142</v>
+        <v>129543153</v>
       </c>
       <c r="B93" t="n">
-        <v>79689</v>
+        <v>90613</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10640,21 +10645,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10664,10 +10669,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>440949</v>
+        <v>440976</v>
       </c>
       <c r="R93" t="n">
-        <v>6754170</v>
+        <v>6754143</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10699,7 +10704,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10709,7 +10714,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10736,50 +10741,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129543175</v>
+        <v>129543142</v>
       </c>
       <c r="B94" t="n">
-        <v>8450</v>
+        <v>79689</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>440896</v>
+        <v>440949</v>
       </c>
       <c r="R94" t="n">
-        <v>6754124</v>
+        <v>6754170</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11169,45 +11169,50 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129543152</v>
+        <v>129543174</v>
       </c>
       <c r="B98" t="n">
-        <v>90613</v>
+        <v>8450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>440718</v>
+        <v>440876</v>
       </c>
       <c r="R98" t="n">
-        <v>6754157</v>
+        <v>6754211</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11239,7 +11244,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11249,7 +11254,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11276,38 +11281,38 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129543170</v>
+        <v>129538483</v>
       </c>
       <c r="B99" t="n">
-        <v>57730</v>
+        <v>8450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -11316,10 +11321,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>440677</v>
+        <v>440916</v>
       </c>
       <c r="R99" t="n">
-        <v>6754247</v>
+        <v>6754159</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11351,7 +11356,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11361,12 +11366,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11381,19 +11381,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129538483</v>
+        <v>129543189</v>
       </c>
       <c r="B100" t="n">
         <v>8450</v>
@@ -11424,7 +11424,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11433,10 +11433,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>440916</v>
+        <v>440793</v>
       </c>
       <c r="R100" t="n">
-        <v>6754159</v>
+        <v>6754070</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11493,19 +11493,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129543174</v>
+        <v>129538851</v>
       </c>
       <c r="B101" t="n">
         <v>8450</v>
@@ -11545,10 +11545,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>440876</v>
+        <v>440918</v>
       </c>
       <c r="R101" t="n">
-        <v>6754211</v>
+        <v>6754126</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11605,62 +11605,57 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129538851</v>
+        <v>129543152</v>
       </c>
       <c r="B102" t="n">
-        <v>8450</v>
+        <v>90613</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>1962</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>440918</v>
+        <v>440718</v>
       </c>
       <c r="R102" t="n">
-        <v>6754126</v>
+        <v>6754157</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11692,7 +11687,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11702,7 +11697,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11717,50 +11712,50 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129543189</v>
+        <v>129543170</v>
       </c>
       <c r="B103" t="n">
-        <v>8450</v>
+        <v>57730</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11769,10 +11764,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>440793</v>
+        <v>440677</v>
       </c>
       <c r="R103" t="n">
-        <v>6754070</v>
+        <v>6754247</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11804,7 +11799,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11814,7 +11809,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD103" t="b">

--- a/artfynd/A 45199-2025 artfynd.xlsx
+++ b/artfynd/A 45199-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129539829</v>
       </c>
       <c r="B2" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129543238</v>
+        <v>129543240</v>
       </c>
       <c r="B4" t="n">
-        <v>91854</v>
+        <v>78741</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440966</v>
+        <v>440736</v>
       </c>
       <c r="R4" t="n">
-        <v>6754151</v>
+        <v>6754282</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,6 +983,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1001,32 +1002,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129543240</v>
+        <v>129543238</v>
       </c>
       <c r="B5" t="n">
-        <v>78736</v>
+        <v>91860</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440736</v>
+        <v>440966</v>
       </c>
       <c r="R5" t="n">
-        <v>6754282</v>
+        <v>6754151</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1072,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1082,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,7 +1091,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1109,32 +1109,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129543168</v>
+        <v>129543147</v>
       </c>
       <c r="B6" t="n">
-        <v>92867</v>
+        <v>79694</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440718</v>
+        <v>440701</v>
       </c>
       <c r="R6" t="n">
-        <v>6754157</v>
+        <v>6754185</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1216,10 +1216,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129543239</v>
+        <v>129543183</v>
       </c>
       <c r="B7" t="n">
-        <v>80110</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,34 +1227,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6457</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440708</v>
+        <v>440945</v>
       </c>
       <c r="R7" t="n">
-        <v>6754116</v>
+        <v>6754252</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,7 +1291,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1296,12 +1301,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1328,45 +1328,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129543147</v>
+        <v>129543191</v>
       </c>
       <c r="B8" t="n">
-        <v>79689</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440701</v>
+        <v>440733</v>
       </c>
       <c r="R8" t="n">
-        <v>6754185</v>
+        <v>6754283</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,7 +1403,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1408,7 +1413,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,45 +1440,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129539852</v>
+        <v>129539316</v>
       </c>
       <c r="B9" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440880</v>
+        <v>440779</v>
       </c>
       <c r="R9" t="n">
-        <v>6754175</v>
+        <v>6754008</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,32 +1552,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129539462</v>
+        <v>129543168</v>
       </c>
       <c r="B10" t="n">
-        <v>79070</v>
+        <v>92873</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440787</v>
+        <v>440718</v>
       </c>
       <c r="R10" t="n">
-        <v>6753947</v>
+        <v>6754157</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,7 +1622,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1622,7 +1632,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1637,12 +1647,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1652,7 +1662,7 @@
         <v>129543158</v>
       </c>
       <c r="B11" t="n">
-        <v>91602</v>
+        <v>91608</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,50 +1766,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129543183</v>
+        <v>129539852</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>79075</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440945</v>
+        <v>440880</v>
       </c>
       <c r="R12" t="n">
-        <v>6754252</v>
+        <v>6754175</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1831,7 +1836,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1841,7 +1846,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,62 +1861,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129543191</v>
+        <v>129539462</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>79075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440733</v>
+        <v>440787</v>
       </c>
       <c r="R13" t="n">
-        <v>6754283</v>
+        <v>6753947</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1968,22 +1968,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129539316</v>
+        <v>129543239</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>80115</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,39 +1991,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6457</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440779</v>
+        <v>440708</v>
       </c>
       <c r="R14" t="n">
-        <v>6754008</v>
+        <v>6754116</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,7 +2050,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2065,7 +2060,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2080,44 +2080,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129543227</v>
+        <v>129539028</v>
       </c>
       <c r="B15" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440744</v>
+        <v>440970</v>
       </c>
       <c r="R15" t="n">
-        <v>6754336</v>
+        <v>6754114</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,57 +2187,62 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129543216</v>
+        <v>129543182</v>
       </c>
       <c r="B16" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440945</v>
+        <v>440934</v>
       </c>
       <c r="R16" t="n">
-        <v>6754252</v>
+        <v>6754244</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2306,32 +2311,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129539028</v>
+        <v>129543216</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>79075</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2341,10 +2346,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440970</v>
+        <v>440945</v>
       </c>
       <c r="R17" t="n">
-        <v>6754114</v>
+        <v>6754252</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2376,7 +2381,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2386,7 +2391,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2401,62 +2406,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543182</v>
+        <v>129543227</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>79075</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440934</v>
+        <v>440744</v>
       </c>
       <c r="R18" t="n">
-        <v>6754244</v>
+        <v>6754336</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2528,7 +2528,7 @@
         <v>129543219</v>
       </c>
       <c r="B19" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,50 +2632,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129543195</v>
+        <v>129538675</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>79075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440708</v>
+        <v>440902</v>
       </c>
       <c r="R20" t="n">
-        <v>6754371</v>
+        <v>6754135</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2707,7 +2702,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2717,7 +2712,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2732,50 +2727,50 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129539529</v>
+        <v>129538905</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>57732</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2784,10 +2779,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440725</v>
+        <v>440970</v>
       </c>
       <c r="R21" t="n">
-        <v>6754011</v>
+        <v>6754114</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2819,7 +2814,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2829,7 +2824,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2856,38 +2851,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129538905</v>
+        <v>129543195</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2896,10 +2891,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440970</v>
+        <v>440708</v>
       </c>
       <c r="R22" t="n">
-        <v>6754114</v>
+        <v>6754371</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2931,7 +2926,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2941,7 +2936,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2956,57 +2951,62 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129538675</v>
+        <v>129539529</v>
       </c>
       <c r="B23" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440902</v>
+        <v>440725</v>
       </c>
       <c r="R23" t="n">
-        <v>6754135</v>
+        <v>6754011</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3075,10 +3075,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129538680</v>
+        <v>129543229</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>79075</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3086,39 +3086,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440918</v>
+        <v>440638</v>
       </c>
       <c r="R24" t="n">
-        <v>6754126</v>
+        <v>6754239</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3150,7 +3145,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3160,7 +3155,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3175,12 +3170,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3190,7 +3185,7 @@
         <v>129543234</v>
       </c>
       <c r="B25" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3297,7 +3292,7 @@
         <v>129539521</v>
       </c>
       <c r="B26" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3404,7 +3399,7 @@
         <v>129543228</v>
       </c>
       <c r="B27" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3508,10 +3503,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543229</v>
+        <v>129538680</v>
       </c>
       <c r="B28" t="n">
-        <v>79070</v>
+        <v>57732</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3519,34 +3514,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440638</v>
+        <v>440918</v>
       </c>
       <c r="R28" t="n">
-        <v>6754239</v>
+        <v>6754126</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3603,12 +3603,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3618,7 +3618,7 @@
         <v>129543222</v>
       </c>
       <c r="B29" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>129543233</v>
       </c>
       <c r="B30" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4389,10 +4389,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129543235</v>
+        <v>129539754</v>
       </c>
       <c r="B36" t="n">
-        <v>79070</v>
+        <v>91608</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4400,34 +4400,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440863</v>
+        <v>440820</v>
       </c>
       <c r="R36" t="n">
-        <v>6754131</v>
+        <v>6754096</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4459,7 +4463,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4469,7 +4473,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4484,22 +4488,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129539703</v>
+        <v>129543159</v>
       </c>
       <c r="B37" t="n">
-        <v>79070</v>
+        <v>91608</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4507,21 +4511,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4531,10 +4535,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440820</v>
+        <v>440738</v>
       </c>
       <c r="R37" t="n">
-        <v>6754096</v>
+        <v>6754021</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4566,7 +4570,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4576,7 +4580,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4591,22 +4595,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129539754</v>
+        <v>129539703</v>
       </c>
       <c r="B38" t="n">
-        <v>91602</v>
+        <v>79075</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4614,28 +4618,24 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
@@ -4714,10 +4714,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129543159</v>
+        <v>129539312</v>
       </c>
       <c r="B39" t="n">
-        <v>91602</v>
+        <v>57732</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4725,34 +4725,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440738</v>
+        <v>440779</v>
       </c>
       <c r="R39" t="n">
-        <v>6754021</v>
+        <v>6754008</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4784,7 +4789,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4794,7 +4799,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4809,12 +4814,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4933,10 +4938,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129539312</v>
+        <v>129543235</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>79075</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4944,39 +4949,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440779</v>
+        <v>440863</v>
       </c>
       <c r="R41" t="n">
-        <v>6754008</v>
+        <v>6754131</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5033,62 +5033,57 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129539589</v>
+        <v>129543145</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>79107</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440769</v>
+        <v>440723</v>
       </c>
       <c r="R42" t="n">
-        <v>6754064</v>
+        <v>6754344</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5120,7 +5115,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5130,7 +5125,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5145,19 +5140,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129538433</v>
+        <v>129539589</v>
       </c>
       <c r="B43" t="n">
         <v>8450</v>
@@ -5197,10 +5192,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440937</v>
+        <v>440769</v>
       </c>
       <c r="R43" t="n">
-        <v>6754141</v>
+        <v>6754064</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5232,7 +5227,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5242,7 +5237,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5269,45 +5264,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129543145</v>
+        <v>129538433</v>
       </c>
       <c r="B44" t="n">
-        <v>79102</v>
+        <v>8450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440723</v>
+        <v>440937</v>
       </c>
       <c r="R44" t="n">
-        <v>6754344</v>
+        <v>6754141</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5364,57 +5364,62 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129543226</v>
+        <v>129543194</v>
       </c>
       <c r="B45" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440757</v>
+        <v>440745</v>
       </c>
       <c r="R45" t="n">
-        <v>6754337</v>
+        <v>6754333</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5446,7 +5451,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5456,7 +5461,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5483,7 +5488,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129543194</v>
+        <v>129539814</v>
       </c>
       <c r="B46" t="n">
         <v>8450</v>
@@ -5523,10 +5528,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440745</v>
+        <v>440861</v>
       </c>
       <c r="R46" t="n">
-        <v>6754333</v>
+        <v>6754168</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5558,7 +5563,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5568,7 +5573,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5583,12 +5588,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5707,50 +5712,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129539814</v>
+        <v>129543226</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>79075</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440861</v>
+        <v>440757</v>
       </c>
       <c r="R48" t="n">
-        <v>6754168</v>
+        <v>6754337</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5807,12 +5807,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5822,7 +5822,7 @@
         <v>129543220</v>
       </c>
       <c r="B49" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>129543236</v>
       </c>
       <c r="B50" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6033,38 +6033,38 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129539404</v>
+        <v>129543198</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>8450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6073,10 +6073,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440775</v>
+        <v>440824</v>
       </c>
       <c r="R51" t="n">
-        <v>6753988</v>
+        <v>6754177</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6133,50 +6133,50 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129543198</v>
+        <v>129539404</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>57732</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440824</v>
+        <v>440775</v>
       </c>
       <c r="R52" t="n">
-        <v>6754177</v>
+        <v>6753988</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6245,12 +6245,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6260,7 +6260,7 @@
         <v>129543166</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>129543230</v>
       </c>
       <c r="B56" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>129538554</v>
       </c>
       <c r="B57" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6807,45 +6807,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129543144</v>
+        <v>129543181</v>
       </c>
       <c r="B58" t="n">
-        <v>91504</v>
+        <v>8450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3242</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440718</v>
+        <v>440990</v>
       </c>
       <c r="R58" t="n">
-        <v>6754215</v>
+        <v>6754140</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6877,7 +6882,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6887,7 +6892,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6914,45 +6919,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129543213</v>
+        <v>129543197</v>
       </c>
       <c r="B59" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440996</v>
+        <v>440785</v>
       </c>
       <c r="R59" t="n">
-        <v>6754160</v>
+        <v>6754107</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6984,7 +6994,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6994,7 +7004,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7021,10 +7031,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129538786</v>
+        <v>129543144</v>
       </c>
       <c r="B60" t="n">
-        <v>79070</v>
+        <v>91510</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7032,21 +7042,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7056,10 +7066,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440918</v>
+        <v>440718</v>
       </c>
       <c r="R60" t="n">
-        <v>6754126</v>
+        <v>6754215</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7091,7 +7101,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7101,7 +7111,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7116,62 +7126,57 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129543181</v>
+        <v>129538786</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>79075</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>440990</v>
+        <v>440918</v>
       </c>
       <c r="R61" t="n">
-        <v>6754140</v>
+        <v>6754126</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7203,7 +7208,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7213,7 +7218,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7228,62 +7233,57 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129543197</v>
+        <v>129543213</v>
       </c>
       <c r="B62" t="n">
-        <v>8450</v>
+        <v>79075</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>440785</v>
+        <v>440996</v>
       </c>
       <c r="R62" t="n">
-        <v>6754107</v>
+        <v>6754160</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7315,7 +7315,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7352,10 +7352,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129543157</v>
+        <v>129543245</v>
       </c>
       <c r="B63" t="n">
-        <v>57890</v>
+        <v>78741</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7363,39 +7363,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440759</v>
+        <v>440986</v>
       </c>
       <c r="R63" t="n">
-        <v>6754342</v>
+        <v>6754157</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7427,7 +7422,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7437,7 +7432,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7446,6 +7441,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7464,50 +7460,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129543179</v>
+        <v>129539371</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>79075</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440821</v>
+        <v>440769</v>
       </c>
       <c r="R64" t="n">
-        <v>6754050</v>
+        <v>6754008</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7539,7 +7530,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7549,7 +7540,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7564,19 +7555,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129543176</v>
+        <v>129543179</v>
       </c>
       <c r="B65" t="n">
         <v>8450</v>
@@ -7607,7 +7598,7 @@
       <c r="I65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7616,10 +7607,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440820</v>
+        <v>440821</v>
       </c>
       <c r="R65" t="n">
-        <v>6754121</v>
+        <v>6754050</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7651,7 +7642,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7661,7 +7652,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7688,7 +7679,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129543192</v>
+        <v>129543176</v>
       </c>
       <c r="B66" t="n">
         <v>8450</v>
@@ -7719,7 +7710,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7728,10 +7719,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440742</v>
+        <v>440820</v>
       </c>
       <c r="R66" t="n">
-        <v>6754310</v>
+        <v>6754121</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7763,7 +7754,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7773,7 +7764,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7800,45 +7791,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129539371</v>
+        <v>129543192</v>
       </c>
       <c r="B67" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>440769</v>
+        <v>440742</v>
       </c>
       <c r="R67" t="n">
-        <v>6754008</v>
+        <v>6754310</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7870,7 +7866,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7880,7 +7876,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7895,22 +7891,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129543245</v>
+        <v>129543157</v>
       </c>
       <c r="B68" t="n">
-        <v>78736</v>
+        <v>57895</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7918,34 +7914,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440986</v>
+        <v>440759</v>
       </c>
       <c r="R68" t="n">
-        <v>6754157</v>
+        <v>6754342</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7977,7 +7978,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7987,7 +7988,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7996,7 +7997,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8018,7 +8018,7 @@
         <v>129543141</v>
       </c>
       <c r="B69" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8122,10 +8122,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129543225</v>
+        <v>129543218</v>
       </c>
       <c r="B70" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8157,10 +8157,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440764</v>
+        <v>440888</v>
       </c>
       <c r="R70" t="n">
-        <v>6754320</v>
+        <v>6754157</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8229,10 +8229,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129538126</v>
+        <v>129543143</v>
       </c>
       <c r="B71" t="n">
-        <v>79070</v>
+        <v>79694</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8240,21 +8240,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8264,10 +8264,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>441002</v>
+        <v>440893</v>
       </c>
       <c r="R71" t="n">
-        <v>6754112</v>
+        <v>6754230</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8299,7 +8299,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8324,22 +8324,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129543143</v>
+        <v>129538247</v>
       </c>
       <c r="B72" t="n">
-        <v>79689</v>
+        <v>57732</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8347,34 +8347,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>440893</v>
+        <v>440944</v>
       </c>
       <c r="R72" t="n">
-        <v>6754230</v>
+        <v>6754122</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8406,7 +8411,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8416,7 +8421,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8431,57 +8436,62 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129543224</v>
+        <v>129543178</v>
       </c>
       <c r="B73" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>440774</v>
+        <v>440816</v>
       </c>
       <c r="R73" t="n">
-        <v>6754313</v>
+        <v>6754178</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8513,7 +8523,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8523,7 +8533,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8550,45 +8560,50 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129543246</v>
+        <v>129543199</v>
       </c>
       <c r="B74" t="n">
-        <v>78736</v>
+        <v>8450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>440893</v>
+        <v>440855</v>
       </c>
       <c r="R74" t="n">
-        <v>6754230</v>
+        <v>6754166</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8620,7 +8635,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8630,7 +8645,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8639,7 +8654,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8658,10 +8672,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129543218</v>
+        <v>129543246</v>
       </c>
       <c r="B75" t="n">
-        <v>79070</v>
+        <v>78741</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8669,21 +8683,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8693,10 +8707,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>440888</v>
+        <v>440893</v>
       </c>
       <c r="R75" t="n">
-        <v>6754157</v>
+        <v>6754230</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8728,7 +8742,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8738,7 +8752,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8747,6 +8761,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8765,10 +8780,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129538247</v>
+        <v>129543225</v>
       </c>
       <c r="B76" t="n">
-        <v>57727</v>
+        <v>79075</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8776,39 +8791,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>440944</v>
+        <v>440764</v>
       </c>
       <c r="R76" t="n">
-        <v>6754122</v>
+        <v>6754320</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8840,7 +8850,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8850,7 +8860,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8865,62 +8875,57 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129543178</v>
+        <v>129538126</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>79075</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>440816</v>
+        <v>441002</v>
       </c>
       <c r="R77" t="n">
-        <v>6754178</v>
+        <v>6754112</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8952,7 +8957,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8962,7 +8967,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8977,62 +8982,57 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129543199</v>
+        <v>129543224</v>
       </c>
       <c r="B78" t="n">
-        <v>8450</v>
+        <v>79075</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>440855</v>
+        <v>440774</v>
       </c>
       <c r="R78" t="n">
-        <v>6754166</v>
+        <v>6754313</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9101,50 +9101,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129538573</v>
+        <v>129543154</v>
       </c>
       <c r="B79" t="n">
-        <v>8450</v>
+        <v>90619</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>1962</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>440932</v>
+        <v>440770</v>
       </c>
       <c r="R79" t="n">
-        <v>6754178</v>
+        <v>6754101</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9176,7 +9171,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9186,7 +9181,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9201,62 +9196,57 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129543173</v>
+        <v>129543215</v>
       </c>
       <c r="B80" t="n">
-        <v>8450</v>
+        <v>79075</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>440917</v>
+        <v>440930</v>
       </c>
       <c r="R80" t="n">
-        <v>6754255</v>
+        <v>6754182</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9288,7 +9278,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9298,7 +9288,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9325,50 +9315,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129543203</v>
+        <v>129543221</v>
       </c>
       <c r="B81" t="n">
-        <v>8450</v>
+        <v>79075</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>440946</v>
+        <v>440739</v>
       </c>
       <c r="R81" t="n">
-        <v>6754123</v>
+        <v>6754147</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9400,7 +9385,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9410,7 +9395,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9437,10 +9422,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129543202</v>
+        <v>129543164</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>80209</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9448,39 +9433,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>440918</v>
+        <v>440708</v>
       </c>
       <c r="R82" t="n">
-        <v>6754161</v>
+        <v>6754116</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9512,7 +9492,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9522,7 +9502,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9549,45 +9534,50 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129543215</v>
+        <v>129543155</v>
       </c>
       <c r="B83" t="n">
-        <v>79070</v>
+        <v>56925</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>440930</v>
+        <v>440878</v>
       </c>
       <c r="R83" t="n">
-        <v>6754182</v>
+        <v>6754126</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9619,7 +9609,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9629,7 +9619,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9656,45 +9646,50 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129543221</v>
+        <v>129538573</v>
       </c>
       <c r="B84" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>440739</v>
+        <v>440932</v>
       </c>
       <c r="R84" t="n">
-        <v>6754147</v>
+        <v>6754178</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9726,7 +9721,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9736,7 +9731,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9751,22 +9746,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129543164</v>
+        <v>129543202</v>
       </c>
       <c r="B85" t="n">
-        <v>80204</v>
+        <v>8450</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9774,34 +9769,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>440708</v>
+        <v>440918</v>
       </c>
       <c r="R85" t="n">
-        <v>6754116</v>
+        <v>6754161</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9843,12 +9843,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9875,45 +9870,50 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129543154</v>
+        <v>129543173</v>
       </c>
       <c r="B86" t="n">
-        <v>90613</v>
+        <v>8450</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>440770</v>
+        <v>440917</v>
       </c>
       <c r="R86" t="n">
-        <v>6754101</v>
+        <v>6754255</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9982,10 +9982,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129543155</v>
+        <v>129543203</v>
       </c>
       <c r="B87" t="n">
-        <v>56920</v>
+        <v>8450</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9993,27 +9993,27 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10022,10 +10022,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>440878</v>
+        <v>440946</v>
       </c>
       <c r="R87" t="n">
-        <v>6754126</v>
+        <v>6754123</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10094,10 +10094,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129543171</v>
+        <v>129543223</v>
       </c>
       <c r="B88" t="n">
-        <v>91634</v>
+        <v>79075</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10105,21 +10105,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10129,10 +10129,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>440996</v>
+        <v>440754</v>
       </c>
       <c r="R88" t="n">
-        <v>6754160</v>
+        <v>6754304</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10204,7 +10204,7 @@
         <v>129538198</v>
       </c>
       <c r="B89" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10308,10 +10308,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129543223</v>
+        <v>129538100</v>
       </c>
       <c r="B90" t="n">
-        <v>79070</v>
+        <v>79694</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10319,21 +10319,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10343,10 +10343,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>440754</v>
+        <v>441007</v>
       </c>
       <c r="R90" t="n">
-        <v>6754304</v>
+        <v>6754124</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10378,7 +10378,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10403,22 +10403,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129538100</v>
+        <v>129543171</v>
       </c>
       <c r="B91" t="n">
-        <v>79689</v>
+        <v>91640</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10426,21 +10426,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10450,10 +10450,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>441007</v>
+        <v>440996</v>
       </c>
       <c r="R91" t="n">
-        <v>6754124</v>
+        <v>6754160</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10510,12 +10510,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10637,7 +10637,7 @@
         <v>129543153</v>
       </c>
       <c r="B93" t="n">
-        <v>90613</v>
+        <v>90619</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
         <v>129543142</v>
       </c>
       <c r="B94" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10848,10 +10848,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129543232</v>
+        <v>129543214</v>
       </c>
       <c r="B95" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10883,10 +10883,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>440798</v>
+        <v>440948</v>
       </c>
       <c r="R95" t="n">
-        <v>6754119</v>
+        <v>6754156</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10918,7 +10918,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10928,7 +10928,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10955,10 +10955,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129543214</v>
+        <v>129543231</v>
       </c>
       <c r="B96" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10990,10 +10990,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>440948</v>
+        <v>440769</v>
       </c>
       <c r="R96" t="n">
-        <v>6754156</v>
+        <v>6754066</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11062,10 +11062,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129543231</v>
+        <v>129543232</v>
       </c>
       <c r="B97" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11097,10 +11097,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>440769</v>
+        <v>440798</v>
       </c>
       <c r="R97" t="n">
-        <v>6754066</v>
+        <v>6754119</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11132,7 +11132,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11617,10 +11617,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129543152</v>
+        <v>129543170</v>
       </c>
       <c r="B102" t="n">
-        <v>90613</v>
+        <v>57735</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11628,34 +11628,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>440718</v>
+        <v>440677</v>
       </c>
       <c r="R102" t="n">
-        <v>6754157</v>
+        <v>6754247</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11687,7 +11692,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11697,7 +11702,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11724,10 +11734,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129543170</v>
+        <v>129543152</v>
       </c>
       <c r="B103" t="n">
-        <v>57730</v>
+        <v>90619</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11735,39 +11745,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>440677</v>
+        <v>440718</v>
       </c>
       <c r="R103" t="n">
-        <v>6754247</v>
+        <v>6754157</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11799,7 +11804,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11809,12 +11814,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11841,10 +11841,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129538156</v>
+        <v>129543217</v>
       </c>
       <c r="B104" t="n">
-        <v>57727</v>
+        <v>79075</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11852,39 +11852,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>440982</v>
+        <v>440902</v>
       </c>
       <c r="R104" t="n">
-        <v>6754123</v>
+        <v>6754164</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11916,7 +11911,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11926,7 +11921,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11941,22 +11936,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129543247</v>
+        <v>129538088</v>
       </c>
       <c r="B105" t="n">
-        <v>78736</v>
+        <v>79075</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11964,21 +11959,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11988,10 +11983,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>440894</v>
+        <v>441007</v>
       </c>
       <c r="R105" t="n">
-        <v>6754104</v>
+        <v>6754124</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12023,7 +12018,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12033,7 +12028,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12042,29 +12037,28 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129543217</v>
+        <v>129543247</v>
       </c>
       <c r="B106" t="n">
-        <v>79070</v>
+        <v>78741</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12072,21 +12066,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12096,10 +12090,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>440902</v>
+        <v>440894</v>
       </c>
       <c r="R106" t="n">
-        <v>6754164</v>
+        <v>6754104</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12131,7 +12125,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12141,7 +12135,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12150,6 +12144,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -12168,10 +12163,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129538088</v>
+        <v>129538156</v>
       </c>
       <c r="B107" t="n">
-        <v>79070</v>
+        <v>57732</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12179,34 +12174,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>441007</v>
+        <v>440982</v>
       </c>
       <c r="R107" t="n">
-        <v>6754124</v>
+        <v>6754123</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 45199-2025 artfynd.xlsx
+++ b/artfynd/A 45199-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129539829</v>
       </c>
       <c r="B2" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129543240</v>
       </c>
       <c r="B4" t="n">
-        <v>78741</v>
+        <v>78742</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>129543238</v>
       </c>
       <c r="B5" t="n">
-        <v>91860</v>
+        <v>91861</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129543147</v>
+        <v>129539852</v>
       </c>
       <c r="B6" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1120,21 +1120,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440701</v>
+        <v>440880</v>
       </c>
       <c r="R6" t="n">
-        <v>6754185</v>
+        <v>6754175</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,62 +1204,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129543183</v>
+        <v>129539462</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440945</v>
+        <v>440787</v>
       </c>
       <c r="R7" t="n">
-        <v>6754252</v>
+        <v>6753947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,7 +1286,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1301,7 +1296,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,62 +1311,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129543191</v>
+        <v>129543168</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>92874</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>4365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440733</v>
+        <v>440718</v>
       </c>
       <c r="R8" t="n">
-        <v>6754283</v>
+        <v>6754157</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,7 +1393,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1413,7 +1403,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1440,50 +1430,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129539316</v>
+        <v>129543158</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>91609</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440779</v>
+        <v>440892</v>
       </c>
       <c r="R9" t="n">
-        <v>6754008</v>
+        <v>6754225</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,7 +1500,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1525,7 +1510,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,44 +1525,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129543168</v>
+        <v>129543239</v>
       </c>
       <c r="B10" t="n">
-        <v>92873</v>
+        <v>80116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4365</v>
+        <v>6457</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1587,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440718</v>
+        <v>440708</v>
       </c>
       <c r="R10" t="n">
-        <v>6754157</v>
+        <v>6754116</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,7 +1607,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1632,7 +1617,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543158</v>
+        <v>129543147</v>
       </c>
       <c r="B11" t="n">
-        <v>91608</v>
+        <v>79695</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1670,21 +1660,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1694,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440892</v>
+        <v>440701</v>
       </c>
       <c r="R11" t="n">
-        <v>6754225</v>
+        <v>6754185</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1719,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1739,7 +1729,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,45 +1756,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129539852</v>
+        <v>129543183</v>
       </c>
       <c r="B12" t="n">
-        <v>79075</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440880</v>
+        <v>440945</v>
       </c>
       <c r="R12" t="n">
-        <v>6754175</v>
+        <v>6754252</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,7 +1831,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1846,7 +1841,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1861,57 +1856,62 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129539462</v>
+        <v>129543191</v>
       </c>
       <c r="B13" t="n">
-        <v>79075</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440787</v>
+        <v>440733</v>
       </c>
       <c r="R13" t="n">
-        <v>6753947</v>
+        <v>6754283</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1968,22 +1968,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129543239</v>
+        <v>129539316</v>
       </c>
       <c r="B14" t="n">
-        <v>80115</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,34 +1991,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6457</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440708</v>
+        <v>440779</v>
       </c>
       <c r="R14" t="n">
-        <v>6754116</v>
+        <v>6754008</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,7 +2055,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2060,12 +2065,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2080,44 +2080,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129539028</v>
+        <v>129543216</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440970</v>
+        <v>440945</v>
       </c>
       <c r="R15" t="n">
-        <v>6754114</v>
+        <v>6754252</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,62 +2187,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129543182</v>
+        <v>129543227</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440934</v>
+        <v>440744</v>
       </c>
       <c r="R16" t="n">
-        <v>6754244</v>
+        <v>6754336</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,7 +2269,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2284,7 +2279,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2311,32 +2306,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129543216</v>
+        <v>129539028</v>
       </c>
       <c r="B17" t="n">
-        <v>79075</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2346,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440945</v>
+        <v>440970</v>
       </c>
       <c r="R17" t="n">
-        <v>6754252</v>
+        <v>6754114</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2381,7 +2376,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2391,7 +2386,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,57 +2401,62 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543227</v>
+        <v>129543182</v>
       </c>
       <c r="B18" t="n">
-        <v>79075</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440744</v>
+        <v>440934</v>
       </c>
       <c r="R18" t="n">
-        <v>6754336</v>
+        <v>6754244</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2528,7 +2528,7 @@
         <v>129543219</v>
       </c>
       <c r="B19" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>129538675</v>
       </c>
       <c r="B20" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>129538905</v>
       </c>
       <c r="B21" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3075,10 +3075,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129543229</v>
+        <v>129543234</v>
       </c>
       <c r="B24" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440638</v>
+        <v>440834</v>
       </c>
       <c r="R24" t="n">
-        <v>6754239</v>
+        <v>6754152</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3182,10 +3182,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129543234</v>
+        <v>129539521</v>
       </c>
       <c r="B25" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440834</v>
+        <v>440725</v>
       </c>
       <c r="R25" t="n">
-        <v>6754152</v>
+        <v>6754011</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3277,22 +3277,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129539521</v>
+        <v>129543228</v>
       </c>
       <c r="B26" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3324,10 +3324,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440725</v>
+        <v>440716</v>
       </c>
       <c r="R26" t="n">
-        <v>6754011</v>
+        <v>6754354</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3384,22 +3384,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543228</v>
+        <v>129543229</v>
       </c>
       <c r="B27" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440716</v>
+        <v>440638</v>
       </c>
       <c r="R27" t="n">
-        <v>6754354</v>
+        <v>6754239</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3506,7 +3506,7 @@
         <v>129538680</v>
       </c>
       <c r="B28" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>129543222</v>
       </c>
       <c r="B29" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>129543233</v>
       </c>
       <c r="B30" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4389,10 +4389,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129539754</v>
+        <v>129543235</v>
       </c>
       <c r="B36" t="n">
-        <v>91608</v>
+        <v>79076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4400,38 +4400,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440820</v>
+        <v>440863</v>
       </c>
       <c r="R36" t="n">
-        <v>6754096</v>
+        <v>6754131</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4463,7 +4459,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4473,7 +4469,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4488,22 +4484,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129543159</v>
+        <v>129539703</v>
       </c>
       <c r="B37" t="n">
-        <v>91608</v>
+        <v>79076</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4511,21 +4507,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4535,10 +4531,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440738</v>
+        <v>440820</v>
       </c>
       <c r="R37" t="n">
-        <v>6754021</v>
+        <v>6754096</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4570,7 +4566,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4580,7 +4576,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4595,22 +4591,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129539703</v>
+        <v>129539754</v>
       </c>
       <c r="B38" t="n">
-        <v>79075</v>
+        <v>91609</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4618,24 +4614,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
@@ -4714,10 +4714,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129539312</v>
+        <v>129543159</v>
       </c>
       <c r="B39" t="n">
-        <v>57732</v>
+        <v>91609</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4725,39 +4725,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440779</v>
+        <v>440738</v>
       </c>
       <c r="R39" t="n">
-        <v>6754008</v>
+        <v>6754021</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4789,7 +4784,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4799,7 +4794,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4814,50 +4809,50 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543190</v>
+        <v>129539312</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4866,10 +4861,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440773</v>
+        <v>440779</v>
       </c>
       <c r="R40" t="n">
-        <v>6754088</v>
+        <v>6754008</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4901,7 +4896,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4911,7 +4906,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4926,57 +4921,62 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129543235</v>
+        <v>129543190</v>
       </c>
       <c r="B41" t="n">
-        <v>79075</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440863</v>
+        <v>440773</v>
       </c>
       <c r="R41" t="n">
-        <v>6754131</v>
+        <v>6754088</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5048,7 +5048,7 @@
         <v>129543145</v>
       </c>
       <c r="B42" t="n">
-        <v>79107</v>
+        <v>79108</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5376,50 +5376,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129543194</v>
+        <v>129543226</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440745</v>
+        <v>440757</v>
       </c>
       <c r="R45" t="n">
-        <v>6754333</v>
+        <v>6754337</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5451,7 +5446,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5461,7 +5456,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5488,7 +5483,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129539814</v>
+        <v>129543194</v>
       </c>
       <c r="B46" t="n">
         <v>8450</v>
@@ -5528,10 +5523,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440861</v>
+        <v>440745</v>
       </c>
       <c r="R46" t="n">
-        <v>6754168</v>
+        <v>6754333</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5563,7 +5558,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5573,7 +5568,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5588,19 +5583,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129538170</v>
+        <v>129539814</v>
       </c>
       <c r="B47" t="n">
         <v>8450</v>
@@ -5631,7 +5626,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5640,10 +5635,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440982</v>
+        <v>440861</v>
       </c>
       <c r="R47" t="n">
-        <v>6754123</v>
+        <v>6754168</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5675,7 +5670,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5685,7 +5680,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5712,45 +5707,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129543226</v>
+        <v>129538170</v>
       </c>
       <c r="B48" t="n">
-        <v>79075</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440757</v>
+        <v>440982</v>
       </c>
       <c r="R48" t="n">
-        <v>6754337</v>
+        <v>6754123</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5807,22 +5807,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129543220</v>
+        <v>129539404</v>
       </c>
       <c r="B49" t="n">
-        <v>79075</v>
+        <v>57733</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5830,34 +5830,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440851</v>
+        <v>440775</v>
       </c>
       <c r="R49" t="n">
-        <v>6754062</v>
+        <v>6753988</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5889,7 +5894,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5899,7 +5904,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5914,22 +5919,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129543236</v>
+        <v>129543166</v>
       </c>
       <c r="B50" t="n">
-        <v>79075</v>
+        <v>57733</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5937,34 +5942,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440970</v>
+        <v>440772</v>
       </c>
       <c r="R50" t="n">
-        <v>6754114</v>
+        <v>6754089</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5996,7 +6006,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6006,7 +6016,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6145,10 +6155,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129539404</v>
+        <v>129543220</v>
       </c>
       <c r="B52" t="n">
-        <v>57732</v>
+        <v>79076</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6156,39 +6166,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440775</v>
+        <v>440851</v>
       </c>
       <c r="R52" t="n">
-        <v>6753988</v>
+        <v>6754062</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6220,7 +6225,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6230,7 +6235,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6245,22 +6250,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129543166</v>
+        <v>129543236</v>
       </c>
       <c r="B53" t="n">
-        <v>57732</v>
+        <v>79076</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6268,39 +6273,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440772</v>
+        <v>440970</v>
       </c>
       <c r="R53" t="n">
-        <v>6754089</v>
+        <v>6754114</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6369,50 +6369,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129543185</v>
+        <v>129543230</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440888</v>
+        <v>440779</v>
       </c>
       <c r="R54" t="n">
-        <v>6754217</v>
+        <v>6754063</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6444,7 +6439,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6454,7 +6449,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6481,7 +6476,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129538256</v>
+        <v>129543185</v>
       </c>
       <c r="B55" t="n">
         <v>8450</v>
@@ -6512,7 +6507,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6521,10 +6516,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440944</v>
+        <v>440888</v>
       </c>
       <c r="R55" t="n">
-        <v>6754122</v>
+        <v>6754217</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6556,7 +6551,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6566,7 +6561,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6581,57 +6576,62 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129543230</v>
+        <v>129538256</v>
       </c>
       <c r="B56" t="n">
-        <v>79075</v>
+        <v>8450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440779</v>
+        <v>440944</v>
       </c>
       <c r="R56" t="n">
-        <v>6754063</v>
+        <v>6754122</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6688,12 +6688,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6703,7 +6703,7 @@
         <v>129538554</v>
       </c>
       <c r="B57" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6807,50 +6807,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129543181</v>
+        <v>129538786</v>
       </c>
       <c r="B58" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440990</v>
+        <v>440918</v>
       </c>
       <c r="R58" t="n">
-        <v>6754140</v>
+        <v>6754126</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6882,7 +6877,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6892,7 +6887,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6907,62 +6902,57 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129543197</v>
+        <v>129543213</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440785</v>
+        <v>440996</v>
       </c>
       <c r="R59" t="n">
-        <v>6754107</v>
+        <v>6754160</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6994,7 +6984,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7004,7 +6994,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7034,7 +7024,7 @@
         <v>129543144</v>
       </c>
       <c r="B60" t="n">
-        <v>91510</v>
+        <v>91511</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7138,45 +7128,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129538786</v>
+        <v>129543181</v>
       </c>
       <c r="B61" t="n">
-        <v>79075</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>440918</v>
+        <v>440990</v>
       </c>
       <c r="R61" t="n">
-        <v>6754126</v>
+        <v>6754140</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7208,7 +7203,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7218,7 +7213,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7233,57 +7228,62 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129543213</v>
+        <v>129543197</v>
       </c>
       <c r="B62" t="n">
-        <v>79075</v>
+        <v>8450</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>440996</v>
+        <v>440785</v>
       </c>
       <c r="R62" t="n">
-        <v>6754160</v>
+        <v>6754107</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7315,7 +7315,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7352,10 +7352,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129543245</v>
+        <v>129543157</v>
       </c>
       <c r="B63" t="n">
-        <v>78741</v>
+        <v>57896</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7363,34 +7363,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440986</v>
+        <v>440759</v>
       </c>
       <c r="R63" t="n">
-        <v>6754157</v>
+        <v>6754342</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7422,7 +7427,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7432,7 +7437,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7441,7 +7446,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7460,10 +7464,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129539371</v>
+        <v>129543245</v>
       </c>
       <c r="B64" t="n">
-        <v>79075</v>
+        <v>78742</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7471,21 +7475,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7495,10 +7499,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440769</v>
+        <v>440986</v>
       </c>
       <c r="R64" t="n">
-        <v>6754008</v>
+        <v>6754157</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7530,7 +7534,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7540,7 +7544,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7549,68 +7553,64 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129543179</v>
+        <v>129539371</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440821</v>
+        <v>440769</v>
       </c>
       <c r="R65" t="n">
-        <v>6754050</v>
+        <v>6754008</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7667,19 +7667,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129543176</v>
+        <v>129543179</v>
       </c>
       <c r="B66" t="n">
         <v>8450</v>
@@ -7710,7 +7710,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440820</v>
+        <v>440821</v>
       </c>
       <c r="R66" t="n">
-        <v>6754121</v>
+        <v>6754050</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7791,7 +7791,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129543192</v>
+        <v>129543176</v>
       </c>
       <c r="B67" t="n">
         <v>8450</v>
@@ -7822,7 +7822,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>440742</v>
+        <v>440820</v>
       </c>
       <c r="R67" t="n">
-        <v>6754310</v>
+        <v>6754121</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7903,38 +7903,38 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129543157</v>
+        <v>129543192</v>
       </c>
       <c r="B68" t="n">
-        <v>57895</v>
+        <v>8450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7943,10 +7943,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440759</v>
+        <v>440742</v>
       </c>
       <c r="R68" t="n">
-        <v>6754342</v>
+        <v>6754310</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8015,10 +8015,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129543141</v>
+        <v>129543246</v>
       </c>
       <c r="B69" t="n">
-        <v>79694</v>
+        <v>78742</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8026,21 +8026,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8050,10 +8050,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440974</v>
+        <v>440893</v>
       </c>
       <c r="R69" t="n">
-        <v>6754141</v>
+        <v>6754230</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8104,6 +8104,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8122,10 +8123,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129543218</v>
+        <v>129538247</v>
       </c>
       <c r="B70" t="n">
-        <v>79075</v>
+        <v>57733</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8133,34 +8134,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440888</v>
+        <v>440944</v>
       </c>
       <c r="R70" t="n">
-        <v>6754157</v>
+        <v>6754122</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8192,7 +8198,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8202,7 +8208,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8217,22 +8223,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129543143</v>
+        <v>129543225</v>
       </c>
       <c r="B71" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8240,21 +8246,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8264,10 +8270,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>440893</v>
+        <v>440764</v>
       </c>
       <c r="R71" t="n">
-        <v>6754230</v>
+        <v>6754320</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8299,7 +8305,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8309,7 +8315,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8336,10 +8342,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129538247</v>
+        <v>129543218</v>
       </c>
       <c r="B72" t="n">
-        <v>57732</v>
+        <v>79076</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8347,39 +8353,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>440944</v>
+        <v>440888</v>
       </c>
       <c r="R72" t="n">
-        <v>6754122</v>
+        <v>6754157</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8411,7 +8412,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8421,7 +8422,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8436,62 +8437,57 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129543178</v>
+        <v>129538126</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>440816</v>
+        <v>441002</v>
       </c>
       <c r="R73" t="n">
-        <v>6754178</v>
+        <v>6754112</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8523,7 +8519,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8533,7 +8529,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8548,62 +8544,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129543199</v>
+        <v>129543224</v>
       </c>
       <c r="B74" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>440855</v>
+        <v>440774</v>
       </c>
       <c r="R74" t="n">
-        <v>6754166</v>
+        <v>6754313</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8635,7 +8626,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8645,7 +8636,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8672,10 +8663,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129543246</v>
+        <v>129543141</v>
       </c>
       <c r="B75" t="n">
-        <v>78741</v>
+        <v>79695</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8683,21 +8674,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8707,10 +8698,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>440893</v>
+        <v>440974</v>
       </c>
       <c r="R75" t="n">
-        <v>6754230</v>
+        <v>6754141</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8742,7 +8733,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8752,7 +8743,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8761,7 +8752,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8780,10 +8770,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129543225</v>
+        <v>129543143</v>
       </c>
       <c r="B76" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8791,21 +8781,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8815,10 +8805,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>440764</v>
+        <v>440893</v>
       </c>
       <c r="R76" t="n">
-        <v>6754320</v>
+        <v>6754230</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8850,7 +8840,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8860,7 +8850,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8887,45 +8877,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129538126</v>
+        <v>129543178</v>
       </c>
       <c r="B77" t="n">
-        <v>79075</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>441002</v>
+        <v>440816</v>
       </c>
       <c r="R77" t="n">
-        <v>6754112</v>
+        <v>6754178</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8957,7 +8952,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8967,7 +8962,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8982,57 +8977,62 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129543224</v>
+        <v>129543199</v>
       </c>
       <c r="B78" t="n">
-        <v>79075</v>
+        <v>8450</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>440774</v>
+        <v>440855</v>
       </c>
       <c r="R78" t="n">
-        <v>6754313</v>
+        <v>6754166</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9101,10 +9101,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129543154</v>
+        <v>129543215</v>
       </c>
       <c r="B79" t="n">
-        <v>90619</v>
+        <v>79076</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9112,21 +9112,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9136,10 +9136,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>440770</v>
+        <v>440930</v>
       </c>
       <c r="R79" t="n">
-        <v>6754101</v>
+        <v>6754182</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9171,7 +9171,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9208,10 +9208,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129543215</v>
+        <v>129543154</v>
       </c>
       <c r="B80" t="n">
-        <v>79075</v>
+        <v>90620</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9219,21 +9219,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9243,10 +9243,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>440930</v>
+        <v>440770</v>
       </c>
       <c r="R80" t="n">
-        <v>6754182</v>
+        <v>6754101</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9315,45 +9315,50 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129543221</v>
+        <v>129543155</v>
       </c>
       <c r="B81" t="n">
-        <v>79075</v>
+        <v>56926</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>440739</v>
+        <v>440878</v>
       </c>
       <c r="R81" t="n">
-        <v>6754147</v>
+        <v>6754126</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9385,7 +9390,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9395,7 +9400,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9422,10 +9427,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129543164</v>
+        <v>129538573</v>
       </c>
       <c r="B82" t="n">
-        <v>80209</v>
+        <v>8450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9433,34 +9438,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>440708</v>
+        <v>440932</v>
       </c>
       <c r="R82" t="n">
-        <v>6754116</v>
+        <v>6754178</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9492,7 +9502,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9502,12 +9512,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9522,22 +9527,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129543155</v>
+        <v>129543202</v>
       </c>
       <c r="B83" t="n">
-        <v>56925</v>
+        <v>8450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9545,27 +9550,27 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9574,10 +9579,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>440878</v>
+        <v>440918</v>
       </c>
       <c r="R83" t="n">
-        <v>6754126</v>
+        <v>6754161</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9609,7 +9614,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9619,7 +9624,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9646,7 +9651,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129538573</v>
+        <v>129543173</v>
       </c>
       <c r="B84" t="n">
         <v>8450</v>
@@ -9686,10 +9691,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>440932</v>
+        <v>440917</v>
       </c>
       <c r="R84" t="n">
-        <v>6754178</v>
+        <v>6754255</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9721,7 +9726,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9731,7 +9736,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9746,19 +9751,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129543202</v>
+        <v>129543203</v>
       </c>
       <c r="B85" t="n">
         <v>8450</v>
@@ -9798,10 +9803,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>440918</v>
+        <v>440946</v>
       </c>
       <c r="R85" t="n">
-        <v>6754161</v>
+        <v>6754123</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9833,7 +9838,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9843,7 +9848,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9870,50 +9875,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129543173</v>
+        <v>129543221</v>
       </c>
       <c r="B86" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>440917</v>
+        <v>440739</v>
       </c>
       <c r="R86" t="n">
-        <v>6754255</v>
+        <v>6754147</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9982,10 +9982,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129543203</v>
+        <v>129543164</v>
       </c>
       <c r="B87" t="n">
-        <v>8450</v>
+        <v>80210</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9993,39 +9993,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>6462</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>440946</v>
+        <v>440708</v>
       </c>
       <c r="R87" t="n">
-        <v>6754123</v>
+        <v>6754116</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10057,7 +10052,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10067,7 +10062,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10094,10 +10094,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129543223</v>
+        <v>129543171</v>
       </c>
       <c r="B88" t="n">
-        <v>79075</v>
+        <v>91641</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10105,21 +10105,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10129,10 +10129,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>440754</v>
+        <v>440996</v>
       </c>
       <c r="R88" t="n">
-        <v>6754304</v>
+        <v>6754160</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10204,7 +10204,7 @@
         <v>129538198</v>
       </c>
       <c r="B89" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10308,10 +10308,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129538100</v>
+        <v>129543223</v>
       </c>
       <c r="B90" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10319,21 +10319,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10343,10 +10343,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>441007</v>
+        <v>440754</v>
       </c>
       <c r="R90" t="n">
-        <v>6754124</v>
+        <v>6754304</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10378,7 +10378,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10403,22 +10403,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129543171</v>
+        <v>129538100</v>
       </c>
       <c r="B91" t="n">
-        <v>91640</v>
+        <v>79695</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10426,21 +10426,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10450,10 +10450,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>440996</v>
+        <v>441007</v>
       </c>
       <c r="R91" t="n">
-        <v>6754160</v>
+        <v>6754124</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10510,62 +10510,57 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129543175</v>
+        <v>129543153</v>
       </c>
       <c r="B92" t="n">
-        <v>8450</v>
+        <v>90620</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>1962</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>440896</v>
+        <v>440976</v>
       </c>
       <c r="R92" t="n">
-        <v>6754124</v>
+        <v>6754143</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10597,7 +10592,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10607,7 +10602,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10634,10 +10629,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129543153</v>
+        <v>129543142</v>
       </c>
       <c r="B93" t="n">
-        <v>90619</v>
+        <v>79695</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10645,21 +10640,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10669,10 +10664,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>440976</v>
+        <v>440949</v>
       </c>
       <c r="R93" t="n">
-        <v>6754143</v>
+        <v>6754170</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10704,7 +10699,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10714,7 +10709,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10741,45 +10736,50 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129543142</v>
+        <v>129543175</v>
       </c>
       <c r="B94" t="n">
-        <v>79694</v>
+        <v>8450</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>440949</v>
+        <v>440896</v>
       </c>
       <c r="R94" t="n">
-        <v>6754170</v>
+        <v>6754124</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10848,10 +10848,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129543214</v>
+        <v>129543231</v>
       </c>
       <c r="B95" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10883,10 +10883,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>440948</v>
+        <v>440769</v>
       </c>
       <c r="R95" t="n">
-        <v>6754156</v>
+        <v>6754066</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10918,7 +10918,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10928,7 +10928,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10955,10 +10955,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129543231</v>
+        <v>129543232</v>
       </c>
       <c r="B96" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10990,10 +10990,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>440769</v>
+        <v>440798</v>
       </c>
       <c r="R96" t="n">
-        <v>6754066</v>
+        <v>6754119</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11062,10 +11062,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129543232</v>
+        <v>129543214</v>
       </c>
       <c r="B97" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11097,10 +11097,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>440798</v>
+        <v>440948</v>
       </c>
       <c r="R97" t="n">
-        <v>6754119</v>
+        <v>6754156</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11132,7 +11132,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11169,50 +11169,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129543174</v>
+        <v>129543152</v>
       </c>
       <c r="B98" t="n">
-        <v>8450</v>
+        <v>90620</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>1962</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>440876</v>
+        <v>440718</v>
       </c>
       <c r="R98" t="n">
-        <v>6754211</v>
+        <v>6754157</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11244,7 +11239,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11254,7 +11249,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11281,7 +11276,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129538483</v>
+        <v>129543174</v>
       </c>
       <c r="B99" t="n">
         <v>8450</v>
@@ -11321,10 +11316,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>440916</v>
+        <v>440876</v>
       </c>
       <c r="R99" t="n">
-        <v>6754159</v>
+        <v>6754211</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11356,7 +11351,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11366,7 +11361,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11381,19 +11376,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129543189</v>
+        <v>129538483</v>
       </c>
       <c r="B100" t="n">
         <v>8450</v>
@@ -11424,7 +11419,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11433,10 +11428,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>440793</v>
+        <v>440916</v>
       </c>
       <c r="R100" t="n">
-        <v>6754070</v>
+        <v>6754159</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11468,7 +11463,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11478,7 +11473,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11493,19 +11488,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129538851</v>
+        <v>129543189</v>
       </c>
       <c r="B101" t="n">
         <v>8450</v>
@@ -11536,7 +11531,7 @@
       <c r="I101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -11545,10 +11540,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>440918</v>
+        <v>440793</v>
       </c>
       <c r="R101" t="n">
-        <v>6754126</v>
+        <v>6754070</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11580,7 +11575,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11590,7 +11585,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11605,50 +11600,50 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129543170</v>
+        <v>129538851</v>
       </c>
       <c r="B102" t="n">
-        <v>57735</v>
+        <v>8450</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -11657,10 +11652,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>440677</v>
+        <v>440918</v>
       </c>
       <c r="R102" t="n">
-        <v>6754247</v>
+        <v>6754126</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11692,7 +11687,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11702,12 +11697,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11722,22 +11712,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129543152</v>
+        <v>129543170</v>
       </c>
       <c r="B103" t="n">
-        <v>90619</v>
+        <v>57736</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11745,34 +11735,39 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>440718</v>
+        <v>440677</v>
       </c>
       <c r="R103" t="n">
-        <v>6754157</v>
+        <v>6754247</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11804,7 +11799,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11814,7 +11809,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11841,10 +11841,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129543217</v>
+        <v>129538156</v>
       </c>
       <c r="B104" t="n">
-        <v>79075</v>
+        <v>57733</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11852,34 +11852,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>440902</v>
+        <v>440982</v>
       </c>
       <c r="R104" t="n">
-        <v>6754164</v>
+        <v>6754123</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11911,7 +11916,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11921,7 +11926,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11936,22 +11941,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129538088</v>
+        <v>129543247</v>
       </c>
       <c r="B105" t="n">
-        <v>79075</v>
+        <v>78742</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11959,21 +11964,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11983,10 +11988,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>441007</v>
+        <v>440894</v>
       </c>
       <c r="R105" t="n">
-        <v>6754124</v>
+        <v>6754104</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12018,7 +12023,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12028,7 +12033,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12037,28 +12042,29 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129543247</v>
+        <v>129543217</v>
       </c>
       <c r="B106" t="n">
-        <v>78741</v>
+        <v>79076</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12066,21 +12072,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12090,10 +12096,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>440894</v>
+        <v>440902</v>
       </c>
       <c r="R106" t="n">
-        <v>6754104</v>
+        <v>6754164</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12125,7 +12131,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12135,7 +12141,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12144,7 +12150,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -12163,10 +12168,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129538156</v>
+        <v>129538088</v>
       </c>
       <c r="B107" t="n">
-        <v>57732</v>
+        <v>79076</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12174,39 +12179,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>440982</v>
+        <v>441007</v>
       </c>
       <c r="R107" t="n">
-        <v>6754123</v>
+        <v>6754124</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 45199-2025 artfynd.xlsx
+++ b/artfynd/A 45199-2025 artfynd.xlsx
@@ -2739,38 +2739,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129538905</v>
+        <v>129543195</v>
       </c>
       <c r="B21" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440970</v>
+        <v>440708</v>
       </c>
       <c r="R21" t="n">
-        <v>6754114</v>
+        <v>6754371</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2839,19 +2839,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129543195</v>
+        <v>129539529</v>
       </c>
       <c r="B22" t="n">
         <v>8450</v>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440708</v>
+        <v>440725</v>
       </c>
       <c r="R22" t="n">
-        <v>6754371</v>
+        <v>6754011</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2951,50 +2951,50 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129539529</v>
+        <v>129538905</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3003,10 +3003,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440725</v>
+        <v>440970</v>
       </c>
       <c r="R23" t="n">
-        <v>6754011</v>
+        <v>6754114</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4165,7 +4165,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129543193</v>
+        <v>129543196</v>
       </c>
       <c r="B34" t="n">
         <v>8450</v>
@@ -4205,10 +4205,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440757</v>
+        <v>440716</v>
       </c>
       <c r="R34" t="n">
-        <v>6754338</v>
+        <v>6754046</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4277,7 +4277,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129543196</v>
+        <v>129543193</v>
       </c>
       <c r="B35" t="n">
         <v>8450</v>
@@ -4317,10 +4317,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440716</v>
+        <v>440757</v>
       </c>
       <c r="R35" t="n">
-        <v>6754046</v>
+        <v>6754338</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5819,10 +5819,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129539404</v>
+        <v>129543220</v>
       </c>
       <c r="B49" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5830,39 +5830,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440775</v>
+        <v>440851</v>
       </c>
       <c r="R49" t="n">
-        <v>6753988</v>
+        <v>6754062</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5894,7 +5889,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5904,7 +5899,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5919,22 +5914,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129543166</v>
+        <v>129543236</v>
       </c>
       <c r="B50" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5942,39 +5937,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440772</v>
+        <v>440970</v>
       </c>
       <c r="R50" t="n">
-        <v>6754089</v>
+        <v>6754114</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6006,7 +5996,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6016,7 +6006,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6155,10 +6145,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129543220</v>
+        <v>129539404</v>
       </c>
       <c r="B52" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6166,34 +6156,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440851</v>
+        <v>440775</v>
       </c>
       <c r="R52" t="n">
-        <v>6754062</v>
+        <v>6753988</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6225,7 +6220,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6235,7 +6230,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6250,22 +6245,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129543236</v>
+        <v>129543166</v>
       </c>
       <c r="B53" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6273,34 +6268,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440970</v>
+        <v>440772</v>
       </c>
       <c r="R53" t="n">
-        <v>6754114</v>
+        <v>6754089</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6369,10 +6369,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129543230</v>
+        <v>129538554</v>
       </c>
       <c r="B54" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6380,21 +6380,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6404,10 +6404,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440779</v>
+        <v>440919</v>
       </c>
       <c r="R54" t="n">
-        <v>6754063</v>
+        <v>6754174</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6464,12 +6464,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6700,10 +6700,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129538554</v>
+        <v>129543230</v>
       </c>
       <c r="B57" t="n">
-        <v>79695</v>
+        <v>79076</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6711,21 +6711,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6735,10 +6735,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440919</v>
+        <v>440779</v>
       </c>
       <c r="R57" t="n">
-        <v>6754174</v>
+        <v>6754063</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6795,12 +6795,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7464,45 +7464,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129543245</v>
+        <v>129543179</v>
       </c>
       <c r="B64" t="n">
-        <v>78742</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440986</v>
+        <v>440821</v>
       </c>
       <c r="R64" t="n">
-        <v>6754157</v>
+        <v>6754050</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7534,7 +7539,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7544,7 +7549,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7553,7 +7558,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7572,45 +7576,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129539371</v>
+        <v>129543176</v>
       </c>
       <c r="B65" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440769</v>
+        <v>440820</v>
       </c>
       <c r="R65" t="n">
-        <v>6754008</v>
+        <v>6754121</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7642,7 +7651,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7652,7 +7661,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7667,19 +7676,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129543179</v>
+        <v>129543192</v>
       </c>
       <c r="B66" t="n">
         <v>8450</v>
@@ -7719,10 +7728,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440821</v>
+        <v>440742</v>
       </c>
       <c r="R66" t="n">
-        <v>6754050</v>
+        <v>6754310</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7754,7 +7763,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7764,7 +7773,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7791,50 +7800,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129543176</v>
+        <v>129543245</v>
       </c>
       <c r="B67" t="n">
-        <v>8450</v>
+        <v>78742</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>440820</v>
+        <v>440986</v>
       </c>
       <c r="R67" t="n">
-        <v>6754121</v>
+        <v>6754157</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7866,7 +7870,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7876,7 +7880,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7885,6 +7889,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7903,50 +7908,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129543192</v>
+        <v>129539371</v>
       </c>
       <c r="B68" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440742</v>
+        <v>440769</v>
       </c>
       <c r="R68" t="n">
-        <v>6754310</v>
+        <v>6754008</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8003,12 +8003,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -11276,38 +11276,38 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129543174</v>
+        <v>129543170</v>
       </c>
       <c r="B99" t="n">
-        <v>8450</v>
+        <v>57736</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -11316,10 +11316,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>440876</v>
+        <v>440677</v>
       </c>
       <c r="R99" t="n">
-        <v>6754211</v>
+        <v>6754247</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11361,7 +11361,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11388,7 +11393,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129538483</v>
+        <v>129543174</v>
       </c>
       <c r="B100" t="n">
         <v>8450</v>
@@ -11428,10 +11433,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>440916</v>
+        <v>440876</v>
       </c>
       <c r="R100" t="n">
-        <v>6754159</v>
+        <v>6754211</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11463,7 +11468,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11473,7 +11478,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11488,19 +11493,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129543189</v>
+        <v>129538483</v>
       </c>
       <c r="B101" t="n">
         <v>8450</v>
@@ -11531,7 +11536,7 @@
       <c r="I101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -11540,10 +11545,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>440793</v>
+        <v>440916</v>
       </c>
       <c r="R101" t="n">
-        <v>6754070</v>
+        <v>6754159</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11575,7 +11580,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11585,7 +11590,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11600,19 +11605,19 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129538851</v>
+        <v>129543189</v>
       </c>
       <c r="B102" t="n">
         <v>8450</v>
@@ -11643,7 +11648,7 @@
       <c r="I102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -11652,10 +11657,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>440918</v>
+        <v>440793</v>
       </c>
       <c r="R102" t="n">
-        <v>6754126</v>
+        <v>6754070</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11687,7 +11692,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11697,7 +11702,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11712,50 +11717,50 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129543170</v>
+        <v>129538851</v>
       </c>
       <c r="B103" t="n">
-        <v>57736</v>
+        <v>8450</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11764,10 +11769,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>440677</v>
+        <v>440918</v>
       </c>
       <c r="R103" t="n">
-        <v>6754247</v>
+        <v>6754126</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11799,7 +11804,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11809,12 +11814,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11829,22 +11829,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129538156</v>
+        <v>129543217</v>
       </c>
       <c r="B104" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11852,39 +11852,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>440982</v>
+        <v>440902</v>
       </c>
       <c r="R104" t="n">
-        <v>6754123</v>
+        <v>6754164</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11916,7 +11911,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11926,7 +11921,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11941,22 +11936,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129543247</v>
+        <v>129538088</v>
       </c>
       <c r="B105" t="n">
-        <v>78742</v>
+        <v>79076</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11964,21 +11959,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11988,10 +11983,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>440894</v>
+        <v>441007</v>
       </c>
       <c r="R105" t="n">
-        <v>6754104</v>
+        <v>6754124</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12023,7 +12018,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12033,7 +12028,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12042,29 +12037,28 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129543217</v>
+        <v>129538156</v>
       </c>
       <c r="B106" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12072,34 +12066,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>440902</v>
+        <v>440982</v>
       </c>
       <c r="R106" t="n">
-        <v>6754164</v>
+        <v>6754123</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12131,7 +12130,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12141,7 +12140,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12156,22 +12155,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129538088</v>
+        <v>129543247</v>
       </c>
       <c r="B107" t="n">
-        <v>79076</v>
+        <v>78742</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12179,21 +12178,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12203,10 +12202,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>441007</v>
+        <v>440894</v>
       </c>
       <c r="R107" t="n">
-        <v>6754124</v>
+        <v>6754104</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12238,7 +12237,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12248,7 +12247,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12257,18 +12256,19 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>

--- a/artfynd/A 45199-2025 artfynd.xlsx
+++ b/artfynd/A 45199-2025 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129539829</v>
+        <v>129539413</v>
       </c>
       <c r="B2" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440861</v>
+        <v>440775</v>
       </c>
       <c r="R2" t="n">
-        <v>6754168</v>
+        <v>6753988</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,50 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129539413</v>
+        <v>129539829</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440775</v>
+        <v>440861</v>
       </c>
       <c r="R3" t="n">
-        <v>6753988</v>
+        <v>6754168</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
         <v>129543240</v>
       </c>
       <c r="B4" t="n">
-        <v>78742</v>
+        <v>78747</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,32 +1002,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129543238</v>
+        <v>129539462</v>
       </c>
       <c r="B5" t="n">
-        <v>91861</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440966</v>
+        <v>440787</v>
       </c>
       <c r="R5" t="n">
-        <v>6754151</v>
+        <v>6753947</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,12 +1097,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1112,7 +1112,7 @@
         <v>129539852</v>
       </c>
       <c r="B6" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,32 +1216,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129539462</v>
+        <v>129543239</v>
       </c>
       <c r="B7" t="n">
-        <v>79076</v>
+        <v>80121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440787</v>
+        <v>440708</v>
       </c>
       <c r="R7" t="n">
-        <v>6753947</v>
+        <v>6754116</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1296,7 +1296,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,44 +1316,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129543168</v>
+        <v>129543147</v>
       </c>
       <c r="B8" t="n">
-        <v>92874</v>
+        <v>79700</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1358,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440718</v>
+        <v>440701</v>
       </c>
       <c r="R8" t="n">
-        <v>6754157</v>
+        <v>6754185</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,7 +1398,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1403,7 +1408,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1430,32 +1435,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129543158</v>
+        <v>129543238</v>
       </c>
       <c r="B9" t="n">
-        <v>91609</v>
+        <v>91866</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>65</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1465,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440892</v>
+        <v>440966</v>
       </c>
       <c r="R9" t="n">
-        <v>6754225</v>
+        <v>6754151</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,7 +1505,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1510,7 +1515,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1537,32 +1542,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129543239</v>
+        <v>129543168</v>
       </c>
       <c r="B10" t="n">
-        <v>80116</v>
+        <v>92879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6457</v>
+        <v>4365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1572,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440708</v>
+        <v>440718</v>
       </c>
       <c r="R10" t="n">
-        <v>6754116</v>
+        <v>6754157</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,7 +1612,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1617,12 +1622,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543147</v>
+        <v>129543158</v>
       </c>
       <c r="B11" t="n">
-        <v>79695</v>
+        <v>91614</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,21 +1660,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440701</v>
+        <v>440892</v>
       </c>
       <c r="R11" t="n">
-        <v>6754185</v>
+        <v>6754225</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2095,7 +2095,7 @@
         <v>129543216</v>
       </c>
       <c r="B15" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>129543227</v>
       </c>
       <c r="B16" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2525,45 +2525,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129543219</v>
+        <v>129543195</v>
       </c>
       <c r="B19" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440890</v>
+        <v>440708</v>
       </c>
       <c r="R19" t="n">
-        <v>6754082</v>
+        <v>6754371</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2595,7 +2600,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2605,7 +2610,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2632,45 +2637,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129538675</v>
+        <v>129539529</v>
       </c>
       <c r="B20" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440902</v>
+        <v>440725</v>
       </c>
       <c r="R20" t="n">
-        <v>6754135</v>
+        <v>6754011</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2702,7 +2712,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2712,7 +2722,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2739,38 +2749,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129543195</v>
+        <v>129538905</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2779,10 +2789,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440708</v>
+        <v>440970</v>
       </c>
       <c r="R21" t="n">
-        <v>6754371</v>
+        <v>6754114</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2814,7 +2824,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2824,7 +2834,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2839,62 +2849,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129539529</v>
+        <v>129543219</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440725</v>
+        <v>440890</v>
       </c>
       <c r="R22" t="n">
-        <v>6754011</v>
+        <v>6754082</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2926,7 +2931,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2936,7 +2941,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2951,22 +2956,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129538905</v>
+        <v>129538675</v>
       </c>
       <c r="B23" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2974,39 +2979,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440970</v>
+        <v>440902</v>
       </c>
       <c r="R23" t="n">
-        <v>6754114</v>
+        <v>6754135</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3075,10 +3075,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129543234</v>
+        <v>129539521</v>
       </c>
       <c r="B24" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440834</v>
+        <v>440725</v>
       </c>
       <c r="R24" t="n">
-        <v>6754152</v>
+        <v>6754011</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3170,22 +3170,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129539521</v>
+        <v>129543234</v>
       </c>
       <c r="B25" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440725</v>
+        <v>440834</v>
       </c>
       <c r="R25" t="n">
-        <v>6754011</v>
+        <v>6754152</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3277,22 +3277,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129543228</v>
+        <v>129538680</v>
       </c>
       <c r="B26" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3300,34 +3300,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440716</v>
+        <v>440918</v>
       </c>
       <c r="R26" t="n">
-        <v>6754354</v>
+        <v>6754126</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3359,7 +3364,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3369,7 +3374,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3384,22 +3389,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543229</v>
+        <v>129543228</v>
       </c>
       <c r="B27" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3431,10 +3436,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440638</v>
+        <v>440716</v>
       </c>
       <c r="R27" t="n">
-        <v>6754239</v>
+        <v>6754354</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3466,7 +3471,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3476,7 +3481,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3503,10 +3508,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129538680</v>
+        <v>129543229</v>
       </c>
       <c r="B28" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3514,39 +3519,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440918</v>
+        <v>440638</v>
       </c>
       <c r="R28" t="n">
-        <v>6754126</v>
+        <v>6754239</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3603,12 +3603,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3618,7 +3618,7 @@
         <v>129543222</v>
       </c>
       <c r="B29" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>129543233</v>
       </c>
       <c r="B30" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129543196</v>
+        <v>129543193</v>
       </c>
       <c r="B34" t="n">
         <v>8450</v>
@@ -4205,10 +4205,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440716</v>
+        <v>440757</v>
       </c>
       <c r="R34" t="n">
-        <v>6754046</v>
+        <v>6754338</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4277,7 +4277,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129543193</v>
+        <v>129543196</v>
       </c>
       <c r="B35" t="n">
         <v>8450</v>
@@ -4317,10 +4317,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440757</v>
+        <v>440716</v>
       </c>
       <c r="R35" t="n">
-        <v>6754338</v>
+        <v>6754046</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4392,7 +4392,7 @@
         <v>129543235</v>
       </c>
       <c r="B36" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4496,10 +4496,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129539703</v>
+        <v>129539754</v>
       </c>
       <c r="B37" t="n">
-        <v>79076</v>
+        <v>91614</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4507,24 +4507,28 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
@@ -4603,10 +4607,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129539754</v>
+        <v>129539703</v>
       </c>
       <c r="B38" t="n">
-        <v>91609</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4614,28 +4618,24 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
@@ -4717,7 +4717,7 @@
         <v>129543159</v>
       </c>
       <c r="B39" t="n">
-        <v>91609</v>
+        <v>91614</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4821,38 +4821,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129539312</v>
+        <v>129543190</v>
       </c>
       <c r="B40" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440779</v>
+        <v>440773</v>
       </c>
       <c r="R40" t="n">
-        <v>6754008</v>
+        <v>6754088</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4921,50 +4921,50 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129543190</v>
+        <v>129539312</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440773</v>
+        <v>440779</v>
       </c>
       <c r="R41" t="n">
-        <v>6754088</v>
+        <v>6754008</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5033,12 +5033,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5048,7 +5048,7 @@
         <v>129543145</v>
       </c>
       <c r="B42" t="n">
-        <v>79108</v>
+        <v>79113</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5376,45 +5376,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129543226</v>
+        <v>129543194</v>
       </c>
       <c r="B45" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440757</v>
+        <v>440745</v>
       </c>
       <c r="R45" t="n">
-        <v>6754337</v>
+        <v>6754333</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5446,7 +5451,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5456,7 +5461,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5483,7 +5488,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129543194</v>
+        <v>129539814</v>
       </c>
       <c r="B46" t="n">
         <v>8450</v>
@@ -5523,10 +5528,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440745</v>
+        <v>440861</v>
       </c>
       <c r="R46" t="n">
-        <v>6754333</v>
+        <v>6754168</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5558,7 +5563,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5568,7 +5573,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5583,19 +5588,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129539814</v>
+        <v>129538170</v>
       </c>
       <c r="B47" t="n">
         <v>8450</v>
@@ -5626,7 +5631,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5635,10 +5640,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440861</v>
+        <v>440982</v>
       </c>
       <c r="R47" t="n">
-        <v>6754168</v>
+        <v>6754123</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5670,7 +5675,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5680,7 +5685,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5707,50 +5712,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129538170</v>
+        <v>129543226</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440982</v>
+        <v>440757</v>
       </c>
       <c r="R48" t="n">
-        <v>6754123</v>
+        <v>6754337</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5807,22 +5807,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129543220</v>
+        <v>129539404</v>
       </c>
       <c r="B49" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5830,34 +5830,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440851</v>
+        <v>440775</v>
       </c>
       <c r="R49" t="n">
-        <v>6754062</v>
+        <v>6753988</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5889,7 +5894,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5899,7 +5904,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5914,22 +5919,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129543236</v>
+        <v>129543220</v>
       </c>
       <c r="B50" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5961,10 +5966,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440970</v>
+        <v>440851</v>
       </c>
       <c r="R50" t="n">
-        <v>6754114</v>
+        <v>6754062</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5996,7 +6001,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6006,7 +6011,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6033,50 +6038,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129543198</v>
+        <v>129543236</v>
       </c>
       <c r="B51" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440824</v>
+        <v>440970</v>
       </c>
       <c r="R51" t="n">
-        <v>6754177</v>
+        <v>6754114</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6145,7 +6145,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129539404</v>
+        <v>129543166</v>
       </c>
       <c r="B52" t="n">
         <v>57733</v>
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440775</v>
+        <v>440772</v>
       </c>
       <c r="R52" t="n">
-        <v>6753988</v>
+        <v>6754089</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6245,50 +6245,50 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129543166</v>
+        <v>129543198</v>
       </c>
       <c r="B53" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6297,10 +6297,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440772</v>
+        <v>440824</v>
       </c>
       <c r="R53" t="n">
-        <v>6754089</v>
+        <v>6754177</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6372,7 +6372,7 @@
         <v>129538554</v>
       </c>
       <c r="B54" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6476,50 +6476,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129543185</v>
+        <v>129543230</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440888</v>
+        <v>440779</v>
       </c>
       <c r="R55" t="n">
-        <v>6754217</v>
+        <v>6754063</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6551,7 +6546,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6561,7 +6556,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6588,7 +6583,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129538256</v>
+        <v>129543185</v>
       </c>
       <c r="B56" t="n">
         <v>8450</v>
@@ -6619,7 +6614,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6628,10 +6623,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440944</v>
+        <v>440888</v>
       </c>
       <c r="R56" t="n">
-        <v>6754122</v>
+        <v>6754217</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6663,7 +6658,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6673,7 +6668,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6688,57 +6683,62 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129543230</v>
+        <v>129538256</v>
       </c>
       <c r="B57" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440779</v>
+        <v>440944</v>
       </c>
       <c r="R57" t="n">
-        <v>6754063</v>
+        <v>6754122</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6795,22 +6795,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129538786</v>
+        <v>129543144</v>
       </c>
       <c r="B58" t="n">
-        <v>79076</v>
+        <v>91516</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6818,21 +6818,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440918</v>
+        <v>440718</v>
       </c>
       <c r="R58" t="n">
-        <v>6754126</v>
+        <v>6754215</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6902,57 +6902,62 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129543213</v>
+        <v>129543181</v>
       </c>
       <c r="B59" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440996</v>
+        <v>440990</v>
       </c>
       <c r="R59" t="n">
-        <v>6754160</v>
+        <v>6754140</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6984,7 +6989,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6994,7 +6999,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7021,45 +7026,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129543144</v>
+        <v>129543197</v>
       </c>
       <c r="B60" t="n">
-        <v>91511</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3242</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440718</v>
+        <v>440785</v>
       </c>
       <c r="R60" t="n">
-        <v>6754215</v>
+        <v>6754107</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7091,7 +7101,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7101,7 +7111,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7128,50 +7138,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129543181</v>
+        <v>129538786</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>440990</v>
+        <v>440918</v>
       </c>
       <c r="R61" t="n">
-        <v>6754140</v>
+        <v>6754126</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7203,7 +7208,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7213,7 +7218,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7228,62 +7233,57 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129543197</v>
+        <v>129543213</v>
       </c>
       <c r="B62" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>440785</v>
+        <v>440996</v>
       </c>
       <c r="R62" t="n">
-        <v>6754107</v>
+        <v>6754160</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7315,7 +7315,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7352,10 +7352,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129543157</v>
+        <v>129543245</v>
       </c>
       <c r="B63" t="n">
-        <v>57896</v>
+        <v>78747</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7363,39 +7363,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440759</v>
+        <v>440986</v>
       </c>
       <c r="R63" t="n">
-        <v>6754342</v>
+        <v>6754157</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7427,7 +7422,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7437,7 +7432,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7446,6 +7441,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7464,38 +7460,38 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129543179</v>
+        <v>129543157</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>57896</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7504,10 +7500,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440821</v>
+        <v>440759</v>
       </c>
       <c r="R64" t="n">
-        <v>6754050</v>
+        <v>6754342</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7539,7 +7535,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7549,7 +7545,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7576,50 +7572,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129543176</v>
+        <v>129539371</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440820</v>
+        <v>440769</v>
       </c>
       <c r="R65" t="n">
-        <v>6754121</v>
+        <v>6754008</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7651,7 +7642,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7661,7 +7652,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7676,19 +7667,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129543192</v>
+        <v>129543179</v>
       </c>
       <c r="B66" t="n">
         <v>8450</v>
@@ -7728,10 +7719,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440742</v>
+        <v>440821</v>
       </c>
       <c r="R66" t="n">
-        <v>6754310</v>
+        <v>6754050</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7763,7 +7754,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7773,7 +7764,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7800,45 +7791,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129543245</v>
+        <v>129543176</v>
       </c>
       <c r="B67" t="n">
-        <v>78742</v>
+        <v>8450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>440986</v>
+        <v>440820</v>
       </c>
       <c r="R67" t="n">
-        <v>6754157</v>
+        <v>6754121</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7870,7 +7866,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7880,7 +7876,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7889,7 +7885,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7908,45 +7903,50 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129539371</v>
+        <v>129543192</v>
       </c>
       <c r="B68" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440769</v>
+        <v>440742</v>
       </c>
       <c r="R68" t="n">
-        <v>6754008</v>
+        <v>6754310</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8003,22 +8003,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129543246</v>
+        <v>129543225</v>
       </c>
       <c r="B69" t="n">
-        <v>78742</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8026,21 +8026,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8050,10 +8050,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440893</v>
+        <v>440764</v>
       </c>
       <c r="R69" t="n">
-        <v>6754230</v>
+        <v>6754320</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8104,7 +8104,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8123,10 +8122,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129538247</v>
+        <v>129543218</v>
       </c>
       <c r="B70" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8134,39 +8133,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440944</v>
+        <v>440888</v>
       </c>
       <c r="R70" t="n">
-        <v>6754122</v>
+        <v>6754157</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8198,7 +8192,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8208,7 +8202,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8223,22 +8217,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129543225</v>
+        <v>129543246</v>
       </c>
       <c r="B71" t="n">
-        <v>79076</v>
+        <v>78747</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8246,21 +8240,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8270,10 +8264,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>440764</v>
+        <v>440893</v>
       </c>
       <c r="R71" t="n">
-        <v>6754320</v>
+        <v>6754230</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8305,7 +8299,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8315,7 +8309,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8324,6 +8318,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8342,10 +8337,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129543218</v>
+        <v>129543141</v>
       </c>
       <c r="B72" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8353,21 +8348,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8377,10 +8372,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>440888</v>
+        <v>440974</v>
       </c>
       <c r="R72" t="n">
-        <v>6754157</v>
+        <v>6754141</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8412,7 +8407,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8422,7 +8417,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8452,7 +8447,7 @@
         <v>129538126</v>
       </c>
       <c r="B73" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8556,10 +8551,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129543224</v>
+        <v>129543143</v>
       </c>
       <c r="B74" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8567,21 +8562,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8591,10 +8586,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>440774</v>
+        <v>440893</v>
       </c>
       <c r="R74" t="n">
-        <v>6754313</v>
+        <v>6754230</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8626,7 +8621,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8636,7 +8631,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8663,10 +8658,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129543141</v>
+        <v>129543224</v>
       </c>
       <c r="B75" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8674,21 +8669,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8698,10 +8693,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>440974</v>
+        <v>440774</v>
       </c>
       <c r="R75" t="n">
-        <v>6754141</v>
+        <v>6754313</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8733,7 +8728,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8743,7 +8738,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8770,10 +8765,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129543143</v>
+        <v>129538247</v>
       </c>
       <c r="B76" t="n">
-        <v>79695</v>
+        <v>57733</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8781,34 +8776,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>440893</v>
+        <v>440944</v>
       </c>
       <c r="R76" t="n">
-        <v>6754230</v>
+        <v>6754122</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8865,12 +8865,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9101,10 +9101,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129543215</v>
+        <v>129543154</v>
       </c>
       <c r="B79" t="n">
-        <v>79076</v>
+        <v>90625</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9112,21 +9112,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9136,10 +9136,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>440930</v>
+        <v>440770</v>
       </c>
       <c r="R79" t="n">
-        <v>6754182</v>
+        <v>6754101</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9171,7 +9171,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9208,32 +9208,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129543154</v>
+        <v>129543164</v>
       </c>
       <c r="B80" t="n">
-        <v>90620</v>
+        <v>80215</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1962</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9243,10 +9243,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>440770</v>
+        <v>440708</v>
       </c>
       <c r="R80" t="n">
-        <v>6754101</v>
+        <v>6754116</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9288,7 +9288,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9315,50 +9320,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129543155</v>
+        <v>129543215</v>
       </c>
       <c r="B81" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>440878</v>
+        <v>440930</v>
       </c>
       <c r="R81" t="n">
-        <v>6754126</v>
+        <v>6754182</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9390,7 +9390,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9427,50 +9427,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129538573</v>
+        <v>129543221</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>440932</v>
+        <v>440739</v>
       </c>
       <c r="R82" t="n">
-        <v>6754178</v>
+        <v>6754147</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9502,7 +9497,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9512,7 +9507,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9527,22 +9522,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129543202</v>
+        <v>129543155</v>
       </c>
       <c r="B83" t="n">
-        <v>8450</v>
+        <v>56926</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9550,27 +9545,27 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9579,10 +9574,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>440918</v>
+        <v>440878</v>
       </c>
       <c r="R83" t="n">
-        <v>6754161</v>
+        <v>6754126</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9614,7 +9609,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9624,7 +9619,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9651,7 +9646,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129543173</v>
+        <v>129538573</v>
       </c>
       <c r="B84" t="n">
         <v>8450</v>
@@ -9691,10 +9686,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>440917</v>
+        <v>440932</v>
       </c>
       <c r="R84" t="n">
-        <v>6754255</v>
+        <v>6754178</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9726,7 +9721,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9736,7 +9731,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9751,19 +9746,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129543203</v>
+        <v>129543202</v>
       </c>
       <c r="B85" t="n">
         <v>8450</v>
@@ -9803,10 +9798,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>440946</v>
+        <v>440918</v>
       </c>
       <c r="R85" t="n">
-        <v>6754123</v>
+        <v>6754161</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9838,7 +9833,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9848,7 +9843,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9875,45 +9870,50 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129543221</v>
+        <v>129543173</v>
       </c>
       <c r="B86" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>440739</v>
+        <v>440917</v>
       </c>
       <c r="R86" t="n">
-        <v>6754147</v>
+        <v>6754255</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9982,10 +9982,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129543164</v>
+        <v>129543203</v>
       </c>
       <c r="B87" t="n">
-        <v>80210</v>
+        <v>8450</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9993,34 +9993,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6462</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>440708</v>
+        <v>440946</v>
       </c>
       <c r="R87" t="n">
-        <v>6754116</v>
+        <v>6754123</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10052,7 +10057,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10062,12 +10067,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10097,7 +10097,7 @@
         <v>129543171</v>
       </c>
       <c r="B88" t="n">
-        <v>91641</v>
+        <v>91646</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10201,10 +10201,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129538198</v>
+        <v>129538100</v>
       </c>
       <c r="B89" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10212,21 +10212,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>440969</v>
+        <v>441007</v>
       </c>
       <c r="R89" t="n">
-        <v>6754129</v>
+        <v>6754124</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10308,10 +10308,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129543223</v>
+        <v>129538198</v>
       </c>
       <c r="B90" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10343,10 +10343,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>440754</v>
+        <v>440969</v>
       </c>
       <c r="R90" t="n">
-        <v>6754304</v>
+        <v>6754129</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10378,7 +10378,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10403,22 +10403,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129538100</v>
+        <v>129543223</v>
       </c>
       <c r="B91" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10426,21 +10426,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10450,10 +10450,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>441007</v>
+        <v>440754</v>
       </c>
       <c r="R91" t="n">
-        <v>6754124</v>
+        <v>6754304</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10485,7 +10485,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10495,7 +10495,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10510,12 +10510,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10525,7 +10525,7 @@
         <v>129543153</v>
       </c>
       <c r="B92" t="n">
-        <v>90620</v>
+        <v>90625</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         <v>129543142</v>
       </c>
       <c r="B93" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>129543231</v>
       </c>
       <c r="B95" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10955,10 +10955,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129543232</v>
+        <v>129543214</v>
       </c>
       <c r="B96" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10990,10 +10990,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>440798</v>
+        <v>440948</v>
       </c>
       <c r="R96" t="n">
-        <v>6754119</v>
+        <v>6754156</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11062,10 +11062,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129543214</v>
+        <v>129543232</v>
       </c>
       <c r="B97" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11097,10 +11097,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>440948</v>
+        <v>440798</v>
       </c>
       <c r="R97" t="n">
-        <v>6754156</v>
+        <v>6754119</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11132,7 +11132,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11172,7 +11172,7 @@
         <v>129543152</v>
       </c>
       <c r="B98" t="n">
-        <v>90620</v>
+        <v>90625</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11841,10 +11841,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129543217</v>
+        <v>129543247</v>
       </c>
       <c r="B104" t="n">
-        <v>79076</v>
+        <v>78747</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11852,21 +11852,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11876,10 +11876,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>440902</v>
+        <v>440894</v>
       </c>
       <c r="R104" t="n">
-        <v>6754164</v>
+        <v>6754104</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11911,7 +11911,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11921,7 +11921,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11930,6 +11930,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11948,10 +11949,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129538088</v>
+        <v>129543217</v>
       </c>
       <c r="B105" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11983,10 +11984,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>441007</v>
+        <v>440902</v>
       </c>
       <c r="R105" t="n">
-        <v>6754124</v>
+        <v>6754164</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12018,7 +12019,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12028,7 +12029,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12043,12 +12044,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -12167,10 +12168,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129543247</v>
+        <v>129538088</v>
       </c>
       <c r="B107" t="n">
-        <v>78742</v>
+        <v>79081</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12178,21 +12179,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12202,10 +12203,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>440894</v>
+        <v>441007</v>
       </c>
       <c r="R107" t="n">
-        <v>6754104</v>
+        <v>6754124</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12237,7 +12238,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12247,7 +12248,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12256,19 +12257,18 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>

--- a/artfynd/A 45199-2025 artfynd.xlsx
+++ b/artfynd/A 45199-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129539413</v>
+        <v>129539829</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440775</v>
+        <v>440861</v>
       </c>
       <c r="R2" t="n">
-        <v>6753988</v>
+        <v>6754168</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129539829</v>
+        <v>129539413</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440861</v>
+        <v>440775</v>
       </c>
       <c r="R3" t="n">
-        <v>6754168</v>
+        <v>6753988</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129543240</v>
+        <v>129543238</v>
       </c>
       <c r="B4" t="n">
-        <v>78747</v>
+        <v>91866</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440736</v>
+        <v>440966</v>
       </c>
       <c r="R4" t="n">
-        <v>6754282</v>
+        <v>6754151</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,7 +983,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1002,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129539462</v>
+        <v>129543240</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440787</v>
+        <v>440736</v>
       </c>
       <c r="R5" t="n">
-        <v>6753947</v>
+        <v>6754282</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1082,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,50 +1090,51 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129539852</v>
+        <v>129543168</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>92879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440880</v>
+        <v>440718</v>
       </c>
       <c r="R6" t="n">
-        <v>6754175</v>
+        <v>6754157</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,44 +1204,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129543239</v>
+        <v>129539462</v>
       </c>
       <c r="B7" t="n">
-        <v>80121</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440708</v>
+        <v>440787</v>
       </c>
       <c r="R7" t="n">
-        <v>6754116</v>
+        <v>6753947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1296,12 +1296,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,22 +1311,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129543147</v>
+        <v>129539852</v>
       </c>
       <c r="B8" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1339,21 +1334,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1363,10 +1358,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440701</v>
+        <v>440880</v>
       </c>
       <c r="R8" t="n">
-        <v>6754185</v>
+        <v>6754175</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,7 +1393,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1408,7 +1403,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,44 +1418,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129543238</v>
+        <v>129543239</v>
       </c>
       <c r="B9" t="n">
-        <v>91866</v>
+        <v>80121</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>65</v>
+        <v>6457</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1470,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440966</v>
+        <v>440708</v>
       </c>
       <c r="R9" t="n">
-        <v>6754151</v>
+        <v>6754116</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,7 +1500,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1515,7 +1510,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1542,32 +1542,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129543168</v>
+        <v>129543147</v>
       </c>
       <c r="B10" t="n">
-        <v>92879</v>
+        <v>79700</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440718</v>
+        <v>440701</v>
       </c>
       <c r="R10" t="n">
-        <v>6754157</v>
+        <v>6754185</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,45 +1649,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543158</v>
+        <v>129543183</v>
       </c>
       <c r="B11" t="n">
-        <v>91614</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440892</v>
+        <v>440945</v>
       </c>
       <c r="R11" t="n">
-        <v>6754225</v>
+        <v>6754252</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,7 +1724,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1729,7 +1734,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1756,7 +1761,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129543183</v>
+        <v>129543191</v>
       </c>
       <c r="B12" t="n">
         <v>8450</v>
@@ -1796,10 +1801,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440945</v>
+        <v>440733</v>
       </c>
       <c r="R12" t="n">
-        <v>6754252</v>
+        <v>6754283</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1831,7 +1836,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1841,7 +1846,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1868,7 +1873,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129543191</v>
+        <v>129539316</v>
       </c>
       <c r="B13" t="n">
         <v>8450</v>
@@ -1899,7 +1904,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1908,10 +1913,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440733</v>
+        <v>440779</v>
       </c>
       <c r="R13" t="n">
-        <v>6754283</v>
+        <v>6754008</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,7 +1948,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1953,7 +1958,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1968,62 +1973,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129539316</v>
+        <v>129543158</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>91614</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440779</v>
+        <v>440892</v>
       </c>
       <c r="R14" t="n">
-        <v>6754008</v>
+        <v>6754225</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2080,19 +2080,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129543216</v>
+        <v>129543227</v>
       </c>
       <c r="B15" t="n">
         <v>79081</v>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440945</v>
+        <v>440744</v>
       </c>
       <c r="R15" t="n">
-        <v>6754252</v>
+        <v>6754336</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2199,7 +2199,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129543227</v>
+        <v>129543216</v>
       </c>
       <c r="B16" t="n">
         <v>79081</v>
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440744</v>
+        <v>440945</v>
       </c>
       <c r="R16" t="n">
-        <v>6754336</v>
+        <v>6754252</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2525,38 +2525,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129543195</v>
+        <v>129538905</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440708</v>
+        <v>440970</v>
       </c>
       <c r="R19" t="n">
-        <v>6754371</v>
+        <v>6754114</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2625,62 +2625,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129539529</v>
+        <v>129543219</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440725</v>
+        <v>440890</v>
       </c>
       <c r="R20" t="n">
-        <v>6754011</v>
+        <v>6754082</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2712,7 +2707,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2722,7 +2717,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2737,22 +2732,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129538905</v>
+        <v>129538675</v>
       </c>
       <c r="B21" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2760,39 +2755,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440970</v>
+        <v>440902</v>
       </c>
       <c r="R21" t="n">
-        <v>6754114</v>
+        <v>6754135</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2861,45 +2851,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129543219</v>
+        <v>129543195</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440890</v>
+        <v>440708</v>
       </c>
       <c r="R22" t="n">
-        <v>6754082</v>
+        <v>6754371</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2931,7 +2926,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2941,7 +2936,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2968,45 +2963,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129538675</v>
+        <v>129539529</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440902</v>
+        <v>440725</v>
       </c>
       <c r="R23" t="n">
-        <v>6754135</v>
+        <v>6754011</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3075,7 +3075,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129539521</v>
+        <v>129543229</v>
       </c>
       <c r="B24" t="n">
         <v>79081</v>
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440725</v>
+        <v>440638</v>
       </c>
       <c r="R24" t="n">
-        <v>6754011</v>
+        <v>6754239</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3170,19 +3170,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129543234</v>
+        <v>129543228</v>
       </c>
       <c r="B25" t="n">
         <v>79081</v>
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440834</v>
+        <v>440716</v>
       </c>
       <c r="R25" t="n">
-        <v>6754152</v>
+        <v>6754354</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3289,10 +3289,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129538680</v>
+        <v>129539521</v>
       </c>
       <c r="B26" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3300,39 +3300,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440918</v>
+        <v>440725</v>
       </c>
       <c r="R26" t="n">
-        <v>6754126</v>
+        <v>6754011</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3364,7 +3359,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3374,7 +3369,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3401,7 +3396,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543228</v>
+        <v>129543234</v>
       </c>
       <c r="B27" t="n">
         <v>79081</v>
@@ -3436,10 +3431,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440716</v>
+        <v>440834</v>
       </c>
       <c r="R27" t="n">
-        <v>6754354</v>
+        <v>6754152</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3471,7 +3466,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3481,7 +3476,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3508,10 +3503,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543229</v>
+        <v>129538680</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3519,34 +3514,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440638</v>
+        <v>440918</v>
       </c>
       <c r="R28" t="n">
-        <v>6754239</v>
+        <v>6754126</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3603,19 +3603,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543222</v>
+        <v>129543233</v>
       </c>
       <c r="B29" t="n">
         <v>79081</v>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440728</v>
+        <v>440819</v>
       </c>
       <c r="R29" t="n">
-        <v>6754306</v>
+        <v>6754114</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3722,7 +3722,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129543233</v>
+        <v>129543222</v>
       </c>
       <c r="B30" t="n">
         <v>79081</v>
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440819</v>
+        <v>440728</v>
       </c>
       <c r="R30" t="n">
-        <v>6754114</v>
+        <v>6754306</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4389,45 +4389,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129543235</v>
+        <v>129543190</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440863</v>
+        <v>440773</v>
       </c>
       <c r="R36" t="n">
-        <v>6754131</v>
+        <v>6754088</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4459,7 +4464,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4469,7 +4474,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4607,10 +4612,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129539703</v>
+        <v>129543159</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>91614</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4618,21 +4623,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4642,10 +4647,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440820</v>
+        <v>440738</v>
       </c>
       <c r="R38" t="n">
-        <v>6754096</v>
+        <v>6754021</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4677,7 +4682,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4687,7 +4692,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4702,22 +4707,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129543159</v>
+        <v>129543235</v>
       </c>
       <c r="B39" t="n">
-        <v>91614</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4725,21 +4730,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4749,10 +4754,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440738</v>
+        <v>440863</v>
       </c>
       <c r="R39" t="n">
-        <v>6754021</v>
+        <v>6754131</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4784,7 +4789,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4794,7 +4799,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4821,50 +4826,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543190</v>
+        <v>129539703</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440773</v>
+        <v>440820</v>
       </c>
       <c r="R40" t="n">
-        <v>6754088</v>
+        <v>6754096</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4921,12 +4921,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5045,45 +5045,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129543145</v>
+        <v>129539589</v>
       </c>
       <c r="B42" t="n">
-        <v>79113</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440723</v>
+        <v>440769</v>
       </c>
       <c r="R42" t="n">
-        <v>6754344</v>
+        <v>6754064</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5115,7 +5120,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5125,7 +5130,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5140,19 +5145,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129539589</v>
+        <v>129538433</v>
       </c>
       <c r="B43" t="n">
         <v>8450</v>
@@ -5192,10 +5197,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440769</v>
+        <v>440937</v>
       </c>
       <c r="R43" t="n">
-        <v>6754064</v>
+        <v>6754141</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5227,7 +5232,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5237,7 +5242,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5264,50 +5269,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129538433</v>
+        <v>129543145</v>
       </c>
       <c r="B44" t="n">
-        <v>8450</v>
+        <v>79113</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440937</v>
+        <v>440723</v>
       </c>
       <c r="R44" t="n">
-        <v>6754141</v>
+        <v>6754344</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5364,12 +5364,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5819,10 +5819,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129539404</v>
+        <v>129543236</v>
       </c>
       <c r="B49" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5830,39 +5830,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440775</v>
+        <v>440970</v>
       </c>
       <c r="R49" t="n">
-        <v>6753988</v>
+        <v>6754114</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5894,7 +5889,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5904,7 +5899,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5919,12 +5914,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6038,10 +6033,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129543236</v>
+        <v>129543166</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6049,34 +6044,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440970</v>
+        <v>440772</v>
       </c>
       <c r="R51" t="n">
-        <v>6754114</v>
+        <v>6754089</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6145,7 +6145,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129543166</v>
+        <v>129539404</v>
       </c>
       <c r="B52" t="n">
         <v>57733</v>
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440772</v>
+        <v>440775</v>
       </c>
       <c r="R52" t="n">
-        <v>6754089</v>
+        <v>6753988</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6245,12 +6245,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6914,50 +6914,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129543181</v>
+        <v>129538786</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440990</v>
+        <v>440918</v>
       </c>
       <c r="R59" t="n">
-        <v>6754140</v>
+        <v>6754126</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6989,7 +6984,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6999,7 +6994,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7014,62 +7009,57 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129543197</v>
+        <v>129543213</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440785</v>
+        <v>440996</v>
       </c>
       <c r="R60" t="n">
-        <v>6754107</v>
+        <v>6754160</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7101,7 +7091,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7111,7 +7101,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7138,45 +7128,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129538786</v>
+        <v>129543181</v>
       </c>
       <c r="B61" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>440918</v>
+        <v>440990</v>
       </c>
       <c r="R61" t="n">
-        <v>6754126</v>
+        <v>6754140</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7208,7 +7203,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7218,7 +7213,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7233,57 +7228,62 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129543213</v>
+        <v>129543197</v>
       </c>
       <c r="B62" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>440996</v>
+        <v>440785</v>
       </c>
       <c r="R62" t="n">
-        <v>6754160</v>
+        <v>6754107</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7315,7 +7315,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7460,38 +7460,38 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129543157</v>
+        <v>129543179</v>
       </c>
       <c r="B64" t="n">
-        <v>57896</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7500,10 +7500,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440759</v>
+        <v>440821</v>
       </c>
       <c r="R64" t="n">
-        <v>6754342</v>
+        <v>6754050</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7572,45 +7572,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129539371</v>
+        <v>129543176</v>
       </c>
       <c r="B65" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440769</v>
+        <v>440820</v>
       </c>
       <c r="R65" t="n">
-        <v>6754008</v>
+        <v>6754121</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7642,7 +7647,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7652,7 +7657,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7667,19 +7672,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129543179</v>
+        <v>129543192</v>
       </c>
       <c r="B66" t="n">
         <v>8450</v>
@@ -7719,10 +7724,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440821</v>
+        <v>440742</v>
       </c>
       <c r="R66" t="n">
-        <v>6754050</v>
+        <v>6754310</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7754,7 +7759,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7764,7 +7769,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7791,50 +7796,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129543176</v>
+        <v>129539371</v>
       </c>
       <c r="B67" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>440820</v>
+        <v>440769</v>
       </c>
       <c r="R67" t="n">
-        <v>6754121</v>
+        <v>6754008</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7891,50 +7891,50 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129543192</v>
+        <v>129543157</v>
       </c>
       <c r="B68" t="n">
-        <v>8450</v>
+        <v>57896</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7943,10 +7943,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440742</v>
+        <v>440759</v>
       </c>
       <c r="R68" t="n">
-        <v>6754310</v>
+        <v>6754342</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8015,10 +8015,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129543225</v>
+        <v>129543141</v>
       </c>
       <c r="B69" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8026,21 +8026,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8050,10 +8050,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440764</v>
+        <v>440974</v>
       </c>
       <c r="R69" t="n">
-        <v>6754320</v>
+        <v>6754141</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8229,10 +8229,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129543246</v>
+        <v>129543225</v>
       </c>
       <c r="B71" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8240,21 +8240,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8264,10 +8264,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>440893</v>
+        <v>440764</v>
       </c>
       <c r="R71" t="n">
-        <v>6754230</v>
+        <v>6754320</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8299,7 +8299,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8318,7 +8318,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8337,10 +8336,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129543141</v>
+        <v>129538126</v>
       </c>
       <c r="B72" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8348,21 +8347,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8372,10 +8371,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>440974</v>
+        <v>441002</v>
       </c>
       <c r="R72" t="n">
-        <v>6754141</v>
+        <v>6754112</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8407,7 +8406,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8417,7 +8416,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8432,22 +8431,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129538126</v>
+        <v>129543143</v>
       </c>
       <c r="B73" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8455,21 +8454,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8479,10 +8478,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>441002</v>
+        <v>440893</v>
       </c>
       <c r="R73" t="n">
-        <v>6754112</v>
+        <v>6754230</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8514,7 +8513,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8524,7 +8523,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8539,22 +8538,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129543143</v>
+        <v>129543224</v>
       </c>
       <c r="B74" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8562,21 +8561,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8586,10 +8585,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>440893</v>
+        <v>440774</v>
       </c>
       <c r="R74" t="n">
-        <v>6754230</v>
+        <v>6754313</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8621,7 +8620,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8631,7 +8630,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8658,10 +8657,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129543224</v>
+        <v>129543246</v>
       </c>
       <c r="B75" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8669,21 +8668,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8693,10 +8692,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>440774</v>
+        <v>440893</v>
       </c>
       <c r="R75" t="n">
-        <v>6754313</v>
+        <v>6754230</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8728,7 +8727,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8738,7 +8737,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8747,6 +8746,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -9101,32 +9101,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129543154</v>
+        <v>129543164</v>
       </c>
       <c r="B79" t="n">
-        <v>90625</v>
+        <v>80215</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1962</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9136,10 +9136,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>440770</v>
+        <v>440708</v>
       </c>
       <c r="R79" t="n">
-        <v>6754101</v>
+        <v>6754116</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9171,7 +9171,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9181,7 +9181,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9208,10 +9213,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129543164</v>
+        <v>129543155</v>
       </c>
       <c r="B80" t="n">
-        <v>80215</v>
+        <v>56926</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9219,34 +9224,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>440708</v>
+        <v>440878</v>
       </c>
       <c r="R80" t="n">
-        <v>6754116</v>
+        <v>6754126</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9278,7 +9288,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9288,12 +9298,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9320,10 +9325,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129543215</v>
+        <v>129543154</v>
       </c>
       <c r="B81" t="n">
-        <v>79081</v>
+        <v>90625</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9331,21 +9336,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9355,10 +9360,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>440930</v>
+        <v>440770</v>
       </c>
       <c r="R81" t="n">
-        <v>6754182</v>
+        <v>6754101</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9390,7 +9395,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9400,7 +9405,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9427,7 +9432,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129543221</v>
+        <v>129543215</v>
       </c>
       <c r="B82" t="n">
         <v>79081</v>
@@ -9462,10 +9467,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>440739</v>
+        <v>440930</v>
       </c>
       <c r="R82" t="n">
-        <v>6754147</v>
+        <v>6754182</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9497,7 +9502,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9507,7 +9512,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9534,50 +9539,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129543155</v>
+        <v>129543221</v>
       </c>
       <c r="B83" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>440878</v>
+        <v>440739</v>
       </c>
       <c r="R83" t="n">
-        <v>6754126</v>
+        <v>6754147</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10201,10 +10201,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129538100</v>
+        <v>129543223</v>
       </c>
       <c r="B89" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10212,21 +10212,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>441007</v>
+        <v>440754</v>
       </c>
       <c r="R89" t="n">
-        <v>6754124</v>
+        <v>6754304</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10271,7 +10271,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10296,22 +10296,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129538198</v>
+        <v>129538100</v>
       </c>
       <c r="B90" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10319,21 +10319,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10343,10 +10343,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>440969</v>
+        <v>441007</v>
       </c>
       <c r="R90" t="n">
-        <v>6754129</v>
+        <v>6754124</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10415,7 +10415,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129543223</v>
+        <v>129538198</v>
       </c>
       <c r="B91" t="n">
         <v>79081</v>
@@ -10450,10 +10450,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>440754</v>
+        <v>440969</v>
       </c>
       <c r="R91" t="n">
-        <v>6754304</v>
+        <v>6754129</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10485,7 +10485,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10495,7 +10495,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10510,12 +10510,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10848,7 +10848,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129543231</v>
+        <v>129543232</v>
       </c>
       <c r="B95" t="n">
         <v>79081</v>
@@ -10883,10 +10883,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>440769</v>
+        <v>440798</v>
       </c>
       <c r="R95" t="n">
-        <v>6754066</v>
+        <v>6754119</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10918,7 +10918,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10928,7 +10928,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11062,7 +11062,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129543232</v>
+        <v>129543231</v>
       </c>
       <c r="B97" t="n">
         <v>79081</v>
@@ -11097,10 +11097,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>440798</v>
+        <v>440769</v>
       </c>
       <c r="R97" t="n">
-        <v>6754119</v>
+        <v>6754066</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11132,7 +11132,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12056,10 +12056,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129538156</v>
+        <v>129538088</v>
       </c>
       <c r="B106" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12067,39 +12067,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>440982</v>
+        <v>441007</v>
       </c>
       <c r="R106" t="n">
-        <v>6754123</v>
+        <v>6754124</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12168,10 +12163,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129538088</v>
+        <v>129538156</v>
       </c>
       <c r="B107" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12179,34 +12174,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>441007</v>
+        <v>440982</v>
       </c>
       <c r="R107" t="n">
-        <v>6754124</v>
+        <v>6754123</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 45199-2025 artfynd.xlsx
+++ b/artfynd/A 45199-2025 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129539829</v>
+        <v>129539413</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440861</v>
+        <v>440775</v>
       </c>
       <c r="R2" t="n">
-        <v>6754168</v>
+        <v>6753988</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,50 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129539413</v>
+        <v>129539829</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440775</v>
+        <v>440861</v>
       </c>
       <c r="R3" t="n">
-        <v>6753988</v>
+        <v>6754168</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,45 +894,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129543238</v>
+        <v>129543183</v>
       </c>
       <c r="B4" t="n">
-        <v>91866</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440966</v>
+        <v>440945</v>
       </c>
       <c r="R4" t="n">
-        <v>6754151</v>
+        <v>6754252</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,45 +1006,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129543240</v>
+        <v>129543191</v>
       </c>
       <c r="B5" t="n">
-        <v>78747</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440736</v>
+        <v>440733</v>
       </c>
       <c r="R5" t="n">
-        <v>6754282</v>
+        <v>6754283</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,7 +1100,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1109,45 +1118,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129543168</v>
+        <v>129539316</v>
       </c>
       <c r="B6" t="n">
-        <v>92879</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4365</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440718</v>
+        <v>440779</v>
       </c>
       <c r="R6" t="n">
-        <v>6754157</v>
+        <v>6754008</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1189,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,44 +1218,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129539462</v>
+        <v>129543168</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>92879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440787</v>
+        <v>440718</v>
       </c>
       <c r="R7" t="n">
-        <v>6753947</v>
+        <v>6754157</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1296,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,22 +1325,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129539852</v>
+        <v>129543158</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>91614</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1334,21 +1348,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1358,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440880</v>
+        <v>440892</v>
       </c>
       <c r="R8" t="n">
-        <v>6754175</v>
+        <v>6754225</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1403,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1418,12 +1432,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1649,50 +1663,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543183</v>
+        <v>129539852</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440945</v>
+        <v>440880</v>
       </c>
       <c r="R11" t="n">
-        <v>6754252</v>
+        <v>6754175</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1733,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1734,7 +1743,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1749,62 +1758,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129543191</v>
+        <v>129539462</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440733</v>
+        <v>440787</v>
       </c>
       <c r="R12" t="n">
-        <v>6754283</v>
+        <v>6753947</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,7 +1840,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1846,7 +1850,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1861,62 +1865,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129539316</v>
+        <v>129543240</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>78747</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440779</v>
+        <v>440736</v>
       </c>
       <c r="R13" t="n">
-        <v>6754008</v>
+        <v>6754282</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,7 +1947,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1958,7 +1957,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,50 +1966,51 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129543158</v>
+        <v>129543238</v>
       </c>
       <c r="B14" t="n">
-        <v>91614</v>
+        <v>91866</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>65</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440892</v>
+        <v>440966</v>
       </c>
       <c r="R14" t="n">
-        <v>6754225</v>
+        <v>6754151</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2092,32 +2092,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129543227</v>
+        <v>129539028</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440744</v>
+        <v>440970</v>
       </c>
       <c r="R15" t="n">
-        <v>6754336</v>
+        <v>6754114</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,57 +2187,62 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129543216</v>
+        <v>129543182</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440945</v>
+        <v>440934</v>
       </c>
       <c r="R16" t="n">
-        <v>6754252</v>
+        <v>6754244</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2306,32 +2311,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129539028</v>
+        <v>129543216</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2341,10 +2346,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440970</v>
+        <v>440945</v>
       </c>
       <c r="R17" t="n">
-        <v>6754114</v>
+        <v>6754252</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2376,7 +2381,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2386,7 +2391,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2401,62 +2406,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543182</v>
+        <v>129543227</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440934</v>
+        <v>440744</v>
       </c>
       <c r="R18" t="n">
-        <v>6754244</v>
+        <v>6754336</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2525,38 +2525,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129538905</v>
+        <v>129539529</v>
       </c>
       <c r="B19" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440970</v>
+        <v>440725</v>
       </c>
       <c r="R19" t="n">
-        <v>6754114</v>
+        <v>6754011</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2637,45 +2637,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129543219</v>
+        <v>129543195</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440890</v>
+        <v>440708</v>
       </c>
       <c r="R20" t="n">
-        <v>6754082</v>
+        <v>6754371</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2707,7 +2712,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2717,7 +2722,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2851,38 +2856,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129543195</v>
+        <v>129538905</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2891,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440708</v>
+        <v>440970</v>
       </c>
       <c r="R22" t="n">
-        <v>6754371</v>
+        <v>6754114</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2926,7 +2931,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2936,7 +2941,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2951,62 +2956,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129539529</v>
+        <v>129543219</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440725</v>
+        <v>440890</v>
       </c>
       <c r="R23" t="n">
-        <v>6754011</v>
+        <v>6754082</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3063,19 +3063,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129543229</v>
+        <v>129543234</v>
       </c>
       <c r="B24" t="n">
         <v>79081</v>
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440638</v>
+        <v>440834</v>
       </c>
       <c r="R24" t="n">
-        <v>6754239</v>
+        <v>6754152</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3182,7 +3182,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129543228</v>
+        <v>129539521</v>
       </c>
       <c r="B25" t="n">
         <v>79081</v>
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440716</v>
+        <v>440725</v>
       </c>
       <c r="R25" t="n">
-        <v>6754354</v>
+        <v>6754011</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3277,19 +3277,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129539521</v>
+        <v>129543228</v>
       </c>
       <c r="B26" t="n">
         <v>79081</v>
@@ -3324,10 +3324,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440725</v>
+        <v>440716</v>
       </c>
       <c r="R26" t="n">
-        <v>6754011</v>
+        <v>6754354</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3384,19 +3384,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543234</v>
+        <v>129543229</v>
       </c>
       <c r="B27" t="n">
         <v>79081</v>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440834</v>
+        <v>440638</v>
       </c>
       <c r="R27" t="n">
-        <v>6754152</v>
+        <v>6754239</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3615,45 +3615,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543233</v>
+        <v>129543188</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440819</v>
+        <v>440824</v>
       </c>
       <c r="R29" t="n">
-        <v>6754114</v>
+        <v>6754063</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3685,7 +3690,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3695,7 +3700,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3722,45 +3727,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129543222</v>
+        <v>129543201</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440728</v>
+        <v>440885</v>
       </c>
       <c r="R30" t="n">
-        <v>6754306</v>
+        <v>6754148</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3792,7 +3802,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3802,7 +3812,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3829,7 +3839,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129543188</v>
+        <v>129543187</v>
       </c>
       <c r="B31" t="n">
         <v>8450</v>
@@ -3869,10 +3879,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440824</v>
+        <v>440887</v>
       </c>
       <c r="R31" t="n">
-        <v>6754063</v>
+        <v>6754181</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3904,7 +3914,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3914,7 +3924,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3941,7 +3951,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129543201</v>
+        <v>129543193</v>
       </c>
       <c r="B32" t="n">
         <v>8450</v>
@@ -3981,10 +3991,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440885</v>
+        <v>440757</v>
       </c>
       <c r="R32" t="n">
-        <v>6754148</v>
+        <v>6754338</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4016,7 +4026,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4026,7 +4036,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4053,50 +4063,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129543187</v>
+        <v>129543222</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440887</v>
+        <v>440728</v>
       </c>
       <c r="R33" t="n">
-        <v>6754181</v>
+        <v>6754306</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4128,7 +4133,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4138,7 +4143,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4165,50 +4170,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129543193</v>
+        <v>129543233</v>
       </c>
       <c r="B34" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440757</v>
+        <v>440819</v>
       </c>
       <c r="R34" t="n">
-        <v>6754338</v>
+        <v>6754114</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4389,50 +4389,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129543190</v>
+        <v>129543235</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440773</v>
+        <v>440863</v>
       </c>
       <c r="R36" t="n">
-        <v>6754088</v>
+        <v>6754131</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4464,7 +4459,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4474,7 +4469,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4501,10 +4496,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129539754</v>
+        <v>129539703</v>
       </c>
       <c r="B37" t="n">
-        <v>91614</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4512,28 +4507,24 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
@@ -4612,45 +4603,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129543159</v>
+        <v>129543190</v>
       </c>
       <c r="B38" t="n">
-        <v>91614</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440738</v>
+        <v>440773</v>
       </c>
       <c r="R38" t="n">
-        <v>6754021</v>
+        <v>6754088</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4682,7 +4678,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4692,7 +4688,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4719,10 +4715,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129543235</v>
+        <v>129539754</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>91614</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4730,34 +4726,38 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440863</v>
+        <v>440820</v>
       </c>
       <c r="R39" t="n">
-        <v>6754131</v>
+        <v>6754096</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4814,22 +4814,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129539703</v>
+        <v>129543159</v>
       </c>
       <c r="B40" t="n">
-        <v>79081</v>
+        <v>91614</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4837,21 +4837,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440820</v>
+        <v>440738</v>
       </c>
       <c r="R40" t="n">
-        <v>6754096</v>
+        <v>6754021</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4921,12 +4921,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5045,50 +5045,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129539589</v>
+        <v>129543145</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>79113</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440769</v>
+        <v>440723</v>
       </c>
       <c r="R42" t="n">
-        <v>6754064</v>
+        <v>6754344</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5120,7 +5115,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5130,7 +5125,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5145,19 +5140,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129538433</v>
+        <v>129539589</v>
       </c>
       <c r="B43" t="n">
         <v>8450</v>
@@ -5197,10 +5192,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440937</v>
+        <v>440769</v>
       </c>
       <c r="R43" t="n">
-        <v>6754141</v>
+        <v>6754064</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5232,7 +5227,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5242,7 +5237,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5269,45 +5264,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129543145</v>
+        <v>129538433</v>
       </c>
       <c r="B44" t="n">
-        <v>79113</v>
+        <v>8450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440723</v>
+        <v>440937</v>
       </c>
       <c r="R44" t="n">
-        <v>6754344</v>
+        <v>6754141</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5364,62 +5364,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129543194</v>
+        <v>129543226</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440745</v>
+        <v>440757</v>
       </c>
       <c r="R45" t="n">
-        <v>6754333</v>
+        <v>6754337</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5451,7 +5446,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5461,7 +5456,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5488,7 +5483,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129539814</v>
+        <v>129543194</v>
       </c>
       <c r="B46" t="n">
         <v>8450</v>
@@ -5528,10 +5523,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440861</v>
+        <v>440745</v>
       </c>
       <c r="R46" t="n">
-        <v>6754168</v>
+        <v>6754333</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5563,7 +5558,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5573,7 +5568,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5588,19 +5583,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129538170</v>
+        <v>129539814</v>
       </c>
       <c r="B47" t="n">
         <v>8450</v>
@@ -5631,7 +5626,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5640,10 +5635,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440982</v>
+        <v>440861</v>
       </c>
       <c r="R47" t="n">
-        <v>6754123</v>
+        <v>6754168</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5675,7 +5670,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5685,7 +5680,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5712,45 +5707,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129543226</v>
+        <v>129538170</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440757</v>
+        <v>440982</v>
       </c>
       <c r="R48" t="n">
-        <v>6754337</v>
+        <v>6754123</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5807,57 +5807,62 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129543236</v>
+        <v>129543198</v>
       </c>
       <c r="B49" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440970</v>
+        <v>440824</v>
       </c>
       <c r="R49" t="n">
-        <v>6754114</v>
+        <v>6754177</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5889,7 +5894,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5899,7 +5904,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6033,10 +6038,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129543166</v>
+        <v>129543236</v>
       </c>
       <c r="B51" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6044,39 +6049,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440772</v>
+        <v>440970</v>
       </c>
       <c r="R51" t="n">
-        <v>6754089</v>
+        <v>6754114</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6257,38 +6257,38 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129543198</v>
+        <v>129543166</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6297,10 +6297,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440824</v>
+        <v>440772</v>
       </c>
       <c r="R53" t="n">
-        <v>6754177</v>
+        <v>6754089</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6369,10 +6369,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129538554</v>
+        <v>129543230</v>
       </c>
       <c r="B54" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6380,21 +6380,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6404,10 +6404,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440919</v>
+        <v>440779</v>
       </c>
       <c r="R54" t="n">
-        <v>6754174</v>
+        <v>6754063</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6464,22 +6464,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129543230</v>
+        <v>129538554</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6487,21 +6487,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6511,10 +6511,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440779</v>
+        <v>440919</v>
       </c>
       <c r="R55" t="n">
-        <v>6754063</v>
+        <v>6754174</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6571,12 +6571,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6807,10 +6807,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129543144</v>
+        <v>129538786</v>
       </c>
       <c r="B58" t="n">
-        <v>91516</v>
+        <v>79081</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6818,21 +6818,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440718</v>
+        <v>440918</v>
       </c>
       <c r="R58" t="n">
-        <v>6754215</v>
+        <v>6754126</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6902,19 +6902,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129538786</v>
+        <v>129543213</v>
       </c>
       <c r="B59" t="n">
         <v>79081</v>
@@ -6949,10 +6949,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440918</v>
+        <v>440996</v>
       </c>
       <c r="R59" t="n">
-        <v>6754126</v>
+        <v>6754160</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7009,22 +7009,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129543213</v>
+        <v>129543144</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>91516</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7032,21 +7032,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440996</v>
+        <v>440718</v>
       </c>
       <c r="R60" t="n">
-        <v>6754160</v>
+        <v>6754215</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7352,10 +7352,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129543245</v>
+        <v>129543157</v>
       </c>
       <c r="B63" t="n">
-        <v>78747</v>
+        <v>57896</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7363,34 +7363,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440986</v>
+        <v>440759</v>
       </c>
       <c r="R63" t="n">
-        <v>6754157</v>
+        <v>6754342</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7422,7 +7427,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7432,7 +7437,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7441,7 +7446,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7460,7 +7464,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129543179</v>
+        <v>129543176</v>
       </c>
       <c r="B64" t="n">
         <v>8450</v>
@@ -7491,7 +7495,7 @@
       <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7500,10 +7504,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440821</v>
+        <v>440820</v>
       </c>
       <c r="R64" t="n">
-        <v>6754050</v>
+        <v>6754121</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7535,7 +7539,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7545,7 +7549,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7572,7 +7576,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129543176</v>
+        <v>129543192</v>
       </c>
       <c r="B65" t="n">
         <v>8450</v>
@@ -7603,7 +7607,7 @@
       <c r="I65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7612,10 +7616,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440820</v>
+        <v>440742</v>
       </c>
       <c r="R65" t="n">
-        <v>6754121</v>
+        <v>6754310</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7647,7 +7651,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7657,7 +7661,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7684,50 +7688,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129543192</v>
+        <v>129539371</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440742</v>
+        <v>440769</v>
       </c>
       <c r="R66" t="n">
-        <v>6754310</v>
+        <v>6754008</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7759,7 +7758,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7769,7 +7768,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7784,22 +7783,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129539371</v>
+        <v>129543245</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7807,21 +7806,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7831,10 +7830,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>440769</v>
+        <v>440986</v>
       </c>
       <c r="R67" t="n">
-        <v>6754008</v>
+        <v>6754157</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7866,7 +7865,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7876,7 +7875,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7885,56 +7884,57 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129543157</v>
+        <v>129543179</v>
       </c>
       <c r="B68" t="n">
-        <v>57896</v>
+        <v>8450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7943,10 +7943,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440759</v>
+        <v>440821</v>
       </c>
       <c r="R68" t="n">
-        <v>6754342</v>
+        <v>6754050</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8015,10 +8015,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129543141</v>
+        <v>129543246</v>
       </c>
       <c r="B69" t="n">
-        <v>79700</v>
+        <v>78747</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8026,21 +8026,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8050,10 +8050,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440974</v>
+        <v>440893</v>
       </c>
       <c r="R69" t="n">
-        <v>6754141</v>
+        <v>6754230</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8104,6 +8104,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8122,45 +8123,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129543218</v>
+        <v>129543178</v>
       </c>
       <c r="B70" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440888</v>
+        <v>440816</v>
       </c>
       <c r="R70" t="n">
-        <v>6754157</v>
+        <v>6754178</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8192,7 +8198,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8202,7 +8208,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8229,45 +8235,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129543225</v>
+        <v>129543199</v>
       </c>
       <c r="B71" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>440764</v>
+        <v>440855</v>
       </c>
       <c r="R71" t="n">
-        <v>6754320</v>
+        <v>6754166</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8299,7 +8310,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8309,7 +8320,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8336,10 +8347,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129538126</v>
+        <v>129538247</v>
       </c>
       <c r="B72" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8347,34 +8358,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>441002</v>
+        <v>440944</v>
       </c>
       <c r="R72" t="n">
-        <v>6754112</v>
+        <v>6754122</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8443,7 +8459,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129543143</v>
+        <v>129543141</v>
       </c>
       <c r="B73" t="n">
         <v>79700</v>
@@ -8478,10 +8494,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>440893</v>
+        <v>440974</v>
       </c>
       <c r="R73" t="n">
-        <v>6754230</v>
+        <v>6754141</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8513,7 +8529,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8523,7 +8539,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8550,7 +8566,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129543224</v>
+        <v>129543225</v>
       </c>
       <c r="B74" t="n">
         <v>79081</v>
@@ -8585,10 +8601,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>440774</v>
+        <v>440764</v>
       </c>
       <c r="R74" t="n">
-        <v>6754313</v>
+        <v>6754320</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8657,10 +8673,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129543246</v>
+        <v>129543218</v>
       </c>
       <c r="B75" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8668,21 +8684,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8692,10 +8708,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>440893</v>
+        <v>440888</v>
       </c>
       <c r="R75" t="n">
-        <v>6754230</v>
+        <v>6754157</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8727,7 +8743,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8737,7 +8753,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8746,7 +8762,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8765,10 +8780,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129538247</v>
+        <v>129538126</v>
       </c>
       <c r="B76" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8776,39 +8791,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>440944</v>
+        <v>441002</v>
       </c>
       <c r="R76" t="n">
-        <v>6754122</v>
+        <v>6754112</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8877,50 +8887,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129543178</v>
+        <v>129543143</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>440816</v>
+        <v>440893</v>
       </c>
       <c r="R77" t="n">
-        <v>6754178</v>
+        <v>6754230</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8952,7 +8957,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8962,7 +8967,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8989,50 +8994,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129543199</v>
+        <v>129543224</v>
       </c>
       <c r="B78" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>440855</v>
+        <v>440774</v>
       </c>
       <c r="R78" t="n">
-        <v>6754166</v>
+        <v>6754313</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9101,32 +9101,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129543164</v>
+        <v>129543154</v>
       </c>
       <c r="B79" t="n">
-        <v>80215</v>
+        <v>90625</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>1962</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9136,10 +9136,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>440708</v>
+        <v>440770</v>
       </c>
       <c r="R79" t="n">
-        <v>6754116</v>
+        <v>6754101</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9171,7 +9171,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9181,12 +9181,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9325,45 +9320,50 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129543154</v>
+        <v>129543203</v>
       </c>
       <c r="B81" t="n">
-        <v>90625</v>
+        <v>8450</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>440770</v>
+        <v>440946</v>
       </c>
       <c r="R81" t="n">
-        <v>6754101</v>
+        <v>6754123</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9646,10 +9646,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129538573</v>
+        <v>129543164</v>
       </c>
       <c r="B84" t="n">
-        <v>8450</v>
+        <v>80215</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9657,39 +9657,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>440932</v>
+        <v>440708</v>
       </c>
       <c r="R84" t="n">
-        <v>6754178</v>
+        <v>6754116</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9721,7 +9716,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9731,7 +9726,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9746,19 +9746,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129543202</v>
+        <v>129538573</v>
       </c>
       <c r="B85" t="n">
         <v>8450</v>
@@ -9789,7 +9789,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9798,10 +9798,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>440918</v>
+        <v>440932</v>
       </c>
       <c r="R85" t="n">
-        <v>6754161</v>
+        <v>6754178</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9858,19 +9858,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129543173</v>
+        <v>129543202</v>
       </c>
       <c r="B86" t="n">
         <v>8450</v>
@@ -9901,7 +9901,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9910,10 +9910,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>440917</v>
+        <v>440918</v>
       </c>
       <c r="R86" t="n">
-        <v>6754255</v>
+        <v>6754161</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9982,7 +9982,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129543203</v>
+        <v>129543173</v>
       </c>
       <c r="B87" t="n">
         <v>8450</v>
@@ -10013,7 +10013,7 @@
       <c r="I87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10022,10 +10022,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>440946</v>
+        <v>440917</v>
       </c>
       <c r="R87" t="n">
-        <v>6754123</v>
+        <v>6754255</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10201,7 +10201,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129543223</v>
+        <v>129538198</v>
       </c>
       <c r="B89" t="n">
         <v>79081</v>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>440754</v>
+        <v>440969</v>
       </c>
       <c r="R89" t="n">
-        <v>6754304</v>
+        <v>6754129</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10271,7 +10271,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10296,22 +10296,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129538100</v>
+        <v>129543223</v>
       </c>
       <c r="B90" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10319,21 +10319,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10343,10 +10343,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>441007</v>
+        <v>440754</v>
       </c>
       <c r="R90" t="n">
-        <v>6754124</v>
+        <v>6754304</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10378,7 +10378,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10403,22 +10403,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129538198</v>
+        <v>129538100</v>
       </c>
       <c r="B91" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10426,21 +10426,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10450,10 +10450,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>440969</v>
+        <v>441007</v>
       </c>
       <c r="R91" t="n">
-        <v>6754129</v>
+        <v>6754124</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10522,10 +10522,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129543153</v>
+        <v>129543142</v>
       </c>
       <c r="B92" t="n">
-        <v>90625</v>
+        <v>79700</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10533,21 +10533,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10557,10 +10557,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>440976</v>
+        <v>440949</v>
       </c>
       <c r="R92" t="n">
-        <v>6754143</v>
+        <v>6754170</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10602,7 +10602,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10629,10 +10629,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129543142</v>
+        <v>129543153</v>
       </c>
       <c r="B93" t="n">
-        <v>79700</v>
+        <v>90625</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10640,21 +10640,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10664,10 +10664,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>440949</v>
+        <v>440976</v>
       </c>
       <c r="R93" t="n">
-        <v>6754170</v>
+        <v>6754143</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10709,7 +10709,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10848,7 +10848,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129543232</v>
+        <v>129543231</v>
       </c>
       <c r="B95" t="n">
         <v>79081</v>
@@ -10883,10 +10883,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>440798</v>
+        <v>440769</v>
       </c>
       <c r="R95" t="n">
-        <v>6754119</v>
+        <v>6754066</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10918,7 +10918,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10928,7 +10928,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10955,7 +10955,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129543214</v>
+        <v>129543232</v>
       </c>
       <c r="B96" t="n">
         <v>79081</v>
@@ -10990,10 +10990,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>440948</v>
+        <v>440798</v>
       </c>
       <c r="R96" t="n">
-        <v>6754156</v>
+        <v>6754119</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11062,7 +11062,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129543231</v>
+        <v>129543214</v>
       </c>
       <c r="B97" t="n">
         <v>79081</v>
@@ -11097,10 +11097,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>440769</v>
+        <v>440948</v>
       </c>
       <c r="R97" t="n">
-        <v>6754066</v>
+        <v>6754156</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11132,7 +11132,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11276,38 +11276,38 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129543170</v>
+        <v>129543189</v>
       </c>
       <c r="B99" t="n">
-        <v>57736</v>
+        <v>8450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -11316,10 +11316,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>440677</v>
+        <v>440793</v>
       </c>
       <c r="R99" t="n">
-        <v>6754247</v>
+        <v>6754070</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11361,12 +11361,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11617,7 +11612,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129543189</v>
+        <v>129538851</v>
       </c>
       <c r="B102" t="n">
         <v>8450</v>
@@ -11648,7 +11643,7 @@
       <c r="I102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -11657,10 +11652,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>440793</v>
+        <v>440918</v>
       </c>
       <c r="R102" t="n">
-        <v>6754070</v>
+        <v>6754126</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11692,7 +11687,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11702,7 +11697,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11717,50 +11712,50 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129538851</v>
+        <v>129543170</v>
       </c>
       <c r="B103" t="n">
-        <v>8450</v>
+        <v>57736</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11769,10 +11764,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>440918</v>
+        <v>440677</v>
       </c>
       <c r="R103" t="n">
-        <v>6754126</v>
+        <v>6754247</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11804,7 +11799,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11814,7 +11809,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11829,12 +11829,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -11949,10 +11949,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129543217</v>
+        <v>129538156</v>
       </c>
       <c r="B105" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11960,34 +11960,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>440902</v>
+        <v>440982</v>
       </c>
       <c r="R105" t="n">
-        <v>6754164</v>
+        <v>6754123</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12019,7 +12024,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12029,7 +12034,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12044,19 +12049,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129538088</v>
+        <v>129543217</v>
       </c>
       <c r="B106" t="n">
         <v>79081</v>
@@ -12091,10 +12096,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>441007</v>
+        <v>440902</v>
       </c>
       <c r="R106" t="n">
-        <v>6754124</v>
+        <v>6754164</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12126,7 +12131,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12136,7 +12141,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12151,22 +12156,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129538156</v>
+        <v>129538088</v>
       </c>
       <c r="B107" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12174,39 +12179,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>440982</v>
+        <v>441007</v>
       </c>
       <c r="R107" t="n">
-        <v>6754123</v>
+        <v>6754124</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 45199-2025 artfynd.xlsx
+++ b/artfynd/A 45199-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129539413</v>
+        <v>129539829</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440775</v>
+        <v>440861</v>
       </c>
       <c r="R2" t="n">
-        <v>6753988</v>
+        <v>6754168</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129539829</v>
+        <v>129539413</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440861</v>
+        <v>440775</v>
       </c>
       <c r="R3" t="n">
-        <v>6754168</v>
+        <v>6753988</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,50 +894,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129543183</v>
+        <v>129543168</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>92879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>4365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440945</v>
+        <v>440718</v>
       </c>
       <c r="R4" t="n">
-        <v>6754252</v>
+        <v>6754157</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,50 +1001,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129543191</v>
+        <v>129543158</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>91614</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440733</v>
+        <v>440892</v>
       </c>
       <c r="R5" t="n">
-        <v>6754283</v>
+        <v>6754225</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,7 +1108,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129539316</v>
+        <v>129543183</v>
       </c>
       <c r="B6" t="n">
         <v>8450</v>
@@ -1149,7 +1139,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1158,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440779</v>
+        <v>440945</v>
       </c>
       <c r="R6" t="n">
-        <v>6754008</v>
+        <v>6754252</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,57 +1208,62 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129543168</v>
+        <v>129543191</v>
       </c>
       <c r="B7" t="n">
-        <v>92879</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440718</v>
+        <v>440733</v>
       </c>
       <c r="R7" t="n">
-        <v>6754157</v>
+        <v>6754283</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,45 +1332,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129543158</v>
+        <v>129539316</v>
       </c>
       <c r="B8" t="n">
-        <v>91614</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440892</v>
+        <v>440779</v>
       </c>
       <c r="R8" t="n">
-        <v>6754225</v>
+        <v>6754008</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,44 +1432,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129543239</v>
+        <v>129543240</v>
       </c>
       <c r="B9" t="n">
-        <v>80121</v>
+        <v>78747</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6457</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440708</v>
+        <v>440736</v>
       </c>
       <c r="R9" t="n">
-        <v>6754116</v>
+        <v>6754282</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1524,12 +1524,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,6 +1533,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1556,32 +1552,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129543147</v>
+        <v>129543238</v>
       </c>
       <c r="B10" t="n">
-        <v>79700</v>
+        <v>91866</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440701</v>
+        <v>440966</v>
       </c>
       <c r="R10" t="n">
-        <v>6754185</v>
+        <v>6754151</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,7 +1622,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1636,7 +1632,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1877,32 +1873,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129543240</v>
+        <v>129543239</v>
       </c>
       <c r="B13" t="n">
-        <v>78747</v>
+        <v>80121</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6457</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1912,10 +1908,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440736</v>
+        <v>440708</v>
       </c>
       <c r="R13" t="n">
-        <v>6754282</v>
+        <v>6754116</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,7 +1943,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1957,7 +1953,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1966,7 +1967,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1985,32 +1985,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129543238</v>
+        <v>129543147</v>
       </c>
       <c r="B14" t="n">
-        <v>91866</v>
+        <v>79700</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440966</v>
+        <v>440701</v>
       </c>
       <c r="R14" t="n">
-        <v>6754151</v>
+        <v>6754185</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2092,32 +2092,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129539028</v>
+        <v>129543216</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440970</v>
+        <v>440945</v>
       </c>
       <c r="R15" t="n">
-        <v>6754114</v>
+        <v>6754252</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,62 +2187,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129543182</v>
+        <v>129543227</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440934</v>
+        <v>440744</v>
       </c>
       <c r="R16" t="n">
-        <v>6754244</v>
+        <v>6754336</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,7 +2269,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2284,7 +2279,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2311,32 +2306,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129543216</v>
+        <v>129539028</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2346,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440945</v>
+        <v>440970</v>
       </c>
       <c r="R17" t="n">
-        <v>6754252</v>
+        <v>6754114</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2381,7 +2376,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2391,7 +2386,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,57 +2401,62 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543227</v>
+        <v>129543182</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440744</v>
+        <v>440934</v>
       </c>
       <c r="R18" t="n">
-        <v>6754336</v>
+        <v>6754244</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2525,50 +2525,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129539529</v>
+        <v>129543219</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440725</v>
+        <v>440890</v>
       </c>
       <c r="R19" t="n">
-        <v>6754011</v>
+        <v>6754082</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2600,7 +2595,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2610,7 +2605,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2625,62 +2620,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129543195</v>
+        <v>129538675</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440708</v>
+        <v>440902</v>
       </c>
       <c r="R20" t="n">
-        <v>6754371</v>
+        <v>6754135</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2712,7 +2702,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2722,7 +2712,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2737,57 +2727,62 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129538675</v>
+        <v>129543195</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440902</v>
+        <v>440708</v>
       </c>
       <c r="R21" t="n">
-        <v>6754135</v>
+        <v>6754371</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2819,7 +2814,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2829,7 +2824,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2844,12 +2839,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2968,45 +2963,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129543219</v>
+        <v>129539529</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440890</v>
+        <v>440725</v>
       </c>
       <c r="R23" t="n">
-        <v>6754082</v>
+        <v>6754011</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3063,12 +3063,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -4063,45 +4063,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129543222</v>
+        <v>129543196</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440728</v>
+        <v>440716</v>
       </c>
       <c r="R33" t="n">
-        <v>6754306</v>
+        <v>6754046</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4133,7 +4138,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4143,7 +4148,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4170,7 +4175,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129543233</v>
+        <v>129543222</v>
       </c>
       <c r="B34" t="n">
         <v>79081</v>
@@ -4205,10 +4210,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440819</v>
+        <v>440728</v>
       </c>
       <c r="R34" t="n">
-        <v>6754114</v>
+        <v>6754306</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4240,7 +4245,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4250,7 +4255,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4277,50 +4282,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129543196</v>
+        <v>129543233</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440716</v>
+        <v>440819</v>
       </c>
       <c r="R35" t="n">
-        <v>6754046</v>
+        <v>6754114</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4389,10 +4389,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129543235</v>
+        <v>129539754</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>91614</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4400,34 +4400,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440863</v>
+        <v>440820</v>
       </c>
       <c r="R36" t="n">
-        <v>6754131</v>
+        <v>6754096</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4459,7 +4463,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4469,7 +4473,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4484,22 +4488,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129539703</v>
+        <v>129543159</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>91614</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4507,21 +4511,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4531,10 +4535,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440820</v>
+        <v>440738</v>
       </c>
       <c r="R37" t="n">
-        <v>6754096</v>
+        <v>6754021</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4566,7 +4570,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4576,7 +4580,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4591,62 +4595,57 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129543190</v>
+        <v>129543235</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440773</v>
+        <v>440863</v>
       </c>
       <c r="R38" t="n">
-        <v>6754088</v>
+        <v>6754131</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4678,7 +4677,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4688,7 +4687,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4715,10 +4714,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129539754</v>
+        <v>129539703</v>
       </c>
       <c r="B39" t="n">
-        <v>91614</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4726,28 +4725,24 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
@@ -4826,10 +4821,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543159</v>
+        <v>129539312</v>
       </c>
       <c r="B40" t="n">
-        <v>91614</v>
+        <v>57733</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4837,34 +4832,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440738</v>
+        <v>440779</v>
       </c>
       <c r="R40" t="n">
-        <v>6754021</v>
+        <v>6754008</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4921,50 +4921,50 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129539312</v>
+        <v>129543190</v>
       </c>
       <c r="B41" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440779</v>
+        <v>440773</v>
       </c>
       <c r="R41" t="n">
-        <v>6754008</v>
+        <v>6754088</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5033,12 +5033,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5819,50 +5819,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129543198</v>
+        <v>129543220</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440824</v>
+        <v>440851</v>
       </c>
       <c r="R49" t="n">
-        <v>6754177</v>
+        <v>6754062</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5894,7 +5889,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5904,7 +5899,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5931,7 +5926,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129543220</v>
+        <v>129543236</v>
       </c>
       <c r="B50" t="n">
         <v>79081</v>
@@ -5966,10 +5961,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440851</v>
+        <v>440970</v>
       </c>
       <c r="R50" t="n">
-        <v>6754062</v>
+        <v>6754114</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6001,7 +5996,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6011,7 +6006,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6038,10 +6033,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129543236</v>
+        <v>129539404</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6049,34 +6044,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440970</v>
+        <v>440775</v>
       </c>
       <c r="R51" t="n">
-        <v>6754114</v>
+        <v>6753988</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6133,19 +6133,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129539404</v>
+        <v>129543166</v>
       </c>
       <c r="B52" t="n">
         <v>57733</v>
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440775</v>
+        <v>440772</v>
       </c>
       <c r="R52" t="n">
-        <v>6753988</v>
+        <v>6754089</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6245,50 +6245,50 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129543166</v>
+        <v>129543198</v>
       </c>
       <c r="B53" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6297,10 +6297,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440772</v>
+        <v>440824</v>
       </c>
       <c r="R53" t="n">
-        <v>6754089</v>
+        <v>6754177</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6369,10 +6369,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129543230</v>
+        <v>129538554</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6380,21 +6380,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6404,10 +6404,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440779</v>
+        <v>440919</v>
       </c>
       <c r="R54" t="n">
-        <v>6754063</v>
+        <v>6754174</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6464,22 +6464,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129538554</v>
+        <v>129543230</v>
       </c>
       <c r="B55" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6487,21 +6487,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6511,10 +6511,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440919</v>
+        <v>440779</v>
       </c>
       <c r="R55" t="n">
-        <v>6754174</v>
+        <v>6754063</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6571,12 +6571,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7021,45 +7021,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129543144</v>
+        <v>129543181</v>
       </c>
       <c r="B60" t="n">
-        <v>91516</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3242</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440718</v>
+        <v>440990</v>
       </c>
       <c r="R60" t="n">
-        <v>6754215</v>
+        <v>6754140</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7091,7 +7096,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7101,7 +7106,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7128,7 +7133,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129543181</v>
+        <v>129543197</v>
       </c>
       <c r="B61" t="n">
         <v>8450</v>
@@ -7168,10 +7173,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>440990</v>
+        <v>440785</v>
       </c>
       <c r="R61" t="n">
-        <v>6754140</v>
+        <v>6754107</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7203,7 +7208,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7213,7 +7218,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7240,50 +7245,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129543197</v>
+        <v>129543144</v>
       </c>
       <c r="B62" t="n">
-        <v>8450</v>
+        <v>91516</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>3242</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>440785</v>
+        <v>440718</v>
       </c>
       <c r="R62" t="n">
-        <v>6754107</v>
+        <v>6754215</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7315,7 +7315,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7352,10 +7352,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129543157</v>
+        <v>129543245</v>
       </c>
       <c r="B63" t="n">
-        <v>57896</v>
+        <v>78747</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7363,39 +7363,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440759</v>
+        <v>440986</v>
       </c>
       <c r="R63" t="n">
-        <v>6754342</v>
+        <v>6754157</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7427,7 +7422,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7437,7 +7432,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7446,6 +7441,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7464,7 +7460,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129543176</v>
+        <v>129543179</v>
       </c>
       <c r="B64" t="n">
         <v>8450</v>
@@ -7495,7 +7491,7 @@
       <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7504,10 +7500,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440820</v>
+        <v>440821</v>
       </c>
       <c r="R64" t="n">
-        <v>6754121</v>
+        <v>6754050</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7539,7 +7535,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7549,7 +7545,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7576,7 +7572,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129543192</v>
+        <v>129543176</v>
       </c>
       <c r="B65" t="n">
         <v>8450</v>
@@ -7607,7 +7603,7 @@
       <c r="I65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7616,10 +7612,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440742</v>
+        <v>440820</v>
       </c>
       <c r="R65" t="n">
-        <v>6754310</v>
+        <v>6754121</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7651,7 +7647,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7661,7 +7657,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7688,45 +7684,50 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129539371</v>
+        <v>129543192</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440769</v>
+        <v>440742</v>
       </c>
       <c r="R66" t="n">
-        <v>6754008</v>
+        <v>6754310</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7758,7 +7759,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7768,7 +7769,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7783,22 +7784,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129543245</v>
+        <v>129539371</v>
       </c>
       <c r="B67" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7806,21 +7807,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7830,10 +7831,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>440986</v>
+        <v>440769</v>
       </c>
       <c r="R67" t="n">
-        <v>6754157</v>
+        <v>6754008</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7865,7 +7866,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7875,7 +7876,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7884,57 +7885,56 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129543179</v>
+        <v>129543157</v>
       </c>
       <c r="B68" t="n">
-        <v>8450</v>
+        <v>57896</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7943,10 +7943,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440821</v>
+        <v>440759</v>
       </c>
       <c r="R68" t="n">
-        <v>6754050</v>
+        <v>6754342</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8123,50 +8123,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129543178</v>
+        <v>129543225</v>
       </c>
       <c r="B70" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440816</v>
+        <v>440764</v>
       </c>
       <c r="R70" t="n">
-        <v>6754178</v>
+        <v>6754320</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8198,7 +8193,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8208,7 +8203,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8235,50 +8230,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129543199</v>
+        <v>129543218</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>440855</v>
+        <v>440888</v>
       </c>
       <c r="R71" t="n">
-        <v>6754166</v>
+        <v>6754157</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8310,7 +8300,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8320,7 +8310,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8347,10 +8337,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129538247</v>
+        <v>129538126</v>
       </c>
       <c r="B72" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8358,39 +8348,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>440944</v>
+        <v>441002</v>
       </c>
       <c r="R72" t="n">
-        <v>6754122</v>
+        <v>6754112</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8459,10 +8444,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129543141</v>
+        <v>129543224</v>
       </c>
       <c r="B73" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8470,21 +8455,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8494,10 +8479,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>440974</v>
+        <v>440774</v>
       </c>
       <c r="R73" t="n">
-        <v>6754141</v>
+        <v>6754313</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8529,7 +8514,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8539,7 +8524,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8566,10 +8551,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129543225</v>
+        <v>129538247</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8577,34 +8562,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>440764</v>
+        <v>440944</v>
       </c>
       <c r="R74" t="n">
-        <v>6754320</v>
+        <v>6754122</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8636,7 +8626,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8646,7 +8636,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8661,22 +8651,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129543218</v>
+        <v>129543141</v>
       </c>
       <c r="B75" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8684,21 +8674,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8708,10 +8698,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>440888</v>
+        <v>440974</v>
       </c>
       <c r="R75" t="n">
-        <v>6754157</v>
+        <v>6754141</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8743,7 +8733,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8753,7 +8743,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8780,10 +8770,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129538126</v>
+        <v>129543143</v>
       </c>
       <c r="B76" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8791,21 +8781,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8815,10 +8805,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>441002</v>
+        <v>440893</v>
       </c>
       <c r="R76" t="n">
-        <v>6754112</v>
+        <v>6754230</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8850,7 +8840,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8860,7 +8850,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8875,57 +8865,62 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129543143</v>
+        <v>129543178</v>
       </c>
       <c r="B77" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>440893</v>
+        <v>440816</v>
       </c>
       <c r="R77" t="n">
-        <v>6754230</v>
+        <v>6754178</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8957,7 +8952,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8967,7 +8962,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8994,45 +8989,50 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129543224</v>
+        <v>129543199</v>
       </c>
       <c r="B78" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>440774</v>
+        <v>440855</v>
       </c>
       <c r="R78" t="n">
-        <v>6754313</v>
+        <v>6754166</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9208,10 +9208,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129543155</v>
+        <v>129543164</v>
       </c>
       <c r="B80" t="n">
-        <v>56926</v>
+        <v>80215</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9219,39 +9219,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>440878</v>
+        <v>440708</v>
       </c>
       <c r="R80" t="n">
-        <v>6754126</v>
+        <v>6754116</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9283,7 +9278,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9293,7 +9288,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9320,50 +9320,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129543203</v>
+        <v>129543215</v>
       </c>
       <c r="B81" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>440946</v>
+        <v>440930</v>
       </c>
       <c r="R81" t="n">
-        <v>6754123</v>
+        <v>6754182</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9395,7 +9390,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9405,7 +9400,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9432,7 +9427,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129543215</v>
+        <v>129543221</v>
       </c>
       <c r="B82" t="n">
         <v>79081</v>
@@ -9467,10 +9462,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>440930</v>
+        <v>440739</v>
       </c>
       <c r="R82" t="n">
-        <v>6754182</v>
+        <v>6754147</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9502,7 +9497,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9512,7 +9507,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9539,45 +9534,50 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129543221</v>
+        <v>129543155</v>
       </c>
       <c r="B83" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>440739</v>
+        <v>440878</v>
       </c>
       <c r="R83" t="n">
-        <v>6754147</v>
+        <v>6754126</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9646,10 +9646,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129543164</v>
+        <v>129538573</v>
       </c>
       <c r="B84" t="n">
-        <v>80215</v>
+        <v>8450</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9657,34 +9657,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6462</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>440708</v>
+        <v>440932</v>
       </c>
       <c r="R84" t="n">
-        <v>6754116</v>
+        <v>6754178</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9716,7 +9721,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9726,12 +9731,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9746,19 +9746,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129538573</v>
+        <v>129543202</v>
       </c>
       <c r="B85" t="n">
         <v>8450</v>
@@ -9789,7 +9789,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9798,10 +9798,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>440932</v>
+        <v>440918</v>
       </c>
       <c r="R85" t="n">
-        <v>6754178</v>
+        <v>6754161</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9858,19 +9858,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129543202</v>
+        <v>129543173</v>
       </c>
       <c r="B86" t="n">
         <v>8450</v>
@@ -9901,7 +9901,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9910,10 +9910,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>440918</v>
+        <v>440917</v>
       </c>
       <c r="R86" t="n">
-        <v>6754161</v>
+        <v>6754255</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9982,7 +9982,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129543173</v>
+        <v>129543203</v>
       </c>
       <c r="B87" t="n">
         <v>8450</v>
@@ -10013,7 +10013,7 @@
       <c r="I87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10022,10 +10022,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>440917</v>
+        <v>440946</v>
       </c>
       <c r="R87" t="n">
-        <v>6754255</v>
+        <v>6754123</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10522,10 +10522,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129543142</v>
+        <v>129543153</v>
       </c>
       <c r="B92" t="n">
-        <v>79700</v>
+        <v>90625</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10533,21 +10533,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10557,10 +10557,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>440949</v>
+        <v>440976</v>
       </c>
       <c r="R92" t="n">
-        <v>6754170</v>
+        <v>6754143</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10602,7 +10602,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10629,10 +10629,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129543153</v>
+        <v>129543142</v>
       </c>
       <c r="B93" t="n">
-        <v>90625</v>
+        <v>79700</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10640,21 +10640,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10664,10 +10664,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>440976</v>
+        <v>440949</v>
       </c>
       <c r="R93" t="n">
-        <v>6754143</v>
+        <v>6754170</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10709,7 +10709,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11276,38 +11276,38 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129543189</v>
+        <v>129543170</v>
       </c>
       <c r="B99" t="n">
-        <v>8450</v>
+        <v>57736</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -11316,10 +11316,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>440793</v>
+        <v>440677</v>
       </c>
       <c r="R99" t="n">
-        <v>6754070</v>
+        <v>6754247</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11361,7 +11361,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11612,7 +11617,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129538851</v>
+        <v>129543189</v>
       </c>
       <c r="B102" t="n">
         <v>8450</v>
@@ -11643,7 +11648,7 @@
       <c r="I102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -11652,10 +11657,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>440918</v>
+        <v>440793</v>
       </c>
       <c r="R102" t="n">
-        <v>6754126</v>
+        <v>6754070</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11687,7 +11692,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11697,7 +11702,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11712,50 +11717,50 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129543170</v>
+        <v>129538851</v>
       </c>
       <c r="B103" t="n">
-        <v>57736</v>
+        <v>8450</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11764,10 +11769,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>440677</v>
+        <v>440918</v>
       </c>
       <c r="R103" t="n">
-        <v>6754247</v>
+        <v>6754126</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11799,7 +11804,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11809,12 +11814,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11829,22 +11829,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129543247</v>
+        <v>129543217</v>
       </c>
       <c r="B104" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11852,21 +11852,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11876,10 +11876,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>440894</v>
+        <v>440902</v>
       </c>
       <c r="R104" t="n">
-        <v>6754104</v>
+        <v>6754164</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11911,7 +11911,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11921,7 +11921,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11930,7 +11930,6 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11949,10 +11948,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129538156</v>
+        <v>129538088</v>
       </c>
       <c r="B105" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11960,39 +11959,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>440982</v>
+        <v>441007</v>
       </c>
       <c r="R105" t="n">
-        <v>6754123</v>
+        <v>6754124</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12061,10 +12055,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129543217</v>
+        <v>129538156</v>
       </c>
       <c r="B106" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12072,34 +12066,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>440902</v>
+        <v>440982</v>
       </c>
       <c r="R106" t="n">
-        <v>6754164</v>
+        <v>6754123</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12131,7 +12130,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12141,7 +12140,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12156,22 +12155,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129538088</v>
+        <v>129543247</v>
       </c>
       <c r="B107" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12179,21 +12178,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12203,10 +12202,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>441007</v>
+        <v>440894</v>
       </c>
       <c r="R107" t="n">
-        <v>6754124</v>
+        <v>6754104</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12238,7 +12237,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12248,7 +12247,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12257,18 +12256,19 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>

--- a/artfynd/A 45199-2025 artfynd.xlsx
+++ b/artfynd/A 45199-2025 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129539829</v>
+        <v>129539413</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440861</v>
+        <v>440775</v>
       </c>
       <c r="R2" t="n">
-        <v>6754168</v>
+        <v>6753988</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,50 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129539413</v>
+        <v>129539829</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440775</v>
+        <v>440861</v>
       </c>
       <c r="R3" t="n">
-        <v>6753988</v>
+        <v>6754168</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129543168</v>
+        <v>129543158</v>
       </c>
       <c r="B4" t="n">
-        <v>92879</v>
+        <v>91618</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4365</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440718</v>
+        <v>440892</v>
       </c>
       <c r="R4" t="n">
-        <v>6754157</v>
+        <v>6754225</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129543158</v>
+        <v>129539462</v>
       </c>
       <c r="B5" t="n">
-        <v>91614</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440892</v>
+        <v>440787</v>
       </c>
       <c r="R5" t="n">
-        <v>6754225</v>
+        <v>6753947</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,62 +1096,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129543183</v>
+        <v>129539852</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440945</v>
+        <v>440880</v>
       </c>
       <c r="R6" t="n">
-        <v>6754252</v>
+        <v>6754175</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,62 +1203,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129543191</v>
+        <v>129543147</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440733</v>
+        <v>440701</v>
       </c>
       <c r="R7" t="n">
-        <v>6754283</v>
+        <v>6754185</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,7 +1322,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129539316</v>
+        <v>129543191</v>
       </c>
       <c r="B8" t="n">
         <v>8450</v>
@@ -1363,7 +1353,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1372,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440779</v>
+        <v>440733</v>
       </c>
       <c r="R8" t="n">
-        <v>6754008</v>
+        <v>6754283</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,57 +1422,62 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129543240</v>
+        <v>129539316</v>
       </c>
       <c r="B9" t="n">
-        <v>78747</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440736</v>
+        <v>440779</v>
       </c>
       <c r="R9" t="n">
-        <v>6754282</v>
+        <v>6754008</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1524,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,64 +1528,68 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129543238</v>
+        <v>129543183</v>
       </c>
       <c r="B10" t="n">
-        <v>91866</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>65</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440966</v>
+        <v>440945</v>
       </c>
       <c r="R10" t="n">
-        <v>6754151</v>
+        <v>6754252</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1632,7 +1631,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129539852</v>
+        <v>129543240</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1670,21 +1669,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1694,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440880</v>
+        <v>440736</v>
       </c>
       <c r="R11" t="n">
-        <v>6754175</v>
+        <v>6754282</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1739,7 +1738,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,50 +1747,51 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129539462</v>
+        <v>129543238</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>91870</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440787</v>
+        <v>440966</v>
       </c>
       <c r="R12" t="n">
-        <v>6753947</v>
+        <v>6754151</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1861,44 +1861,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129543239</v>
+        <v>129543168</v>
       </c>
       <c r="B13" t="n">
-        <v>80121</v>
+        <v>92883</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6457</v>
+        <v>4365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440708</v>
+        <v>440718</v>
       </c>
       <c r="R13" t="n">
-        <v>6754116</v>
+        <v>6754157</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1953,12 +1953,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,32 +1980,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129543147</v>
+        <v>129543239</v>
       </c>
       <c r="B14" t="n">
-        <v>79700</v>
+        <v>80121</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6457</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2020,10 +2015,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440701</v>
+        <v>440708</v>
       </c>
       <c r="R14" t="n">
-        <v>6754185</v>
+        <v>6754116</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,7 +2050,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2065,7 +2060,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2092,45 +2092,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129543216</v>
+        <v>129543182</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440945</v>
+        <v>440934</v>
       </c>
       <c r="R15" t="n">
-        <v>6754252</v>
+        <v>6754244</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2199,32 +2204,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129543227</v>
+        <v>129539028</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2234,10 +2239,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440744</v>
+        <v>440970</v>
       </c>
       <c r="R16" t="n">
-        <v>6754336</v>
+        <v>6754114</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2269,7 +2274,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2279,7 +2284,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,44 +2299,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129539028</v>
+        <v>129543227</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2341,10 +2346,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440970</v>
+        <v>440744</v>
       </c>
       <c r="R17" t="n">
-        <v>6754114</v>
+        <v>6754336</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2376,7 +2381,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2386,7 +2391,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2401,62 +2406,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543182</v>
+        <v>129543216</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440934</v>
+        <v>440945</v>
       </c>
       <c r="R18" t="n">
-        <v>6754244</v>
+        <v>6754252</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2739,38 +2739,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129543195</v>
+        <v>129538905</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440708</v>
+        <v>440970</v>
       </c>
       <c r="R21" t="n">
-        <v>6754371</v>
+        <v>6754114</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2839,50 +2839,50 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129538905</v>
+        <v>129543195</v>
       </c>
       <c r="B22" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440970</v>
+        <v>440708</v>
       </c>
       <c r="R22" t="n">
-        <v>6754114</v>
+        <v>6754371</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2951,12 +2951,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3075,7 +3075,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129543234</v>
+        <v>129543229</v>
       </c>
       <c r="B24" t="n">
         <v>79081</v>
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440834</v>
+        <v>440638</v>
       </c>
       <c r="R24" t="n">
-        <v>6754152</v>
+        <v>6754239</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3182,7 +3182,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129539521</v>
+        <v>129543228</v>
       </c>
       <c r="B25" t="n">
         <v>79081</v>
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440725</v>
+        <v>440716</v>
       </c>
       <c r="R25" t="n">
-        <v>6754011</v>
+        <v>6754354</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3277,19 +3277,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129543228</v>
+        <v>129539521</v>
       </c>
       <c r="B26" t="n">
         <v>79081</v>
@@ -3324,10 +3324,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440716</v>
+        <v>440725</v>
       </c>
       <c r="R26" t="n">
-        <v>6754354</v>
+        <v>6754011</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3384,19 +3384,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543229</v>
+        <v>129543234</v>
       </c>
       <c r="B27" t="n">
         <v>79081</v>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440638</v>
+        <v>440834</v>
       </c>
       <c r="R27" t="n">
-        <v>6754239</v>
+        <v>6754152</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3615,7 +3615,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543188</v>
+        <v>129543201</v>
       </c>
       <c r="B29" t="n">
         <v>8450</v>
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440824</v>
+        <v>440885</v>
       </c>
       <c r="R29" t="n">
-        <v>6754063</v>
+        <v>6754148</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3727,7 +3727,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129543201</v>
+        <v>129543196</v>
       </c>
       <c r="B30" t="n">
         <v>8450</v>
@@ -3767,10 +3767,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440885</v>
+        <v>440716</v>
       </c>
       <c r="R30" t="n">
-        <v>6754148</v>
+        <v>6754046</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4063,7 +4063,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129543196</v>
+        <v>129543188</v>
       </c>
       <c r="B33" t="n">
         <v>8450</v>
@@ -4103,10 +4103,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440716</v>
+        <v>440824</v>
       </c>
       <c r="R33" t="n">
-        <v>6754046</v>
+        <v>6754063</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4175,7 +4175,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129543222</v>
+        <v>129543233</v>
       </c>
       <c r="B34" t="n">
         <v>79081</v>
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440728</v>
+        <v>440819</v>
       </c>
       <c r="R34" t="n">
-        <v>6754306</v>
+        <v>6754114</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4282,7 +4282,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129543233</v>
+        <v>129543222</v>
       </c>
       <c r="B35" t="n">
         <v>79081</v>
@@ -4317,10 +4317,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440819</v>
+        <v>440728</v>
       </c>
       <c r="R35" t="n">
-        <v>6754114</v>
+        <v>6754306</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4389,37 +4389,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129539754</v>
+        <v>129543190</v>
       </c>
       <c r="B36" t="n">
-        <v>91614</v>
+        <v>8450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4428,10 +4429,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440820</v>
+        <v>440773</v>
       </c>
       <c r="R36" t="n">
-        <v>6754096</v>
+        <v>6754088</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4463,7 +4464,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4473,7 +4474,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4488,22 +4489,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129543159</v>
+        <v>129539754</v>
       </c>
       <c r="B37" t="n">
-        <v>91614</v>
+        <v>91618</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4528,17 +4529,21 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440738</v>
+        <v>440820</v>
       </c>
       <c r="R37" t="n">
-        <v>6754021</v>
+        <v>6754096</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4570,7 +4575,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4580,7 +4585,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4595,22 +4600,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129543235</v>
+        <v>129539312</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4618,34 +4623,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440863</v>
+        <v>440779</v>
       </c>
       <c r="R38" t="n">
-        <v>6754131</v>
+        <v>6754008</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4677,7 +4687,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4687,7 +4697,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4702,22 +4712,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129539703</v>
+        <v>129543159</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>91618</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4725,21 +4735,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4749,10 +4759,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440820</v>
+        <v>440738</v>
       </c>
       <c r="R39" t="n">
-        <v>6754096</v>
+        <v>6754021</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4784,7 +4794,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4794,7 +4804,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4809,22 +4819,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129539312</v>
+        <v>129543235</v>
       </c>
       <c r="B40" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4832,39 +4842,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440779</v>
+        <v>440863</v>
       </c>
       <c r="R40" t="n">
-        <v>6754008</v>
+        <v>6754131</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,7 +4901,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4906,7 +4911,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4921,62 +4926,57 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129543190</v>
+        <v>129539703</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440773</v>
+        <v>440820</v>
       </c>
       <c r="R41" t="n">
-        <v>6754088</v>
+        <v>6754096</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5033,12 +5033,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5152,7 +5152,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129539589</v>
+        <v>129538433</v>
       </c>
       <c r="B43" t="n">
         <v>8450</v>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440769</v>
+        <v>440937</v>
       </c>
       <c r="R43" t="n">
-        <v>6754064</v>
+        <v>6754141</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5264,7 +5264,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129538433</v>
+        <v>129539589</v>
       </c>
       <c r="B44" t="n">
         <v>8450</v>
@@ -5304,10 +5304,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440937</v>
+        <v>440769</v>
       </c>
       <c r="R44" t="n">
-        <v>6754141</v>
+        <v>6754064</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5483,7 +5483,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129543194</v>
+        <v>129539814</v>
       </c>
       <c r="B46" t="n">
         <v>8450</v>
@@ -5523,10 +5523,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440745</v>
+        <v>440861</v>
       </c>
       <c r="R46" t="n">
-        <v>6754333</v>
+        <v>6754168</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5583,19 +5583,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129539814</v>
+        <v>129538170</v>
       </c>
       <c r="B47" t="n">
         <v>8450</v>
@@ -5626,7 +5626,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5635,10 +5635,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440861</v>
+        <v>440982</v>
       </c>
       <c r="R47" t="n">
-        <v>6754168</v>
+        <v>6754123</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5707,7 +5707,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129538170</v>
+        <v>129543194</v>
       </c>
       <c r="B48" t="n">
         <v>8450</v>
@@ -5738,7 +5738,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440982</v>
+        <v>440745</v>
       </c>
       <c r="R48" t="n">
-        <v>6754123</v>
+        <v>6754333</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5807,19 +5807,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129543220</v>
+        <v>129543236</v>
       </c>
       <c r="B49" t="n">
         <v>79081</v>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440851</v>
+        <v>440970</v>
       </c>
       <c r="R49" t="n">
-        <v>6754062</v>
+        <v>6754114</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5926,7 +5926,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129543236</v>
+        <v>129543220</v>
       </c>
       <c r="B50" t="n">
         <v>79081</v>
@@ -5961,10 +5961,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440970</v>
+        <v>440851</v>
       </c>
       <c r="R50" t="n">
-        <v>6754114</v>
+        <v>6754062</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7248,7 +7248,7 @@
         <v>129543144</v>
       </c>
       <c r="B62" t="n">
-        <v>91516</v>
+        <v>91520</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7352,10 +7352,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129543245</v>
+        <v>129539371</v>
       </c>
       <c r="B63" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7363,21 +7363,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7387,10 +7387,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440986</v>
+        <v>440769</v>
       </c>
       <c r="R63" t="n">
-        <v>6754157</v>
+        <v>6754008</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7441,69 +7441,63 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129543179</v>
+        <v>129543245</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>78747</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440821</v>
+        <v>440986</v>
       </c>
       <c r="R64" t="n">
-        <v>6754050</v>
+        <v>6754157</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7535,7 +7529,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7545,7 +7539,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7554,6 +7548,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7572,38 +7567,38 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129543176</v>
+        <v>129543157</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>57896</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7612,10 +7607,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440820</v>
+        <v>440759</v>
       </c>
       <c r="R65" t="n">
-        <v>6754121</v>
+        <v>6754342</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7647,7 +7642,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7657,7 +7652,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7684,7 +7679,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129543192</v>
+        <v>129543179</v>
       </c>
       <c r="B66" t="n">
         <v>8450</v>
@@ -7724,10 +7719,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440742</v>
+        <v>440821</v>
       </c>
       <c r="R66" t="n">
-        <v>6754310</v>
+        <v>6754050</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7759,7 +7754,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7769,7 +7764,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7796,45 +7791,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129539371</v>
+        <v>129543176</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>440769</v>
+        <v>440820</v>
       </c>
       <c r="R67" t="n">
-        <v>6754008</v>
+        <v>6754121</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7891,50 +7891,50 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129543157</v>
+        <v>129543192</v>
       </c>
       <c r="B68" t="n">
-        <v>57896</v>
+        <v>8450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7943,10 +7943,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440759</v>
+        <v>440742</v>
       </c>
       <c r="R68" t="n">
-        <v>6754342</v>
+        <v>6754310</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8123,10 +8123,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129543225</v>
+        <v>129543141</v>
       </c>
       <c r="B70" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8134,21 +8134,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8158,10 +8158,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440764</v>
+        <v>440974</v>
       </c>
       <c r="R70" t="n">
-        <v>6754320</v>
+        <v>6754141</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8193,7 +8193,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8230,10 +8230,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129543218</v>
+        <v>129538247</v>
       </c>
       <c r="B71" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8241,34 +8241,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>440888</v>
+        <v>440944</v>
       </c>
       <c r="R71" t="n">
-        <v>6754157</v>
+        <v>6754122</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8300,7 +8305,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8310,7 +8315,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8325,57 +8330,62 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129538126</v>
+        <v>129543199</v>
       </c>
       <c r="B72" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>441002</v>
+        <v>440855</v>
       </c>
       <c r="R72" t="n">
-        <v>6754112</v>
+        <v>6754166</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8407,7 +8417,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8417,7 +8427,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8432,57 +8442,62 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129543224</v>
+        <v>129543178</v>
       </c>
       <c r="B73" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>440774</v>
+        <v>440816</v>
       </c>
       <c r="R73" t="n">
-        <v>6754313</v>
+        <v>6754178</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8514,7 +8529,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8524,7 +8539,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8551,10 +8566,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129538247</v>
+        <v>129543218</v>
       </c>
       <c r="B74" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8562,39 +8577,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>440944</v>
+        <v>440888</v>
       </c>
       <c r="R74" t="n">
-        <v>6754122</v>
+        <v>6754157</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8626,7 +8636,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8636,7 +8646,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8651,22 +8661,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129543141</v>
+        <v>129543225</v>
       </c>
       <c r="B75" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8674,21 +8684,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8698,10 +8708,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>440974</v>
+        <v>440764</v>
       </c>
       <c r="R75" t="n">
-        <v>6754141</v>
+        <v>6754320</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8733,7 +8743,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8743,7 +8753,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8770,10 +8780,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129543143</v>
+        <v>129538126</v>
       </c>
       <c r="B76" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8781,21 +8791,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8805,10 +8815,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>440893</v>
+        <v>441002</v>
       </c>
       <c r="R76" t="n">
-        <v>6754230</v>
+        <v>6754112</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8840,7 +8850,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8850,7 +8860,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8865,62 +8875,57 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129543178</v>
+        <v>129543143</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>440816</v>
+        <v>440893</v>
       </c>
       <c r="R77" t="n">
-        <v>6754178</v>
+        <v>6754230</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8952,7 +8957,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8962,7 +8967,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8989,50 +8994,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129543199</v>
+        <v>129543224</v>
       </c>
       <c r="B78" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>440855</v>
+        <v>440774</v>
       </c>
       <c r="R78" t="n">
-        <v>6754166</v>
+        <v>6754313</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9101,32 +9101,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129543154</v>
+        <v>129543164</v>
       </c>
       <c r="B79" t="n">
-        <v>90625</v>
+        <v>80215</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1962</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9136,10 +9136,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>440770</v>
+        <v>440708</v>
       </c>
       <c r="R79" t="n">
-        <v>6754101</v>
+        <v>6754116</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9171,7 +9171,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9181,7 +9181,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9208,32 +9213,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129543164</v>
+        <v>129543154</v>
       </c>
       <c r="B80" t="n">
-        <v>80215</v>
+        <v>90629</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>1962</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9243,10 +9248,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>440708</v>
+        <v>440770</v>
       </c>
       <c r="R80" t="n">
-        <v>6754116</v>
+        <v>6754101</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9278,7 +9283,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9288,12 +9293,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9320,45 +9320,50 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129543215</v>
+        <v>129543155</v>
       </c>
       <c r="B81" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>440930</v>
+        <v>440878</v>
       </c>
       <c r="R81" t="n">
-        <v>6754182</v>
+        <v>6754126</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9390,7 +9395,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9400,7 +9405,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9427,7 +9432,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129543221</v>
+        <v>129543215</v>
       </c>
       <c r="B82" t="n">
         <v>79081</v>
@@ -9462,10 +9467,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>440739</v>
+        <v>440930</v>
       </c>
       <c r="R82" t="n">
-        <v>6754147</v>
+        <v>6754182</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9497,7 +9502,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9507,7 +9512,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9534,50 +9539,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129543155</v>
+        <v>129543221</v>
       </c>
       <c r="B83" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>440878</v>
+        <v>440739</v>
       </c>
       <c r="R83" t="n">
-        <v>6754126</v>
+        <v>6754147</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9646,7 +9646,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129538573</v>
+        <v>129543173</v>
       </c>
       <c r="B84" t="n">
         <v>8450</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>440932</v>
+        <v>440917</v>
       </c>
       <c r="R84" t="n">
-        <v>6754178</v>
+        <v>6754255</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9746,19 +9746,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129543202</v>
+        <v>129538573</v>
       </c>
       <c r="B85" t="n">
         <v>8450</v>
@@ -9789,7 +9789,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9798,10 +9798,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>440918</v>
+        <v>440932</v>
       </c>
       <c r="R85" t="n">
-        <v>6754161</v>
+        <v>6754178</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9858,19 +9858,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129543173</v>
+        <v>129543203</v>
       </c>
       <c r="B86" t="n">
         <v>8450</v>
@@ -9901,7 +9901,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9910,10 +9910,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>440917</v>
+        <v>440946</v>
       </c>
       <c r="R86" t="n">
-        <v>6754255</v>
+        <v>6754123</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9982,7 +9982,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129543203</v>
+        <v>129543202</v>
       </c>
       <c r="B87" t="n">
         <v>8450</v>
@@ -10022,10 +10022,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>440946</v>
+        <v>440918</v>
       </c>
       <c r="R87" t="n">
-        <v>6754123</v>
+        <v>6754161</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10094,10 +10094,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129543171</v>
+        <v>129538100</v>
       </c>
       <c r="B88" t="n">
-        <v>91646</v>
+        <v>79700</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10105,21 +10105,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10129,10 +10129,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>440996</v>
+        <v>441007</v>
       </c>
       <c r="R88" t="n">
-        <v>6754160</v>
+        <v>6754124</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10189,19 +10189,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129538198</v>
+        <v>129543223</v>
       </c>
       <c r="B89" t="n">
         <v>79081</v>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>440969</v>
+        <v>440754</v>
       </c>
       <c r="R89" t="n">
-        <v>6754129</v>
+        <v>6754304</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10271,7 +10271,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10296,22 +10296,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129543223</v>
+        <v>129543171</v>
       </c>
       <c r="B90" t="n">
-        <v>79081</v>
+        <v>91650</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10319,21 +10319,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10343,10 +10343,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>440754</v>
+        <v>440996</v>
       </c>
       <c r="R90" t="n">
-        <v>6754304</v>
+        <v>6754160</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10378,7 +10378,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10415,10 +10415,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129538100</v>
+        <v>129538198</v>
       </c>
       <c r="B91" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10426,21 +10426,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10450,10 +10450,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>441007</v>
+        <v>440969</v>
       </c>
       <c r="R91" t="n">
-        <v>6754124</v>
+        <v>6754129</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10525,7 +10525,7 @@
         <v>129543153</v>
       </c>
       <c r="B92" t="n">
-        <v>90625</v>
+        <v>90629</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129543231</v>
+        <v>129543232</v>
       </c>
       <c r="B95" t="n">
         <v>79081</v>
@@ -10883,10 +10883,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>440769</v>
+        <v>440798</v>
       </c>
       <c r="R95" t="n">
-        <v>6754066</v>
+        <v>6754119</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10918,7 +10918,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10928,7 +10928,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10955,7 +10955,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129543232</v>
+        <v>129543214</v>
       </c>
       <c r="B96" t="n">
         <v>79081</v>
@@ -10990,10 +10990,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>440798</v>
+        <v>440948</v>
       </c>
       <c r="R96" t="n">
-        <v>6754119</v>
+        <v>6754156</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11062,7 +11062,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129543214</v>
+        <v>129543231</v>
       </c>
       <c r="B97" t="n">
         <v>79081</v>
@@ -11097,10 +11097,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>440948</v>
+        <v>440769</v>
       </c>
       <c r="R97" t="n">
-        <v>6754156</v>
+        <v>6754066</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11132,7 +11132,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11169,45 +11169,50 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129543152</v>
+        <v>129543189</v>
       </c>
       <c r="B98" t="n">
-        <v>90625</v>
+        <v>8450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>440718</v>
+        <v>440793</v>
       </c>
       <c r="R98" t="n">
-        <v>6754157</v>
+        <v>6754070</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11239,7 +11244,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11249,7 +11254,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11276,38 +11281,38 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129543170</v>
+        <v>129538851</v>
       </c>
       <c r="B99" t="n">
-        <v>57736</v>
+        <v>8450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -11316,10 +11321,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>440677</v>
+        <v>440918</v>
       </c>
       <c r="R99" t="n">
-        <v>6754247</v>
+        <v>6754126</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11351,7 +11356,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11361,12 +11366,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11381,19 +11381,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129543174</v>
+        <v>129538483</v>
       </c>
       <c r="B100" t="n">
         <v>8450</v>
@@ -11433,10 +11433,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>440876</v>
+        <v>440916</v>
       </c>
       <c r="R100" t="n">
-        <v>6754211</v>
+        <v>6754159</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11493,19 +11493,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129538483</v>
+        <v>129543174</v>
       </c>
       <c r="B101" t="n">
         <v>8450</v>
@@ -11545,10 +11545,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>440916</v>
+        <v>440876</v>
       </c>
       <c r="R101" t="n">
-        <v>6754159</v>
+        <v>6754211</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11605,50 +11605,50 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129543189</v>
+        <v>129543170</v>
       </c>
       <c r="B102" t="n">
-        <v>8450</v>
+        <v>57736</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -11657,10 +11657,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>440793</v>
+        <v>440677</v>
       </c>
       <c r="R102" t="n">
-        <v>6754070</v>
+        <v>6754247</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11692,7 +11692,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11702,7 +11702,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11729,50 +11734,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129538851</v>
+        <v>129543152</v>
       </c>
       <c r="B103" t="n">
-        <v>8450</v>
+        <v>90629</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>1962</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>440918</v>
+        <v>440718</v>
       </c>
       <c r="R103" t="n">
-        <v>6754126</v>
+        <v>6754157</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11829,22 +11829,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129543217</v>
+        <v>129543247</v>
       </c>
       <c r="B104" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11852,21 +11852,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11876,10 +11876,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>440902</v>
+        <v>440894</v>
       </c>
       <c r="R104" t="n">
-        <v>6754164</v>
+        <v>6754104</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11911,7 +11911,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11921,7 +11921,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11930,6 +11930,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11948,10 +11949,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129538088</v>
+        <v>129538156</v>
       </c>
       <c r="B105" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11959,34 +11960,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>441007</v>
+        <v>440982</v>
       </c>
       <c r="R105" t="n">
-        <v>6754124</v>
+        <v>6754123</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12055,10 +12061,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129538156</v>
+        <v>129543217</v>
       </c>
       <c r="B106" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12066,39 +12072,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>440982</v>
+        <v>440902</v>
       </c>
       <c r="R106" t="n">
-        <v>6754123</v>
+        <v>6754164</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12130,7 +12131,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12140,7 +12141,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12155,22 +12156,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129543247</v>
+        <v>129538088</v>
       </c>
       <c r="B107" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12178,21 +12179,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12202,10 +12203,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>440894</v>
+        <v>441007</v>
       </c>
       <c r="R107" t="n">
-        <v>6754104</v>
+        <v>6754124</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12237,7 +12238,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12247,7 +12248,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12256,19 +12257,18 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>

--- a/artfynd/A 45199-2025 artfynd.xlsx
+++ b/artfynd/A 45199-2025 artfynd.xlsx
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129543158</v>
+        <v>129543240</v>
       </c>
       <c r="B4" t="n">
-        <v>91618</v>
+        <v>78747</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440892</v>
+        <v>440736</v>
       </c>
       <c r="R4" t="n">
-        <v>6754225</v>
+        <v>6754282</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,6 +983,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1001,32 +1002,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129539462</v>
+        <v>129543238</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440787</v>
+        <v>440966</v>
       </c>
       <c r="R5" t="n">
-        <v>6753947</v>
+        <v>6754151</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1072,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1082,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,22 +1097,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129539852</v>
+        <v>129543158</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>91620</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1120,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440880</v>
+        <v>440892</v>
       </c>
       <c r="R6" t="n">
-        <v>6754175</v>
+        <v>6754225</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1179,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1189,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,44 +1204,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129543147</v>
+        <v>129543168</v>
       </c>
       <c r="B7" t="n">
-        <v>79700</v>
+        <v>92885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440701</v>
+        <v>440718</v>
       </c>
       <c r="R7" t="n">
-        <v>6754185</v>
+        <v>6754157</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1286,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1296,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,10 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129543191</v>
+        <v>129543239</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>80121</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,39 +1334,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6457</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440733</v>
+        <v>440708</v>
       </c>
       <c r="R8" t="n">
-        <v>6754283</v>
+        <v>6754116</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1393,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1403,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,50 +1435,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129539316</v>
+        <v>129543147</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440779</v>
+        <v>440701</v>
       </c>
       <c r="R9" t="n">
-        <v>6754008</v>
+        <v>6754185</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,7 +1505,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1515,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,62 +1530,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129543183</v>
+        <v>129539852</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440945</v>
+        <v>440880</v>
       </c>
       <c r="R10" t="n">
-        <v>6754252</v>
+        <v>6754175</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,7 +1612,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1631,7 +1622,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1646,22 +1637,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543240</v>
+        <v>129539462</v>
       </c>
       <c r="B11" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,21 +1660,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1693,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440736</v>
+        <v>440787</v>
       </c>
       <c r="R11" t="n">
-        <v>6754282</v>
+        <v>6753947</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,7 +1719,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,7 +1729,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1747,64 +1738,68 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129543238</v>
+        <v>129543183</v>
       </c>
       <c r="B12" t="n">
-        <v>91870</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440966</v>
+        <v>440945</v>
       </c>
       <c r="R12" t="n">
-        <v>6754151</v>
+        <v>6754252</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,7 +1831,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1846,7 +1841,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1873,45 +1868,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129543168</v>
+        <v>129543191</v>
       </c>
       <c r="B13" t="n">
-        <v>92883</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4365</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440718</v>
+        <v>440733</v>
       </c>
       <c r="R13" t="n">
-        <v>6754157</v>
+        <v>6754283</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1980,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129543239</v>
+        <v>129539316</v>
       </c>
       <c r="B14" t="n">
-        <v>80121</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,34 +1991,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6457</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440708</v>
+        <v>440779</v>
       </c>
       <c r="R14" t="n">
-        <v>6754116</v>
+        <v>6754008</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,7 +2055,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2060,12 +2065,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2080,62 +2080,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129543182</v>
+        <v>129543216</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440934</v>
+        <v>440945</v>
       </c>
       <c r="R15" t="n">
-        <v>6754244</v>
+        <v>6754252</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2204,32 +2199,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129539028</v>
+        <v>129543227</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2239,10 +2234,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440970</v>
+        <v>440744</v>
       </c>
       <c r="R16" t="n">
-        <v>6754114</v>
+        <v>6754336</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,7 +2269,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2284,7 +2279,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2299,44 +2294,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129543227</v>
+        <v>129539028</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2346,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440744</v>
+        <v>440970</v>
       </c>
       <c r="R17" t="n">
-        <v>6754336</v>
+        <v>6754114</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2381,7 +2376,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2391,7 +2386,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,57 +2401,62 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543216</v>
+        <v>129543182</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440945</v>
+        <v>440934</v>
       </c>
       <c r="R18" t="n">
-        <v>6754252</v>
+        <v>6754244</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2525,45 +2525,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129543219</v>
+        <v>129543195</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440890</v>
+        <v>440708</v>
       </c>
       <c r="R19" t="n">
-        <v>6754082</v>
+        <v>6754371</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2595,7 +2600,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2605,7 +2610,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2632,45 +2637,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129538675</v>
+        <v>129539529</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440902</v>
+        <v>440725</v>
       </c>
       <c r="R20" t="n">
-        <v>6754135</v>
+        <v>6754011</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2702,7 +2712,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2712,7 +2722,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2851,50 +2861,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129543195</v>
+        <v>129543219</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440708</v>
+        <v>440890</v>
       </c>
       <c r="R22" t="n">
-        <v>6754371</v>
+        <v>6754082</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2926,7 +2931,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2936,7 +2941,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2963,50 +2968,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129539529</v>
+        <v>129538675</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440725</v>
+        <v>440902</v>
       </c>
       <c r="R23" t="n">
-        <v>6754011</v>
+        <v>6754135</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3075,10 +3075,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129543229</v>
+        <v>129538680</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3086,34 +3086,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440638</v>
+        <v>440918</v>
       </c>
       <c r="R24" t="n">
-        <v>6754239</v>
+        <v>6754126</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3145,7 +3150,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3155,7 +3160,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3170,19 +3175,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129543228</v>
+        <v>129543234</v>
       </c>
       <c r="B25" t="n">
         <v>79081</v>
@@ -3217,10 +3222,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440716</v>
+        <v>440834</v>
       </c>
       <c r="R25" t="n">
-        <v>6754354</v>
+        <v>6754152</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3252,7 +3257,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3262,7 +3267,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3396,7 +3401,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543234</v>
+        <v>129543228</v>
       </c>
       <c r="B27" t="n">
         <v>79081</v>
@@ -3431,10 +3436,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440834</v>
+        <v>440716</v>
       </c>
       <c r="R27" t="n">
-        <v>6754152</v>
+        <v>6754354</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3466,7 +3471,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3476,7 +3481,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3503,10 +3508,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129538680</v>
+        <v>129543229</v>
       </c>
       <c r="B28" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3514,39 +3519,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440918</v>
+        <v>440638</v>
       </c>
       <c r="R28" t="n">
-        <v>6754126</v>
+        <v>6754239</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3603,62 +3603,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543201</v>
+        <v>129543222</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440885</v>
+        <v>440728</v>
       </c>
       <c r="R29" t="n">
-        <v>6754148</v>
+        <v>6754306</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3690,7 +3685,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3700,7 +3695,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3727,50 +3722,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129543196</v>
+        <v>129543233</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440716</v>
+        <v>440819</v>
       </c>
       <c r="R30" t="n">
-        <v>6754046</v>
+        <v>6754114</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3802,7 +3792,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3812,7 +3802,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3839,7 +3829,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129543187</v>
+        <v>129543188</v>
       </c>
       <c r="B31" t="n">
         <v>8450</v>
@@ -3879,10 +3869,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440887</v>
+        <v>440824</v>
       </c>
       <c r="R31" t="n">
-        <v>6754181</v>
+        <v>6754063</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3914,7 +3904,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3924,7 +3914,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3951,7 +3941,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129543193</v>
+        <v>129543201</v>
       </c>
       <c r="B32" t="n">
         <v>8450</v>
@@ -3991,10 +3981,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440757</v>
+        <v>440885</v>
       </c>
       <c r="R32" t="n">
-        <v>6754338</v>
+        <v>6754148</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4026,7 +4016,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4036,7 +4026,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4063,7 +4053,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129543188</v>
+        <v>129543187</v>
       </c>
       <c r="B33" t="n">
         <v>8450</v>
@@ -4103,10 +4093,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440824</v>
+        <v>440887</v>
       </c>
       <c r="R33" t="n">
-        <v>6754063</v>
+        <v>6754181</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4138,7 +4128,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4148,7 +4138,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4175,45 +4165,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129543233</v>
+        <v>129543193</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440819</v>
+        <v>440757</v>
       </c>
       <c r="R34" t="n">
-        <v>6754114</v>
+        <v>6754338</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4245,7 +4240,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4255,7 +4250,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4282,45 +4277,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129543222</v>
+        <v>129543196</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440728</v>
+        <v>440716</v>
       </c>
       <c r="R35" t="n">
-        <v>6754306</v>
+        <v>6754046</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4389,38 +4389,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129543190</v>
+        <v>129539312</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440773</v>
+        <v>440779</v>
       </c>
       <c r="R36" t="n">
-        <v>6754088</v>
+        <v>6754008</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4489,12 +4489,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4504,7 +4504,7 @@
         <v>129539754</v>
       </c>
       <c r="B37" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4612,10 +4612,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129539312</v>
+        <v>129543159</v>
       </c>
       <c r="B38" t="n">
-        <v>57733</v>
+        <v>91620</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4623,39 +4623,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440779</v>
+        <v>440738</v>
       </c>
       <c r="R38" t="n">
-        <v>6754008</v>
+        <v>6754021</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4687,7 +4682,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4697,7 +4692,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4712,22 +4707,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129543159</v>
+        <v>129543235</v>
       </c>
       <c r="B39" t="n">
-        <v>91618</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4735,21 +4730,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4759,10 +4754,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440738</v>
+        <v>440863</v>
       </c>
       <c r="R39" t="n">
-        <v>6754021</v>
+        <v>6754131</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4794,7 +4789,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4804,7 +4799,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4831,7 +4826,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543235</v>
+        <v>129539703</v>
       </c>
       <c r="B40" t="n">
         <v>79081</v>
@@ -4866,10 +4861,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440863</v>
+        <v>440820</v>
       </c>
       <c r="R40" t="n">
-        <v>6754131</v>
+        <v>6754096</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4901,7 +4896,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4911,7 +4906,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4926,57 +4921,62 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129539703</v>
+        <v>129543190</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440820</v>
+        <v>440773</v>
       </c>
       <c r="R41" t="n">
-        <v>6754096</v>
+        <v>6754088</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5033,12 +5033,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5152,7 +5152,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129538433</v>
+        <v>129539589</v>
       </c>
       <c r="B43" t="n">
         <v>8450</v>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440937</v>
+        <v>440769</v>
       </c>
       <c r="R43" t="n">
-        <v>6754141</v>
+        <v>6754064</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5264,7 +5264,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129539589</v>
+        <v>129538433</v>
       </c>
       <c r="B44" t="n">
         <v>8450</v>
@@ -5304,10 +5304,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440769</v>
+        <v>440937</v>
       </c>
       <c r="R44" t="n">
-        <v>6754064</v>
+        <v>6754141</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5483,7 +5483,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129539814</v>
+        <v>129543194</v>
       </c>
       <c r="B46" t="n">
         <v>8450</v>
@@ -5523,10 +5523,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440861</v>
+        <v>440745</v>
       </c>
       <c r="R46" t="n">
-        <v>6754168</v>
+        <v>6754333</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5583,19 +5583,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129538170</v>
+        <v>129539814</v>
       </c>
       <c r="B47" t="n">
         <v>8450</v>
@@ -5626,7 +5626,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5635,10 +5635,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440982</v>
+        <v>440861</v>
       </c>
       <c r="R47" t="n">
-        <v>6754123</v>
+        <v>6754168</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5707,7 +5707,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129543194</v>
+        <v>129538170</v>
       </c>
       <c r="B48" t="n">
         <v>8450</v>
@@ -5738,7 +5738,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440745</v>
+        <v>440982</v>
       </c>
       <c r="R48" t="n">
-        <v>6754333</v>
+        <v>6754123</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5807,19 +5807,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129543236</v>
+        <v>129543220</v>
       </c>
       <c r="B49" t="n">
         <v>79081</v>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440970</v>
+        <v>440851</v>
       </c>
       <c r="R49" t="n">
-        <v>6754114</v>
+        <v>6754062</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5926,10 +5926,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129543220</v>
+        <v>129539404</v>
       </c>
       <c r="B50" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5937,34 +5937,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440851</v>
+        <v>440775</v>
       </c>
       <c r="R50" t="n">
-        <v>6754062</v>
+        <v>6753988</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5996,7 +6001,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6006,7 +6011,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6021,19 +6026,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129539404</v>
+        <v>129543166</v>
       </c>
       <c r="B51" t="n">
         <v>57733</v>
@@ -6073,10 +6078,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440775</v>
+        <v>440772</v>
       </c>
       <c r="R51" t="n">
-        <v>6753988</v>
+        <v>6754089</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6108,7 +6113,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6118,7 +6123,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6133,22 +6138,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129543166</v>
+        <v>129543236</v>
       </c>
       <c r="B52" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6156,39 +6161,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440772</v>
+        <v>440970</v>
       </c>
       <c r="R52" t="n">
-        <v>6754089</v>
+        <v>6754114</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6369,10 +6369,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129538554</v>
+        <v>129543230</v>
       </c>
       <c r="B54" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6380,21 +6380,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6404,10 +6404,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440919</v>
+        <v>440779</v>
       </c>
       <c r="R54" t="n">
-        <v>6754174</v>
+        <v>6754063</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6464,22 +6464,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129543230</v>
+        <v>129538554</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6487,21 +6487,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6511,10 +6511,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440779</v>
+        <v>440919</v>
       </c>
       <c r="R55" t="n">
-        <v>6754063</v>
+        <v>6754174</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6571,12 +6571,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6807,10 +6807,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129538786</v>
+        <v>129543144</v>
       </c>
       <c r="B58" t="n">
-        <v>79081</v>
+        <v>91522</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6818,21 +6818,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440918</v>
+        <v>440718</v>
       </c>
       <c r="R58" t="n">
-        <v>6754126</v>
+        <v>6754215</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6902,19 +6902,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129543213</v>
+        <v>129538786</v>
       </c>
       <c r="B59" t="n">
         <v>79081</v>
@@ -6949,10 +6949,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440996</v>
+        <v>440918</v>
       </c>
       <c r="R59" t="n">
-        <v>6754160</v>
+        <v>6754126</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7009,62 +7009,57 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129543181</v>
+        <v>129543213</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440990</v>
+        <v>440996</v>
       </c>
       <c r="R60" t="n">
-        <v>6754140</v>
+        <v>6754160</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7096,7 +7091,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7106,7 +7101,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7133,7 +7128,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129543197</v>
+        <v>129543181</v>
       </c>
       <c r="B61" t="n">
         <v>8450</v>
@@ -7173,10 +7168,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>440785</v>
+        <v>440990</v>
       </c>
       <c r="R61" t="n">
-        <v>6754107</v>
+        <v>6754140</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7208,7 +7203,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7218,7 +7213,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7245,45 +7240,50 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129543144</v>
+        <v>129543197</v>
       </c>
       <c r="B62" t="n">
-        <v>91520</v>
+        <v>8450</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3242</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>440718</v>
+        <v>440785</v>
       </c>
       <c r="R62" t="n">
-        <v>6754215</v>
+        <v>6754107</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7315,7 +7315,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7352,10 +7352,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129539371</v>
+        <v>129543245</v>
       </c>
       <c r="B63" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7363,21 +7363,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7387,10 +7387,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440769</v>
+        <v>440986</v>
       </c>
       <c r="R63" t="n">
-        <v>6754008</v>
+        <v>6754157</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7441,28 +7441,29 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129543245</v>
+        <v>129539371</v>
       </c>
       <c r="B64" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7470,21 +7471,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7494,10 +7495,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440986</v>
+        <v>440769</v>
       </c>
       <c r="R64" t="n">
-        <v>6754157</v>
+        <v>6754008</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7529,7 +7530,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7539,7 +7540,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7548,19 +7549,18 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -8015,10 +8015,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129543246</v>
+        <v>129543225</v>
       </c>
       <c r="B69" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8026,21 +8026,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8050,10 +8050,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440893</v>
+        <v>440764</v>
       </c>
       <c r="R69" t="n">
-        <v>6754230</v>
+        <v>6754320</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8104,7 +8104,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8123,10 +8122,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129543141</v>
+        <v>129543246</v>
       </c>
       <c r="B70" t="n">
-        <v>79700</v>
+        <v>78747</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8134,21 +8133,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8158,10 +8157,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440974</v>
+        <v>440893</v>
       </c>
       <c r="R70" t="n">
-        <v>6754141</v>
+        <v>6754230</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8193,7 +8192,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8203,7 +8202,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8212,6 +8211,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8342,50 +8342,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129543199</v>
+        <v>129543141</v>
       </c>
       <c r="B72" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>440855</v>
+        <v>440974</v>
       </c>
       <c r="R72" t="n">
-        <v>6754166</v>
+        <v>6754141</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8417,7 +8412,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8427,7 +8422,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8454,50 +8449,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129543178</v>
+        <v>129543218</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>440816</v>
+        <v>440888</v>
       </c>
       <c r="R73" t="n">
-        <v>6754178</v>
+        <v>6754157</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8529,7 +8519,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8539,7 +8529,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8566,7 +8556,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129543218</v>
+        <v>129538126</v>
       </c>
       <c r="B74" t="n">
         <v>79081</v>
@@ -8601,10 +8591,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>440888</v>
+        <v>441002</v>
       </c>
       <c r="R74" t="n">
-        <v>6754157</v>
+        <v>6754112</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8636,7 +8626,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8646,7 +8636,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8661,22 +8651,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129543225</v>
+        <v>129543143</v>
       </c>
       <c r="B75" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8684,21 +8674,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8708,10 +8698,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>440764</v>
+        <v>440893</v>
       </c>
       <c r="R75" t="n">
-        <v>6754320</v>
+        <v>6754230</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8743,7 +8733,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8753,7 +8743,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8780,7 +8770,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129538126</v>
+        <v>129543224</v>
       </c>
       <c r="B76" t="n">
         <v>79081</v>
@@ -8815,10 +8805,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>441002</v>
+        <v>440774</v>
       </c>
       <c r="R76" t="n">
-        <v>6754112</v>
+        <v>6754313</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8850,7 +8840,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8860,7 +8850,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8875,57 +8865,62 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129543143</v>
+        <v>129543178</v>
       </c>
       <c r="B77" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>440893</v>
+        <v>440816</v>
       </c>
       <c r="R77" t="n">
-        <v>6754230</v>
+        <v>6754178</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8957,7 +8952,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8967,7 +8962,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8994,45 +8989,50 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129543224</v>
+        <v>129543199</v>
       </c>
       <c r="B78" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>440774</v>
+        <v>440855</v>
       </c>
       <c r="R78" t="n">
-        <v>6754313</v>
+        <v>6754166</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9213,45 +9213,50 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129543154</v>
+        <v>129543155</v>
       </c>
       <c r="B80" t="n">
-        <v>90629</v>
+        <v>56926</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1962</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>440770</v>
+        <v>440878</v>
       </c>
       <c r="R80" t="n">
-        <v>6754101</v>
+        <v>6754126</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9283,7 +9288,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9293,7 +9298,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9320,50 +9325,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129543155</v>
+        <v>129543154</v>
       </c>
       <c r="B81" t="n">
-        <v>56926</v>
+        <v>90631</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100138</v>
+        <v>1962</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>440878</v>
+        <v>440770</v>
       </c>
       <c r="R81" t="n">
-        <v>6754126</v>
+        <v>6754101</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9646,7 +9646,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129543173</v>
+        <v>129538573</v>
       </c>
       <c r="B84" t="n">
         <v>8450</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>440917</v>
+        <v>440932</v>
       </c>
       <c r="R84" t="n">
-        <v>6754255</v>
+        <v>6754178</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9746,19 +9746,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129538573</v>
+        <v>129543202</v>
       </c>
       <c r="B85" t="n">
         <v>8450</v>
@@ -9789,7 +9789,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9798,10 +9798,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>440932</v>
+        <v>440918</v>
       </c>
       <c r="R85" t="n">
-        <v>6754178</v>
+        <v>6754161</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9858,19 +9858,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129543203</v>
+        <v>129543173</v>
       </c>
       <c r="B86" t="n">
         <v>8450</v>
@@ -9901,7 +9901,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9910,10 +9910,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>440946</v>
+        <v>440917</v>
       </c>
       <c r="R86" t="n">
-        <v>6754123</v>
+        <v>6754255</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9982,7 +9982,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129543202</v>
+        <v>129543203</v>
       </c>
       <c r="B87" t="n">
         <v>8450</v>
@@ -10022,10 +10022,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>440918</v>
+        <v>440946</v>
       </c>
       <c r="R87" t="n">
-        <v>6754161</v>
+        <v>6754123</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10094,10 +10094,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129538100</v>
+        <v>129543171</v>
       </c>
       <c r="B88" t="n">
-        <v>79700</v>
+        <v>91652</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10105,21 +10105,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10129,10 +10129,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>441007</v>
+        <v>440996</v>
       </c>
       <c r="R88" t="n">
-        <v>6754124</v>
+        <v>6754160</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10189,19 +10189,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129543223</v>
+        <v>129538198</v>
       </c>
       <c r="B89" t="n">
         <v>79081</v>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>440754</v>
+        <v>440969</v>
       </c>
       <c r="R89" t="n">
-        <v>6754304</v>
+        <v>6754129</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10271,7 +10271,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10296,22 +10296,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129543171</v>
+        <v>129543223</v>
       </c>
       <c r="B90" t="n">
-        <v>91650</v>
+        <v>79081</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10319,21 +10319,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10343,10 +10343,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>440996</v>
+        <v>440754</v>
       </c>
       <c r="R90" t="n">
-        <v>6754160</v>
+        <v>6754304</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10378,7 +10378,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10415,10 +10415,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129538198</v>
+        <v>129538100</v>
       </c>
       <c r="B91" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10426,21 +10426,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10450,10 +10450,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>440969</v>
+        <v>441007</v>
       </c>
       <c r="R91" t="n">
-        <v>6754129</v>
+        <v>6754124</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10525,7 +10525,7 @@
         <v>129543153</v>
       </c>
       <c r="B92" t="n">
-        <v>90629</v>
+        <v>90631</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10629,45 +10629,50 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129543142</v>
+        <v>129543175</v>
       </c>
       <c r="B93" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>440949</v>
+        <v>440896</v>
       </c>
       <c r="R93" t="n">
-        <v>6754170</v>
+        <v>6754124</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10699,7 +10704,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10709,7 +10714,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10736,50 +10741,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129543175</v>
+        <v>129543142</v>
       </c>
       <c r="B94" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>440896</v>
+        <v>440949</v>
       </c>
       <c r="R94" t="n">
-        <v>6754124</v>
+        <v>6754170</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10848,7 +10848,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129543232</v>
+        <v>129543231</v>
       </c>
       <c r="B95" t="n">
         <v>79081</v>
@@ -10883,10 +10883,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>440798</v>
+        <v>440769</v>
       </c>
       <c r="R95" t="n">
-        <v>6754119</v>
+        <v>6754066</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10918,7 +10918,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10928,7 +10928,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10955,7 +10955,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129543214</v>
+        <v>129543232</v>
       </c>
       <c r="B96" t="n">
         <v>79081</v>
@@ -10990,10 +10990,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>440948</v>
+        <v>440798</v>
       </c>
       <c r="R96" t="n">
-        <v>6754156</v>
+        <v>6754119</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11062,7 +11062,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129543231</v>
+        <v>129543214</v>
       </c>
       <c r="B97" t="n">
         <v>79081</v>
@@ -11097,10 +11097,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>440769</v>
+        <v>440948</v>
       </c>
       <c r="R97" t="n">
-        <v>6754066</v>
+        <v>6754156</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11132,7 +11132,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11169,50 +11169,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129543189</v>
+        <v>129543152</v>
       </c>
       <c r="B98" t="n">
-        <v>8450</v>
+        <v>90631</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>1962</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>440793</v>
+        <v>440718</v>
       </c>
       <c r="R98" t="n">
-        <v>6754070</v>
+        <v>6754157</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11244,7 +11239,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11254,7 +11249,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11281,38 +11276,38 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129538851</v>
+        <v>129543170</v>
       </c>
       <c r="B99" t="n">
-        <v>8450</v>
+        <v>57736</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -11321,10 +11316,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>440918</v>
+        <v>440677</v>
       </c>
       <c r="R99" t="n">
-        <v>6754126</v>
+        <v>6754247</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11356,7 +11351,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11366,7 +11361,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11381,19 +11381,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129538483</v>
+        <v>129543174</v>
       </c>
       <c r="B100" t="n">
         <v>8450</v>
@@ -11433,10 +11433,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>440916</v>
+        <v>440876</v>
       </c>
       <c r="R100" t="n">
-        <v>6754159</v>
+        <v>6754211</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11493,19 +11493,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129543174</v>
+        <v>129538483</v>
       </c>
       <c r="B101" t="n">
         <v>8450</v>
@@ -11545,10 +11545,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>440876</v>
+        <v>440916</v>
       </c>
       <c r="R101" t="n">
-        <v>6754211</v>
+        <v>6754159</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11605,50 +11605,50 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129543170</v>
+        <v>129543189</v>
       </c>
       <c r="B102" t="n">
-        <v>57736</v>
+        <v>8450</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -11657,10 +11657,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>440677</v>
+        <v>440793</v>
       </c>
       <c r="R102" t="n">
-        <v>6754247</v>
+        <v>6754070</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11692,7 +11692,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11702,12 +11702,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11734,45 +11729,50 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129543152</v>
+        <v>129538851</v>
       </c>
       <c r="B103" t="n">
-        <v>90629</v>
+        <v>8450</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>440718</v>
+        <v>440918</v>
       </c>
       <c r="R103" t="n">
-        <v>6754157</v>
+        <v>6754126</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11829,12 +11829,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>

--- a/artfynd/A 45199-2025 artfynd.xlsx
+++ b/artfynd/A 45199-2025 artfynd.xlsx
@@ -2092,7 +2092,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129543216</v>
+        <v>129543227</v>
       </c>
       <c r="B15" t="n">
         <v>79081</v>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440945</v>
+        <v>440744</v>
       </c>
       <c r="R15" t="n">
-        <v>6754252</v>
+        <v>6754336</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2199,7 +2199,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129543227</v>
+        <v>129543216</v>
       </c>
       <c r="B16" t="n">
         <v>79081</v>
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440744</v>
+        <v>440945</v>
       </c>
       <c r="R16" t="n">
-        <v>6754336</v>
+        <v>6754252</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3075,10 +3075,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129538680</v>
+        <v>129543234</v>
       </c>
       <c r="B24" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3086,39 +3086,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fagerheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440918</v>
+        <v>440834</v>
       </c>
       <c r="R24" t="n">
-        <v>6754126</v>
+        <v>6754152</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3150,7 +3145,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3160,7 +3155,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3175,19 +3170,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129543234</v>
+        <v>129539521</v>
       </c>
       <c r="B25" t="n">
         <v>79081</v>
@@ -3222,10 +3217,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440834</v>
+        <v>440725</v>
       </c>
       <c r="R25" t="n">
-        <v>6754152</v>
+        <v>6754011</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3257,7 +3252,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3267,7 +3262,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3282,19 +3277,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129539521</v>
+        <v>129543228</v>
       </c>
       <c r="B26" t="n">
         <v>79081</v>
@@ -3329,10 +3324,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440725</v>
+        <v>440716</v>
       </c>
       <c r="R26" t="n">
-        <v>6754011</v>
+        <v>6754354</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3364,7 +3359,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3374,7 +3369,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3389,19 +3384,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543228</v>
+        <v>129543229</v>
       </c>
       <c r="B27" t="n">
         <v>79081</v>
@@ -3436,10 +3431,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440716</v>
+        <v>440638</v>
       </c>
       <c r="R27" t="n">
-        <v>6754354</v>
+        <v>6754239</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3471,7 +3466,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3481,7 +3476,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3508,10 +3503,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543229</v>
+        <v>129538680</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3519,34 +3514,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>